--- a/data/trans_orig/AIRE_2-Provincia-trans_orig.xlsx
+++ b/data/trans_orig/AIRE_2-Provincia-trans_orig.xlsx
@@ -843,12 +843,12 @@
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>4738</t>
+          <t>4423</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>13488</t>
+          <t>12983</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -858,12 +858,12 @@
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>16,36%</t>
+          <t>15,27%</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>46,57%</t>
+          <t>44,83%</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
@@ -878,12 +878,12 @@
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>8390</t>
+          <t>8406</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>19580</t>
+          <t>19596</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
@@ -893,12 +893,12 @@
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>22,62%</t>
+          <t>22,67%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>52,8%</t>
+          <t>52,84%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -913,12 +913,12 @@
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>15287</t>
+          <t>15937</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>28916</t>
+          <t>29624</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
@@ -928,12 +928,12 @@
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>23,15%</t>
+          <t>24,13%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>43,78%</t>
+          <t>44,85%</t>
         </is>
       </c>
     </row>
@@ -956,12 +956,12 @@
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>10186</t>
+          <t>10808</t>
         </is>
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>19793</t>
+          <t>20986</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
@@ -971,12 +971,12 @@
       </c>
       <c r="H6" s="2" t="inlineStr">
         <is>
-          <t>35,17%</t>
+          <t>37,31%</t>
         </is>
       </c>
       <c r="I6" s="2" t="inlineStr">
         <is>
-          <t>68,34%</t>
+          <t>72,46%</t>
         </is>
       </c>
       <c r="J6" s="2" t="inlineStr">
@@ -991,12 +991,12 @@
       </c>
       <c r="L6" s="2" t="inlineStr">
         <is>
-          <t>15155</t>
+          <t>15328</t>
         </is>
       </c>
       <c r="M6" s="2" t="inlineStr">
         <is>
-          <t>26233</t>
+          <t>26851</t>
         </is>
       </c>
       <c r="N6" s="2" t="inlineStr">
@@ -1006,12 +1006,12 @@
       </c>
       <c r="O6" s="2" t="inlineStr">
         <is>
-          <t>40,87%</t>
+          <t>41,33%</t>
         </is>
       </c>
       <c r="P6" s="2" t="inlineStr">
         <is>
-          <t>70,74%</t>
+          <t>72,41%</t>
         </is>
       </c>
       <c r="Q6" s="2" t="inlineStr">
@@ -1026,12 +1026,12 @@
       </c>
       <c r="S6" s="2" t="inlineStr">
         <is>
-          <t>28616</t>
+          <t>28849</t>
         </is>
       </c>
       <c r="T6" s="2" t="inlineStr">
         <is>
-          <t>43283</t>
+          <t>43107</t>
         </is>
       </c>
       <c r="U6" s="2" t="inlineStr">
@@ -1041,12 +1041,12 @@
       </c>
       <c r="V6" s="2" t="inlineStr">
         <is>
-          <t>43,33%</t>
+          <t>43,68%</t>
         </is>
       </c>
       <c r="W6" s="2" t="inlineStr">
         <is>
-          <t>65,53%</t>
+          <t>65,27%</t>
         </is>
       </c>
     </row>
@@ -1069,12 +1069,12 @@
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>2055</t>
+          <t>1604</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>9414</t>
+          <t>8896</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
@@ -1084,12 +1084,12 @@
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>7,1%</t>
+          <t>5,54%</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>32,5%</t>
+          <t>30,71%</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
@@ -1109,7 +1109,7 @@
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>2648</t>
+          <t>2521</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
@@ -1124,7 +1124,7 @@
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>7,14%</t>
+          <t>6,8%</t>
         </is>
       </c>
       <c r="Q7" s="2" t="inlineStr">
@@ -1139,12 +1139,12 @@
       </c>
       <c r="S7" s="2" t="inlineStr">
         <is>
-          <t>2568</t>
+          <t>2576</t>
         </is>
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>10167</t>
+          <t>10433</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
@@ -1154,12 +1154,12 @@
       </c>
       <c r="V7" s="2" t="inlineStr">
         <is>
-          <t>3,89%</t>
+          <t>3,9%</t>
         </is>
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>15,39%</t>
+          <t>15,8%</t>
         </is>
       </c>
     </row>
@@ -1187,7 +1187,7 @@
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>2990</t>
+          <t>3017</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -1202,7 +1202,7 @@
       </c>
       <c r="I8" s="2" t="inlineStr">
         <is>
-          <t>10,32%</t>
+          <t>10,42%</t>
         </is>
       </c>
       <c r="J8" s="2" t="inlineStr">
@@ -1217,12 +1217,12 @@
       </c>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t>441</t>
+          <t>436</t>
         </is>
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>5546</t>
+          <t>5889</t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr">
@@ -1232,12 +1232,12 @@
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>1,19%</t>
+          <t>1,17%</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t>14,95%</t>
+          <t>15,88%</t>
         </is>
       </c>
       <c r="Q8" s="2" t="inlineStr">
@@ -1252,12 +1252,12 @@
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>664</t>
+          <t>621</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>6736</t>
+          <t>6447</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
@@ -1267,12 +1267,12 @@
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>1,0%</t>
+          <t>0,94%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>10,2%</t>
+          <t>9,76%</t>
         </is>
       </c>
     </row>
@@ -1412,12 +1412,12 @@
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>2055</t>
+          <t>2120</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>18610</t>
+          <t>18763</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -1427,12 +1427,12 @@
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>3,04%</t>
+          <t>3,13%</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>27,51%</t>
+          <t>27,74%</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -1447,12 +1447,12 @@
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>5258</t>
+          <t>5295</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>15578</t>
+          <t>15349</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
@@ -1462,12 +1462,12 @@
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>12,6%</t>
+          <t>12,68%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>37,32%</t>
+          <t>36,77%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -1482,12 +1482,12 @@
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>8736</t>
+          <t>7714</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>29684</t>
+          <t>28630</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
@@ -1497,12 +1497,12 @@
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>7,99%</t>
+          <t>7,05%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>27,14%</t>
+          <t>26,17%</t>
         </is>
       </c>
     </row>
@@ -1525,12 +1525,12 @@
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>22235</t>
+          <t>21438</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>59660</t>
+          <t>58681</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
@@ -1540,12 +1540,12 @@
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>32,87%</t>
+          <t>31,69%</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>88,2%</t>
+          <t>86,75%</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
@@ -1560,12 +1560,12 @@
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>13835</t>
+          <t>13757</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>26236</t>
+          <t>25676</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
@@ -1575,12 +1575,12 @@
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>33,14%</t>
+          <t>32,95%</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
         <is>
-          <t>62,85%</t>
+          <t>61,51%</t>
         </is>
       </c>
       <c r="Q11" s="2" t="inlineStr">
@@ -1595,12 +1595,12 @@
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>43429</t>
+          <t>43033</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>87184</t>
+          <t>88716</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
@@ -1610,12 +1610,12 @@
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>39,7%</t>
+          <t>39,34%</t>
         </is>
       </c>
       <c r="W11" s="2" t="inlineStr">
         <is>
-          <t>79,7%</t>
+          <t>81,1%</t>
         </is>
       </c>
     </row>
@@ -1638,12 +1638,12 @@
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>3754</t>
+          <t>3655</t>
         </is>
       </c>
       <c r="F12" s="2" t="inlineStr">
         <is>
-          <t>24247</t>
+          <t>23776</t>
         </is>
       </c>
       <c r="G12" s="2" t="inlineStr">
@@ -1653,12 +1653,12 @@
       </c>
       <c r="H12" s="2" t="inlineStr">
         <is>
-          <t>5,55%</t>
+          <t>5,4%</t>
         </is>
       </c>
       <c r="I12" s="2" t="inlineStr">
         <is>
-          <t>35,85%</t>
+          <t>35,15%</t>
         </is>
       </c>
       <c r="J12" s="2" t="inlineStr">
@@ -1673,12 +1673,12 @@
       </c>
       <c r="L12" s="2" t="inlineStr">
         <is>
-          <t>5675</t>
+          <t>5726</t>
         </is>
       </c>
       <c r="M12" s="2" t="inlineStr">
         <is>
-          <t>16579</t>
+          <t>17368</t>
         </is>
       </c>
       <c r="N12" s="2" t="inlineStr">
@@ -1688,12 +1688,12 @@
       </c>
       <c r="O12" s="2" t="inlineStr">
         <is>
-          <t>13,59%</t>
+          <t>13,72%</t>
         </is>
       </c>
       <c r="P12" s="2" t="inlineStr">
         <is>
-          <t>39,71%</t>
+          <t>41,6%</t>
         </is>
       </c>
       <c r="Q12" s="2" t="inlineStr">
@@ -1708,12 +1708,12 @@
       </c>
       <c r="S12" s="2" t="inlineStr">
         <is>
-          <t>9541</t>
+          <t>10298</t>
         </is>
       </c>
       <c r="T12" s="2" t="inlineStr">
         <is>
-          <t>34776</t>
+          <t>35177</t>
         </is>
       </c>
       <c r="U12" s="2" t="inlineStr">
@@ -1723,12 +1723,12 @@
       </c>
       <c r="V12" s="2" t="inlineStr">
         <is>
-          <t>8,72%</t>
+          <t>9,41%</t>
         </is>
       </c>
       <c r="W12" s="2" t="inlineStr">
         <is>
-          <t>31,79%</t>
+          <t>32,16%</t>
         </is>
       </c>
     </row>
@@ -1756,7 +1756,7 @@
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>6121</t>
+          <t>6128</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
@@ -1771,7 +1771,7 @@
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>9,05%</t>
+          <t>9,06%</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
@@ -1791,7 +1791,7 @@
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>2025</t>
+          <t>2352</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
@@ -1806,7 +1806,7 @@
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>4,85%</t>
+          <t>5,63%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -1821,12 +1821,12 @@
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>550</t>
+          <t>508</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>6236</t>
+          <t>6679</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
@@ -1836,12 +1836,12 @@
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>0,5%</t>
+          <t>0,46%</t>
         </is>
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>5,7%</t>
+          <t>6,11%</t>
         </is>
       </c>
     </row>
@@ -1869,7 +1869,7 @@
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>6177</t>
+          <t>6026</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -1884,7 +1884,7 @@
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>9,13%</t>
+          <t>8,91%</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr">
@@ -1904,7 +1904,7 @@
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>5087</t>
+          <t>5667</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
@@ -1919,7 +1919,7 @@
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>12,19%</t>
+          <t>13,57%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -1934,12 +1934,12 @@
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>501</t>
+          <t>558</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>7478</t>
+          <t>7417</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
@@ -1949,12 +1949,12 @@
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>0,46%</t>
+          <t>0,51%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>6,84%</t>
+          <t>6,78%</t>
         </is>
       </c>
     </row>
@@ -2129,12 +2129,12 @@
       </c>
       <c r="L16" s="2" t="inlineStr">
         <is>
-          <t>366</t>
+          <t>377</t>
         </is>
       </c>
       <c r="M16" s="2" t="inlineStr">
         <is>
-          <t>3886</t>
+          <t>4494</t>
         </is>
       </c>
       <c r="N16" s="2" t="inlineStr">
@@ -2144,12 +2144,12 @@
       </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>1,42%</t>
+          <t>1,47%</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>15,12%</t>
+          <t>17,49%</t>
         </is>
       </c>
       <c r="Q16" s="2" t="inlineStr">
@@ -2164,12 +2164,12 @@
       </c>
       <c r="S16" s="2" t="inlineStr">
         <is>
-          <t>373</t>
+          <t>371</t>
         </is>
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>4258</t>
+          <t>4264</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
@@ -2184,7 +2184,7 @@
       </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>9,18%</t>
+          <t>9,19%</t>
         </is>
       </c>
     </row>
@@ -2207,12 +2207,12 @@
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>2237</t>
+          <t>2332</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>8073</t>
+          <t>8131</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
@@ -2222,12 +2222,12 @@
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>10,81%</t>
+          <t>11,27%</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>39,01%</t>
+          <t>39,28%</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
@@ -2242,12 +2242,12 @@
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>5631</t>
+          <t>5778</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>13557</t>
+          <t>13710</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
@@ -2257,12 +2257,12 @@
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>21,91%</t>
+          <t>22,48%</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
         <is>
-          <t>52,75%</t>
+          <t>53,35%</t>
         </is>
       </c>
       <c r="Q17" s="2" t="inlineStr">
@@ -2277,12 +2277,12 @@
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>9219</t>
+          <t>9865</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>19589</t>
+          <t>20202</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
@@ -2292,12 +2292,12 @@
       </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>19,87%</t>
+          <t>21,26%</t>
         </is>
       </c>
       <c r="W17" s="2" t="inlineStr">
         <is>
-          <t>42,22%</t>
+          <t>43,54%</t>
         </is>
       </c>
     </row>
@@ -2320,12 +2320,12 @@
       </c>
       <c r="E18" s="2" t="inlineStr">
         <is>
-          <t>6560</t>
+          <t>6823</t>
         </is>
       </c>
       <c r="F18" s="2" t="inlineStr">
         <is>
-          <t>13454</t>
+          <t>13296</t>
         </is>
       </c>
       <c r="G18" s="2" t="inlineStr">
@@ -2335,12 +2335,12 @@
       </c>
       <c r="H18" s="2" t="inlineStr">
         <is>
-          <t>31,69%</t>
+          <t>32,97%</t>
         </is>
       </c>
       <c r="I18" s="2" t="inlineStr">
         <is>
-          <t>65,0%</t>
+          <t>64,24%</t>
         </is>
       </c>
       <c r="J18" s="2" t="inlineStr">
@@ -2355,12 +2355,12 @@
       </c>
       <c r="L18" s="2" t="inlineStr">
         <is>
-          <t>5303</t>
+          <t>5245</t>
         </is>
       </c>
       <c r="M18" s="2" t="inlineStr">
         <is>
-          <t>12484</t>
+          <t>12463</t>
         </is>
       </c>
       <c r="N18" s="2" t="inlineStr">
@@ -2370,12 +2370,12 @@
       </c>
       <c r="O18" s="2" t="inlineStr">
         <is>
-          <t>20,63%</t>
+          <t>20,41%</t>
         </is>
       </c>
       <c r="P18" s="2" t="inlineStr">
         <is>
-          <t>48,58%</t>
+          <t>48,5%</t>
         </is>
       </c>
       <c r="Q18" s="2" t="inlineStr">
@@ -2390,12 +2390,12 @@
       </c>
       <c r="S18" s="2" t="inlineStr">
         <is>
-          <t>13842</t>
+          <t>13743</t>
         </is>
       </c>
       <c r="T18" s="2" t="inlineStr">
         <is>
-          <t>24355</t>
+          <t>23914</t>
         </is>
       </c>
       <c r="U18" s="2" t="inlineStr">
@@ -2405,12 +2405,12 @@
       </c>
       <c r="V18" s="2" t="inlineStr">
         <is>
-          <t>29,83%</t>
+          <t>29,62%</t>
         </is>
       </c>
       <c r="W18" s="2" t="inlineStr">
         <is>
-          <t>52,49%</t>
+          <t>51,54%</t>
         </is>
       </c>
     </row>
@@ -2438,7 +2438,7 @@
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>3812</t>
+          <t>3795</t>
         </is>
       </c>
       <c r="G19" s="2" t="inlineStr">
@@ -2453,7 +2453,7 @@
       </c>
       <c r="I19" s="2" t="inlineStr">
         <is>
-          <t>18,42%</t>
+          <t>18,33%</t>
         </is>
       </c>
       <c r="J19" s="2" t="inlineStr">
@@ -2468,12 +2468,12 @@
       </c>
       <c r="L19" s="2" t="inlineStr">
         <is>
-          <t>695</t>
+          <t>683</t>
         </is>
       </c>
       <c r="M19" s="2" t="inlineStr">
         <is>
-          <t>6469</t>
+          <t>5979</t>
         </is>
       </c>
       <c r="N19" s="2" t="inlineStr">
@@ -2483,12 +2483,12 @@
       </c>
       <c r="O19" s="2" t="inlineStr">
         <is>
-          <t>2,71%</t>
+          <t>2,66%</t>
         </is>
       </c>
       <c r="P19" s="2" t="inlineStr">
         <is>
-          <t>25,17%</t>
+          <t>23,26%</t>
         </is>
       </c>
       <c r="Q19" s="2" t="inlineStr">
@@ -2503,12 +2503,12 @@
       </c>
       <c r="S19" s="2" t="inlineStr">
         <is>
-          <t>1765</t>
+          <t>1381</t>
         </is>
       </c>
       <c r="T19" s="2" t="inlineStr">
         <is>
-          <t>8482</t>
+          <t>7672</t>
         </is>
       </c>
       <c r="U19" s="2" t="inlineStr">
@@ -2518,12 +2518,12 @@
       </c>
       <c r="V19" s="2" t="inlineStr">
         <is>
-          <t>3,8%</t>
+          <t>2,98%</t>
         </is>
       </c>
       <c r="W19" s="2" t="inlineStr">
         <is>
-          <t>18,28%</t>
+          <t>16,54%</t>
         </is>
       </c>
     </row>
@@ -2546,12 +2546,12 @@
       </c>
       <c r="E20" s="2" t="inlineStr">
         <is>
-          <t>2248</t>
+          <t>2044</t>
         </is>
       </c>
       <c r="F20" s="2" t="inlineStr">
         <is>
-          <t>8044</t>
+          <t>7897</t>
         </is>
       </c>
       <c r="G20" s="2" t="inlineStr">
@@ -2561,12 +2561,12 @@
       </c>
       <c r="H20" s="2" t="inlineStr">
         <is>
-          <t>10,86%</t>
+          <t>9,87%</t>
         </is>
       </c>
       <c r="I20" s="2" t="inlineStr">
         <is>
-          <t>38,86%</t>
+          <t>38,15%</t>
         </is>
       </c>
       <c r="J20" s="2" t="inlineStr">
@@ -2581,12 +2581,12 @@
       </c>
       <c r="L20" s="2" t="inlineStr">
         <is>
-          <t>1307</t>
+          <t>1279</t>
         </is>
       </c>
       <c r="M20" s="2" t="inlineStr">
         <is>
-          <t>7386</t>
+          <t>7297</t>
         </is>
       </c>
       <c r="N20" s="2" t="inlineStr">
@@ -2596,12 +2596,12 @@
       </c>
       <c r="O20" s="2" t="inlineStr">
         <is>
-          <t>5,08%</t>
+          <t>4,98%</t>
         </is>
       </c>
       <c r="P20" s="2" t="inlineStr">
         <is>
-          <t>28,74%</t>
+          <t>28,39%</t>
         </is>
       </c>
       <c r="Q20" s="2" t="inlineStr">
@@ -2616,12 +2616,12 @@
       </c>
       <c r="S20" s="2" t="inlineStr">
         <is>
-          <t>4661</t>
+          <t>4457</t>
         </is>
       </c>
       <c r="T20" s="2" t="inlineStr">
         <is>
-          <t>12667</t>
+          <t>12903</t>
         </is>
       </c>
       <c r="U20" s="2" t="inlineStr">
@@ -2631,12 +2631,12 @@
       </c>
       <c r="V20" s="2" t="inlineStr">
         <is>
-          <t>10,05%</t>
+          <t>9,61%</t>
         </is>
       </c>
       <c r="W20" s="2" t="inlineStr">
         <is>
-          <t>27,3%</t>
+          <t>27,81%</t>
         </is>
       </c>
     </row>
@@ -2776,12 +2776,12 @@
       </c>
       <c r="E22" s="2" t="inlineStr">
         <is>
-          <t>1059</t>
+          <t>1311</t>
         </is>
       </c>
       <c r="F22" s="2" t="inlineStr">
         <is>
-          <t>8197</t>
+          <t>8273</t>
         </is>
       </c>
       <c r="G22" s="2" t="inlineStr">
@@ -2791,12 +2791,12 @@
       </c>
       <c r="H22" s="2" t="inlineStr">
         <is>
-          <t>4,87%</t>
+          <t>6,03%</t>
         </is>
       </c>
       <c r="I22" s="2" t="inlineStr">
         <is>
-          <t>37,69%</t>
+          <t>38,03%</t>
         </is>
       </c>
       <c r="J22" s="2" t="inlineStr">
@@ -2811,12 +2811,12 @@
       </c>
       <c r="L22" s="2" t="inlineStr">
         <is>
-          <t>995</t>
+          <t>961</t>
         </is>
       </c>
       <c r="M22" s="2" t="inlineStr">
         <is>
-          <t>8847</t>
+          <t>7798</t>
         </is>
       </c>
       <c r="N22" s="2" t="inlineStr">
@@ -2826,12 +2826,12 @@
       </c>
       <c r="O22" s="2" t="inlineStr">
         <is>
-          <t>6,4%</t>
+          <t>6,18%</t>
         </is>
       </c>
       <c r="P22" s="2" t="inlineStr">
         <is>
-          <t>56,95%</t>
+          <t>50,2%</t>
         </is>
       </c>
       <c r="Q22" s="2" t="inlineStr">
@@ -2846,12 +2846,12 @@
       </c>
       <c r="S22" s="2" t="inlineStr">
         <is>
-          <t>3520</t>
+          <t>3477</t>
         </is>
       </c>
       <c r="T22" s="2" t="inlineStr">
         <is>
-          <t>13195</t>
+          <t>13132</t>
         </is>
       </c>
       <c r="U22" s="2" t="inlineStr">
@@ -2861,12 +2861,12 @@
       </c>
       <c r="V22" s="2" t="inlineStr">
         <is>
-          <t>9,44%</t>
+          <t>9,33%</t>
         </is>
       </c>
       <c r="W22" s="2" t="inlineStr">
         <is>
-          <t>35,39%</t>
+          <t>35,22%</t>
         </is>
       </c>
     </row>
@@ -2889,12 +2889,12 @@
       </c>
       <c r="E23" s="2" t="inlineStr">
         <is>
-          <t>1383</t>
+          <t>1654</t>
         </is>
       </c>
       <c r="F23" s="2" t="inlineStr">
         <is>
-          <t>8160</t>
+          <t>8818</t>
         </is>
       </c>
       <c r="G23" s="2" t="inlineStr">
@@ -2904,12 +2904,12 @@
       </c>
       <c r="H23" s="2" t="inlineStr">
         <is>
-          <t>6,36%</t>
+          <t>7,61%</t>
         </is>
       </c>
       <c r="I23" s="2" t="inlineStr">
         <is>
-          <t>37,52%</t>
+          <t>40,54%</t>
         </is>
       </c>
       <c r="J23" s="2" t="inlineStr">
@@ -2924,12 +2924,12 @@
       </c>
       <c r="L23" s="2" t="inlineStr">
         <is>
-          <t>1033</t>
+          <t>989</t>
         </is>
       </c>
       <c r="M23" s="2" t="inlineStr">
         <is>
-          <t>8893</t>
+          <t>9039</t>
         </is>
       </c>
       <c r="N23" s="2" t="inlineStr">
@@ -2939,12 +2939,12 @@
       </c>
       <c r="O23" s="2" t="inlineStr">
         <is>
-          <t>6,65%</t>
+          <t>6,37%</t>
         </is>
       </c>
       <c r="P23" s="2" t="inlineStr">
         <is>
-          <t>57,25%</t>
+          <t>58,19%</t>
         </is>
       </c>
       <c r="Q23" s="2" t="inlineStr">
@@ -2959,12 +2959,12 @@
       </c>
       <c r="S23" s="2" t="inlineStr">
         <is>
-          <t>3755</t>
+          <t>3636</t>
         </is>
       </c>
       <c r="T23" s="2" t="inlineStr">
         <is>
-          <t>13481</t>
+          <t>13589</t>
         </is>
       </c>
       <c r="U23" s="2" t="inlineStr">
@@ -2974,12 +2974,12 @@
       </c>
       <c r="V23" s="2" t="inlineStr">
         <is>
-          <t>10,07%</t>
+          <t>9,75%</t>
         </is>
       </c>
       <c r="W23" s="2" t="inlineStr">
         <is>
-          <t>36,16%</t>
+          <t>36,45%</t>
         </is>
       </c>
     </row>
@@ -3002,12 +3002,12 @@
       </c>
       <c r="E24" s="2" t="inlineStr">
         <is>
-          <t>3846</t>
+          <t>3739</t>
         </is>
       </c>
       <c r="F24" s="2" t="inlineStr">
         <is>
-          <t>10923</t>
+          <t>10924</t>
         </is>
       </c>
       <c r="G24" s="2" t="inlineStr">
@@ -3017,12 +3017,12 @@
       </c>
       <c r="H24" s="2" t="inlineStr">
         <is>
-          <t>17,68%</t>
+          <t>17,19%</t>
         </is>
       </c>
       <c r="I24" s="2" t="inlineStr">
         <is>
-          <t>50,22%</t>
+          <t>50,23%</t>
         </is>
       </c>
       <c r="J24" s="2" t="inlineStr">
@@ -3037,12 +3037,12 @@
       </c>
       <c r="L24" s="2" t="inlineStr">
         <is>
-          <t>1049</t>
+          <t>1171</t>
         </is>
       </c>
       <c r="M24" s="2" t="inlineStr">
         <is>
-          <t>8601</t>
+          <t>8667</t>
         </is>
       </c>
       <c r="N24" s="2" t="inlineStr">
@@ -3052,12 +3052,12 @@
       </c>
       <c r="O24" s="2" t="inlineStr">
         <is>
-          <t>6,75%</t>
+          <t>7,54%</t>
         </is>
       </c>
       <c r="P24" s="2" t="inlineStr">
         <is>
-          <t>55,37%</t>
+          <t>55,79%</t>
         </is>
       </c>
       <c r="Q24" s="2" t="inlineStr">
@@ -3072,12 +3072,12 @@
       </c>
       <c r="S24" s="2" t="inlineStr">
         <is>
-          <t>6711</t>
+          <t>6504</t>
         </is>
       </c>
       <c r="T24" s="2" t="inlineStr">
         <is>
-          <t>17333</t>
+          <t>16531</t>
         </is>
       </c>
       <c r="U24" s="2" t="inlineStr">
@@ -3087,12 +3087,12 @@
       </c>
       <c r="V24" s="2" t="inlineStr">
         <is>
-          <t>18,0%</t>
+          <t>17,44%</t>
         </is>
       </c>
       <c r="W24" s="2" t="inlineStr">
         <is>
-          <t>46,49%</t>
+          <t>44,34%</t>
         </is>
       </c>
     </row>
@@ -3120,7 +3120,7 @@
       </c>
       <c r="F25" s="2" t="inlineStr">
         <is>
-          <t>4943</t>
+          <t>4433</t>
         </is>
       </c>
       <c r="G25" s="2" t="inlineStr">
@@ -3135,7 +3135,7 @@
       </c>
       <c r="I25" s="2" t="inlineStr">
         <is>
-          <t>22,73%</t>
+          <t>20,38%</t>
         </is>
       </c>
       <c r="J25" s="2" t="inlineStr">
@@ -3155,7 +3155,7 @@
       </c>
       <c r="M25" s="2" t="inlineStr">
         <is>
-          <t>7235</t>
+          <t>7327</t>
         </is>
       </c>
       <c r="N25" s="2" t="inlineStr">
@@ -3170,7 +3170,7 @@
       </c>
       <c r="P25" s="2" t="inlineStr">
         <is>
-          <t>46,57%</t>
+          <t>47,17%</t>
         </is>
       </c>
       <c r="Q25" s="2" t="inlineStr">
@@ -3185,12 +3185,12 @@
       </c>
       <c r="S25" s="2" t="inlineStr">
         <is>
-          <t>978</t>
+          <t>999</t>
         </is>
       </c>
       <c r="T25" s="2" t="inlineStr">
         <is>
-          <t>9449</t>
+          <t>9285</t>
         </is>
       </c>
       <c r="U25" s="2" t="inlineStr">
@@ -3200,12 +3200,12 @@
       </c>
       <c r="V25" s="2" t="inlineStr">
         <is>
-          <t>2,62%</t>
+          <t>2,68%</t>
         </is>
       </c>
       <c r="W25" s="2" t="inlineStr">
         <is>
-          <t>25,34%</t>
+          <t>24,9%</t>
         </is>
       </c>
     </row>
@@ -3228,12 +3228,12 @@
       </c>
       <c r="E26" s="2" t="inlineStr">
         <is>
-          <t>2593</t>
+          <t>2856</t>
         </is>
       </c>
       <c r="F26" s="2" t="inlineStr">
         <is>
-          <t>10121</t>
+          <t>10587</t>
         </is>
       </c>
       <c r="G26" s="2" t="inlineStr">
@@ -3243,12 +3243,12 @@
       </c>
       <c r="H26" s="2" t="inlineStr">
         <is>
-          <t>11,92%</t>
+          <t>13,13%</t>
         </is>
       </c>
       <c r="I26" s="2" t="inlineStr">
         <is>
-          <t>46,53%</t>
+          <t>48,67%</t>
         </is>
       </c>
       <c r="J26" s="2" t="inlineStr">
@@ -3268,7 +3268,7 @@
       </c>
       <c r="M26" s="2" t="inlineStr">
         <is>
-          <t>5698</t>
+          <t>5972</t>
         </is>
       </c>
       <c r="N26" s="2" t="inlineStr">
@@ -3283,7 +3283,7 @@
       </c>
       <c r="P26" s="2" t="inlineStr">
         <is>
-          <t>36,68%</t>
+          <t>38,44%</t>
         </is>
       </c>
       <c r="Q26" s="2" t="inlineStr">
@@ -3298,12 +3298,12 @@
       </c>
       <c r="S26" s="2" t="inlineStr">
         <is>
-          <t>4353</t>
+          <t>4388</t>
         </is>
       </c>
       <c r="T26" s="2" t="inlineStr">
         <is>
-          <t>13565</t>
+          <t>13634</t>
         </is>
       </c>
       <c r="U26" s="2" t="inlineStr">
@@ -3313,12 +3313,12 @@
       </c>
       <c r="V26" s="2" t="inlineStr">
         <is>
-          <t>11,67%</t>
+          <t>11,77%</t>
         </is>
       </c>
       <c r="W26" s="2" t="inlineStr">
         <is>
-          <t>36,38%</t>
+          <t>36,57%</t>
         </is>
       </c>
     </row>
@@ -3576,7 +3576,7 @@
       </c>
       <c r="F29" s="2" t="inlineStr">
         <is>
-          <t>2483</t>
+          <t>2900</t>
         </is>
       </c>
       <c r="G29" s="2" t="inlineStr">
@@ -3591,7 +3591,7 @@
       </c>
       <c r="I29" s="2" t="inlineStr">
         <is>
-          <t>28,75%</t>
+          <t>33,58%</t>
         </is>
       </c>
       <c r="J29" s="2" t="inlineStr">
@@ -3606,12 +3606,12 @@
       </c>
       <c r="L29" s="2" t="inlineStr">
         <is>
-          <t>1221</t>
+          <t>1153</t>
         </is>
       </c>
       <c r="M29" s="2" t="inlineStr">
         <is>
-          <t>5788</t>
+          <t>5812</t>
         </is>
       </c>
       <c r="N29" s="2" t="inlineStr">
@@ -3621,12 +3621,12 @@
       </c>
       <c r="O29" s="2" t="inlineStr">
         <is>
-          <t>9,41%</t>
+          <t>8,88%</t>
         </is>
       </c>
       <c r="P29" s="2" t="inlineStr">
         <is>
-          <t>44,59%</t>
+          <t>44,78%</t>
         </is>
       </c>
       <c r="Q29" s="2" t="inlineStr">
@@ -3641,12 +3641,12 @@
       </c>
       <c r="S29" s="2" t="inlineStr">
         <is>
-          <t>1600</t>
+          <t>1553</t>
         </is>
       </c>
       <c r="T29" s="2" t="inlineStr">
         <is>
-          <t>6770</t>
+          <t>6661</t>
         </is>
       </c>
       <c r="U29" s="2" t="inlineStr">
@@ -3656,12 +3656,12 @@
       </c>
       <c r="V29" s="2" t="inlineStr">
         <is>
-          <t>7,4%</t>
+          <t>7,18%</t>
         </is>
       </c>
       <c r="W29" s="2" t="inlineStr">
         <is>
-          <t>31,32%</t>
+          <t>30,81%</t>
         </is>
       </c>
     </row>
@@ -3684,7 +3684,7 @@
       </c>
       <c r="E30" s="2" t="inlineStr">
         <is>
-          <t>6155</t>
+          <t>5738</t>
         </is>
       </c>
       <c r="F30" s="2" t="inlineStr">
@@ -3699,7 +3699,7 @@
       </c>
       <c r="H30" s="2" t="inlineStr">
         <is>
-          <t>71,25%</t>
+          <t>66,42%</t>
         </is>
       </c>
       <c r="I30" s="2" t="inlineStr">
@@ -3719,12 +3719,12 @@
       </c>
       <c r="L30" s="2" t="inlineStr">
         <is>
-          <t>7191</t>
+          <t>7167</t>
         </is>
       </c>
       <c r="M30" s="2" t="inlineStr">
         <is>
-          <t>11758</t>
+          <t>11826</t>
         </is>
       </c>
       <c r="N30" s="2" t="inlineStr">
@@ -3734,12 +3734,12 @@
       </c>
       <c r="O30" s="2" t="inlineStr">
         <is>
-          <t>55,41%</t>
+          <t>55,22%</t>
         </is>
       </c>
       <c r="P30" s="2" t="inlineStr">
         <is>
-          <t>90,59%</t>
+          <t>91,12%</t>
         </is>
       </c>
       <c r="Q30" s="2" t="inlineStr">
@@ -3754,12 +3754,12 @@
       </c>
       <c r="S30" s="2" t="inlineStr">
         <is>
-          <t>14848</t>
+          <t>14957</t>
         </is>
       </c>
       <c r="T30" s="2" t="inlineStr">
         <is>
-          <t>20018</t>
+          <t>20065</t>
         </is>
       </c>
       <c r="U30" s="2" t="inlineStr">
@@ -3769,12 +3769,12 @@
       </c>
       <c r="V30" s="2" t="inlineStr">
         <is>
-          <t>68,68%</t>
+          <t>69,19%</t>
         </is>
       </c>
       <c r="W30" s="2" t="inlineStr">
         <is>
-          <t>92,6%</t>
+          <t>92,82%</t>
         </is>
       </c>
     </row>
@@ -4145,7 +4145,7 @@
       </c>
       <c r="F34" s="2" t="inlineStr">
         <is>
-          <t>2694</t>
+          <t>2702</t>
         </is>
       </c>
       <c r="G34" s="2" t="inlineStr">
@@ -4160,7 +4160,7 @@
       </c>
       <c r="I34" s="2" t="inlineStr">
         <is>
-          <t>15,04%</t>
+          <t>15,09%</t>
         </is>
       </c>
       <c r="J34" s="2" t="inlineStr">
@@ -4215,7 +4215,7 @@
       </c>
       <c r="T34" s="2" t="inlineStr">
         <is>
-          <t>2360</t>
+          <t>2380</t>
         </is>
       </c>
       <c r="U34" s="2" t="inlineStr">
@@ -4230,7 +4230,7 @@
       </c>
       <c r="W34" s="2" t="inlineStr">
         <is>
-          <t>5,61%</t>
+          <t>5,65%</t>
         </is>
       </c>
     </row>
@@ -4253,12 +4253,12 @@
       </c>
       <c r="E35" s="2" t="inlineStr">
         <is>
-          <t>1366</t>
+          <t>1494</t>
         </is>
       </c>
       <c r="F35" s="2" t="inlineStr">
         <is>
-          <t>6371</t>
+          <t>6800</t>
         </is>
       </c>
       <c r="G35" s="2" t="inlineStr">
@@ -4268,12 +4268,12 @@
       </c>
       <c r="H35" s="2" t="inlineStr">
         <is>
-          <t>7,63%</t>
+          <t>8,34%</t>
         </is>
       </c>
       <c r="I35" s="2" t="inlineStr">
         <is>
-          <t>35,58%</t>
+          <t>37,97%</t>
         </is>
       </c>
       <c r="J35" s="2" t="inlineStr">
@@ -4288,12 +4288,12 @@
       </c>
       <c r="L35" s="2" t="inlineStr">
         <is>
-          <t>2603</t>
+          <t>2253</t>
         </is>
       </c>
       <c r="M35" s="2" t="inlineStr">
         <is>
-          <t>8828</t>
+          <t>9166</t>
         </is>
       </c>
       <c r="N35" s="2" t="inlineStr">
@@ -4303,12 +4303,12 @@
       </c>
       <c r="O35" s="2" t="inlineStr">
         <is>
-          <t>10,76%</t>
+          <t>9,31%</t>
         </is>
       </c>
       <c r="P35" s="2" t="inlineStr">
         <is>
-          <t>36,5%</t>
+          <t>37,9%</t>
         </is>
       </c>
       <c r="Q35" s="2" t="inlineStr">
@@ -4323,12 +4323,12 @@
       </c>
       <c r="S35" s="2" t="inlineStr">
         <is>
-          <t>5152</t>
+          <t>5360</t>
         </is>
       </c>
       <c r="T35" s="2" t="inlineStr">
         <is>
-          <t>13561</t>
+          <t>13862</t>
         </is>
       </c>
       <c r="U35" s="2" t="inlineStr">
@@ -4338,12 +4338,12 @@
       </c>
       <c r="V35" s="2" t="inlineStr">
         <is>
-          <t>12,24%</t>
+          <t>12,73%</t>
         </is>
       </c>
       <c r="W35" s="2" t="inlineStr">
         <is>
-          <t>32,22%</t>
+          <t>32,93%</t>
         </is>
       </c>
     </row>
@@ -4366,12 +4366,12 @@
       </c>
       <c r="E36" s="2" t="inlineStr">
         <is>
-          <t>7875</t>
+          <t>8390</t>
         </is>
       </c>
       <c r="F36" s="2" t="inlineStr">
         <is>
-          <t>14109</t>
+          <t>14314</t>
         </is>
       </c>
       <c r="G36" s="2" t="inlineStr">
@@ -4381,12 +4381,12 @@
       </c>
       <c r="H36" s="2" t="inlineStr">
         <is>
-          <t>43,98%</t>
+          <t>46,85%</t>
         </is>
       </c>
       <c r="I36" s="2" t="inlineStr">
         <is>
-          <t>78,79%</t>
+          <t>79,93%</t>
         </is>
       </c>
       <c r="J36" s="2" t="inlineStr">
@@ -4401,12 +4401,12 @@
       </c>
       <c r="L36" s="2" t="inlineStr">
         <is>
-          <t>12182</t>
+          <t>12434</t>
         </is>
       </c>
       <c r="M36" s="2" t="inlineStr">
         <is>
-          <t>20015</t>
+          <t>20064</t>
         </is>
       </c>
       <c r="N36" s="2" t="inlineStr">
@@ -4416,12 +4416,12 @@
       </c>
       <c r="O36" s="2" t="inlineStr">
         <is>
-          <t>50,37%</t>
+          <t>51,42%</t>
         </is>
       </c>
       <c r="P36" s="2" t="inlineStr">
         <is>
-          <t>82,76%</t>
+          <t>82,96%</t>
         </is>
       </c>
       <c r="Q36" s="2" t="inlineStr">
@@ -4436,12 +4436,12 @@
       </c>
       <c r="S36" s="2" t="inlineStr">
         <is>
-          <t>22897</t>
+          <t>22660</t>
         </is>
       </c>
       <c r="T36" s="2" t="inlineStr">
         <is>
-          <t>32708</t>
+          <t>32824</t>
         </is>
       </c>
       <c r="U36" s="2" t="inlineStr">
@@ -4451,12 +4451,12 @@
       </c>
       <c r="V36" s="2" t="inlineStr">
         <is>
-          <t>54,4%</t>
+          <t>53,83%</t>
         </is>
       </c>
       <c r="W36" s="2" t="inlineStr">
         <is>
-          <t>77,71%</t>
+          <t>77,98%</t>
         </is>
       </c>
     </row>
@@ -4519,7 +4519,7 @@
       </c>
       <c r="M37" s="2" t="inlineStr">
         <is>
-          <t>4765</t>
+          <t>4600</t>
         </is>
       </c>
       <c r="N37" s="2" t="inlineStr">
@@ -4534,7 +4534,7 @@
       </c>
       <c r="P37" s="2" t="inlineStr">
         <is>
-          <t>19,7%</t>
+          <t>19,02%</t>
         </is>
       </c>
       <c r="Q37" s="2" t="inlineStr">
@@ -4554,7 +4554,7 @@
       </c>
       <c r="T37" s="2" t="inlineStr">
         <is>
-          <t>5115</t>
+          <t>5279</t>
         </is>
       </c>
       <c r="U37" s="2" t="inlineStr">
@@ -4569,7 +4569,7 @@
       </c>
       <c r="W37" s="2" t="inlineStr">
         <is>
-          <t>12,15%</t>
+          <t>12,54%</t>
         </is>
       </c>
     </row>
@@ -4592,12 +4592,12 @@
       </c>
       <c r="E38" s="2" t="inlineStr">
         <is>
-          <t>958</t>
+          <t>979</t>
         </is>
       </c>
       <c r="F38" s="2" t="inlineStr">
         <is>
-          <t>5761</t>
+          <t>5594</t>
         </is>
       </c>
       <c r="G38" s="2" t="inlineStr">
@@ -4607,12 +4607,12 @@
       </c>
       <c r="H38" s="2" t="inlineStr">
         <is>
-          <t>5,35%</t>
+          <t>5,47%</t>
         </is>
       </c>
       <c r="I38" s="2" t="inlineStr">
         <is>
-          <t>32,17%</t>
+          <t>31,24%</t>
         </is>
       </c>
       <c r="J38" s="2" t="inlineStr">
@@ -4627,12 +4627,12 @@
       </c>
       <c r="L38" s="2" t="inlineStr">
         <is>
-          <t>335</t>
+          <t>339</t>
         </is>
       </c>
       <c r="M38" s="2" t="inlineStr">
         <is>
-          <t>4146</t>
+          <t>3972</t>
         </is>
       </c>
       <c r="N38" s="2" t="inlineStr">
@@ -4642,12 +4642,12 @@
       </c>
       <c r="O38" s="2" t="inlineStr">
         <is>
-          <t>1,39%</t>
+          <t>1,4%</t>
         </is>
       </c>
       <c r="P38" s="2" t="inlineStr">
         <is>
-          <t>17,14%</t>
+          <t>16,42%</t>
         </is>
       </c>
       <c r="Q38" s="2" t="inlineStr">
@@ -4662,12 +4662,12 @@
       </c>
       <c r="S38" s="2" t="inlineStr">
         <is>
-          <t>1731</t>
+          <t>1833</t>
         </is>
       </c>
       <c r="T38" s="2" t="inlineStr">
         <is>
-          <t>7381</t>
+          <t>7442</t>
         </is>
       </c>
       <c r="U38" s="2" t="inlineStr">
@@ -4677,12 +4677,12 @@
       </c>
       <c r="V38" s="2" t="inlineStr">
         <is>
-          <t>4,11%</t>
+          <t>4,35%</t>
         </is>
       </c>
       <c r="W38" s="2" t="inlineStr">
         <is>
-          <t>17,54%</t>
+          <t>17,68%</t>
         </is>
       </c>
     </row>
@@ -4822,12 +4822,12 @@
       </c>
       <c r="E40" s="2" t="inlineStr">
         <is>
-          <t>557</t>
+          <t>555</t>
         </is>
       </c>
       <c r="F40" s="2" t="inlineStr">
         <is>
-          <t>5785</t>
+          <t>5463</t>
         </is>
       </c>
       <c r="G40" s="2" t="inlineStr">
@@ -4837,12 +4837,12 @@
       </c>
       <c r="H40" s="2" t="inlineStr">
         <is>
-          <t>1,54%</t>
+          <t>1,53%</t>
         </is>
       </c>
       <c r="I40" s="2" t="inlineStr">
         <is>
-          <t>15,99%</t>
+          <t>15,1%</t>
         </is>
       </c>
       <c r="J40" s="2" t="inlineStr">
@@ -4857,12 +4857,12 @@
       </c>
       <c r="L40" s="2" t="inlineStr">
         <is>
-          <t>1595</t>
+          <t>1655</t>
         </is>
       </c>
       <c r="M40" s="2" t="inlineStr">
         <is>
-          <t>10593</t>
+          <t>10192</t>
         </is>
       </c>
       <c r="N40" s="2" t="inlineStr">
@@ -4872,12 +4872,12 @@
       </c>
       <c r="O40" s="2" t="inlineStr">
         <is>
-          <t>3,74%</t>
+          <t>3,88%</t>
         </is>
       </c>
       <c r="P40" s="2" t="inlineStr">
         <is>
-          <t>24,85%</t>
+          <t>23,91%</t>
         </is>
       </c>
       <c r="Q40" s="2" t="inlineStr">
@@ -4892,12 +4892,12 @@
       </c>
       <c r="S40" s="2" t="inlineStr">
         <is>
-          <t>2928</t>
+          <t>3047</t>
         </is>
       </c>
       <c r="T40" s="2" t="inlineStr">
         <is>
-          <t>12516</t>
+          <t>12472</t>
         </is>
       </c>
       <c r="U40" s="2" t="inlineStr">
@@ -4907,12 +4907,12 @@
       </c>
       <c r="V40" s="2" t="inlineStr">
         <is>
-          <t>3,72%</t>
+          <t>3,87%</t>
         </is>
       </c>
       <c r="W40" s="2" t="inlineStr">
         <is>
-          <t>15,88%</t>
+          <t>15,83%</t>
         </is>
       </c>
     </row>
@@ -4935,12 +4935,12 @@
       </c>
       <c r="E41" s="2" t="inlineStr">
         <is>
-          <t>4591</t>
+          <t>4702</t>
         </is>
       </c>
       <c r="F41" s="2" t="inlineStr">
         <is>
-          <t>15419</t>
+          <t>14902</t>
         </is>
       </c>
       <c r="G41" s="2" t="inlineStr">
@@ -4950,12 +4950,12 @@
       </c>
       <c r="H41" s="2" t="inlineStr">
         <is>
-          <t>12,69%</t>
+          <t>13,0%</t>
         </is>
       </c>
       <c r="I41" s="2" t="inlineStr">
         <is>
-          <t>42,62%</t>
+          <t>41,19%</t>
         </is>
       </c>
       <c r="J41" s="2" t="inlineStr">
@@ -4970,12 +4970,12 @@
       </c>
       <c r="L41" s="2" t="inlineStr">
         <is>
-          <t>4258</t>
+          <t>4709</t>
         </is>
       </c>
       <c r="M41" s="2" t="inlineStr">
         <is>
-          <t>14014</t>
+          <t>15185</t>
         </is>
       </c>
       <c r="N41" s="2" t="inlineStr">
@@ -4985,12 +4985,12 @@
       </c>
       <c r="O41" s="2" t="inlineStr">
         <is>
-          <t>9,99%</t>
+          <t>11,05%</t>
         </is>
       </c>
       <c r="P41" s="2" t="inlineStr">
         <is>
-          <t>32,88%</t>
+          <t>35,63%</t>
         </is>
       </c>
       <c r="Q41" s="2" t="inlineStr">
@@ -5005,12 +5005,12 @@
       </c>
       <c r="S41" s="2" t="inlineStr">
         <is>
-          <t>11566</t>
+          <t>10940</t>
         </is>
       </c>
       <c r="T41" s="2" t="inlineStr">
         <is>
-          <t>25432</t>
+          <t>25642</t>
         </is>
       </c>
       <c r="U41" s="2" t="inlineStr">
@@ -5020,12 +5020,12 @@
       </c>
       <c r="V41" s="2" t="inlineStr">
         <is>
-          <t>14,68%</t>
+          <t>13,88%</t>
         </is>
       </c>
       <c r="W41" s="2" t="inlineStr">
         <is>
-          <t>32,27%</t>
+          <t>32,54%</t>
         </is>
       </c>
     </row>
@@ -5048,12 +5048,12 @@
       </c>
       <c r="E42" s="2" t="inlineStr">
         <is>
-          <t>10541</t>
+          <t>10660</t>
         </is>
       </c>
       <c r="F42" s="2" t="inlineStr">
         <is>
-          <t>20988</t>
+          <t>20611</t>
         </is>
       </c>
       <c r="G42" s="2" t="inlineStr">
@@ -5063,12 +5063,12 @@
       </c>
       <c r="H42" s="2" t="inlineStr">
         <is>
-          <t>29,13%</t>
+          <t>29,46%</t>
         </is>
       </c>
       <c r="I42" s="2" t="inlineStr">
         <is>
-          <t>58,01%</t>
+          <t>56,96%</t>
         </is>
       </c>
       <c r="J42" s="2" t="inlineStr">
@@ -5083,12 +5083,12 @@
       </c>
       <c r="L42" s="2" t="inlineStr">
         <is>
-          <t>15527</t>
+          <t>14153</t>
         </is>
       </c>
       <c r="M42" s="2" t="inlineStr">
         <is>
-          <t>27299</t>
+          <t>26020</t>
         </is>
       </c>
       <c r="N42" s="2" t="inlineStr">
@@ -5098,12 +5098,12 @@
       </c>
       <c r="O42" s="2" t="inlineStr">
         <is>
-          <t>36,43%</t>
+          <t>33,2%</t>
         </is>
       </c>
       <c r="P42" s="2" t="inlineStr">
         <is>
-          <t>64,04%</t>
+          <t>61,04%</t>
         </is>
       </c>
       <c r="Q42" s="2" t="inlineStr">
@@ -5118,12 +5118,12 @@
       </c>
       <c r="S42" s="2" t="inlineStr">
         <is>
-          <t>29459</t>
+          <t>28076</t>
         </is>
       </c>
       <c r="T42" s="2" t="inlineStr">
         <is>
-          <t>45081</t>
+          <t>44737</t>
         </is>
       </c>
       <c r="U42" s="2" t="inlineStr">
@@ -5133,12 +5133,12 @@
       </c>
       <c r="V42" s="2" t="inlineStr">
         <is>
-          <t>37,38%</t>
+          <t>35,63%</t>
         </is>
       </c>
       <c r="W42" s="2" t="inlineStr">
         <is>
-          <t>57,2%</t>
+          <t>56,77%</t>
         </is>
       </c>
     </row>
@@ -5161,12 +5161,12 @@
       </c>
       <c r="E43" s="2" t="inlineStr">
         <is>
-          <t>2751</t>
+          <t>2743</t>
         </is>
       </c>
       <c r="F43" s="2" t="inlineStr">
         <is>
-          <t>10714</t>
+          <t>10826</t>
         </is>
       </c>
       <c r="G43" s="2" t="inlineStr">
@@ -5176,12 +5176,12 @@
       </c>
       <c r="H43" s="2" t="inlineStr">
         <is>
-          <t>7,6%</t>
+          <t>7,58%</t>
         </is>
       </c>
       <c r="I43" s="2" t="inlineStr">
         <is>
-          <t>29,61%</t>
+          <t>29,92%</t>
         </is>
       </c>
       <c r="J43" s="2" t="inlineStr">
@@ -5196,12 +5196,12 @@
       </c>
       <c r="L43" s="2" t="inlineStr">
         <is>
-          <t>1757</t>
+          <t>1815</t>
         </is>
       </c>
       <c r="M43" s="2" t="inlineStr">
         <is>
-          <t>9675</t>
+          <t>10014</t>
         </is>
       </c>
       <c r="N43" s="2" t="inlineStr">
@@ -5211,12 +5211,12 @@
       </c>
       <c r="O43" s="2" t="inlineStr">
         <is>
-          <t>4,12%</t>
+          <t>4,26%</t>
         </is>
       </c>
       <c r="P43" s="2" t="inlineStr">
         <is>
-          <t>22,7%</t>
+          <t>23,49%</t>
         </is>
       </c>
       <c r="Q43" s="2" t="inlineStr">
@@ -5231,12 +5231,12 @@
       </c>
       <c r="S43" s="2" t="inlineStr">
         <is>
-          <t>6678</t>
+          <t>6137</t>
         </is>
       </c>
       <c r="T43" s="2" t="inlineStr">
         <is>
-          <t>16581</t>
+          <t>16745</t>
         </is>
       </c>
       <c r="U43" s="2" t="inlineStr">
@@ -5246,12 +5246,12 @@
       </c>
       <c r="V43" s="2" t="inlineStr">
         <is>
-          <t>8,47%</t>
+          <t>7,79%</t>
         </is>
       </c>
       <c r="W43" s="2" t="inlineStr">
         <is>
-          <t>21,04%</t>
+          <t>21,25%</t>
         </is>
       </c>
     </row>
@@ -5274,12 +5274,12 @@
       </c>
       <c r="E44" s="2" t="inlineStr">
         <is>
-          <t>829</t>
+          <t>1445</t>
         </is>
       </c>
       <c r="F44" s="2" t="inlineStr">
         <is>
-          <t>8470</t>
+          <t>8882</t>
         </is>
       </c>
       <c r="G44" s="2" t="inlineStr">
@@ -5289,12 +5289,12 @@
       </c>
       <c r="H44" s="2" t="inlineStr">
         <is>
-          <t>2,29%</t>
+          <t>3,99%</t>
         </is>
       </c>
       <c r="I44" s="2" t="inlineStr">
         <is>
-          <t>23,41%</t>
+          <t>24,55%</t>
         </is>
       </c>
       <c r="J44" s="2" t="inlineStr">
@@ -5309,12 +5309,12 @@
       </c>
       <c r="L44" s="2" t="inlineStr">
         <is>
-          <t>943</t>
+          <t>992</t>
         </is>
       </c>
       <c r="M44" s="2" t="inlineStr">
         <is>
-          <t>8634</t>
+          <t>9296</t>
         </is>
       </c>
       <c r="N44" s="2" t="inlineStr">
@@ -5324,12 +5324,12 @@
       </c>
       <c r="O44" s="2" t="inlineStr">
         <is>
-          <t>2,21%</t>
+          <t>2,33%</t>
         </is>
       </c>
       <c r="P44" s="2" t="inlineStr">
         <is>
-          <t>20,26%</t>
+          <t>21,81%</t>
         </is>
       </c>
       <c r="Q44" s="2" t="inlineStr">
@@ -5344,12 +5344,12 @@
       </c>
       <c r="S44" s="2" t="inlineStr">
         <is>
-          <t>3744</t>
+          <t>3653</t>
         </is>
       </c>
       <c r="T44" s="2" t="inlineStr">
         <is>
-          <t>14797</t>
+          <t>13488</t>
         </is>
       </c>
       <c r="U44" s="2" t="inlineStr">
@@ -5359,12 +5359,12 @@
       </c>
       <c r="V44" s="2" t="inlineStr">
         <is>
-          <t>4,75%</t>
+          <t>4,64%</t>
         </is>
       </c>
       <c r="W44" s="2" t="inlineStr">
         <is>
-          <t>18,78%</t>
+          <t>17,12%</t>
         </is>
       </c>
     </row>
@@ -5544,7 +5544,7 @@
       </c>
       <c r="M46" s="2" t="inlineStr">
         <is>
-          <t>3260</t>
+          <t>3065</t>
         </is>
       </c>
       <c r="N46" s="2" t="inlineStr">
@@ -5559,7 +5559,7 @@
       </c>
       <c r="P46" s="2" t="inlineStr">
         <is>
-          <t>4,05%</t>
+          <t>3,81%</t>
         </is>
       </c>
       <c r="Q46" s="2" t="inlineStr">
@@ -5579,7 +5579,7 @@
       </c>
       <c r="T46" s="2" t="inlineStr">
         <is>
-          <t>3353</t>
+          <t>2714</t>
         </is>
       </c>
       <c r="U46" s="2" t="inlineStr">
@@ -5594,7 +5594,7 @@
       </c>
       <c r="W46" s="2" t="inlineStr">
         <is>
-          <t>2,56%</t>
+          <t>2,08%</t>
         </is>
       </c>
     </row>
@@ -5617,12 +5617,12 @@
       </c>
       <c r="E47" s="2" t="inlineStr">
         <is>
-          <t>1805</t>
+          <t>1744</t>
         </is>
       </c>
       <c r="F47" s="2" t="inlineStr">
         <is>
-          <t>7654</t>
+          <t>7364</t>
         </is>
       </c>
       <c r="G47" s="2" t="inlineStr">
@@ -5632,12 +5632,12 @@
       </c>
       <c r="H47" s="2" t="inlineStr">
         <is>
-          <t>3,58%</t>
+          <t>3,46%</t>
         </is>
       </c>
       <c r="I47" s="2" t="inlineStr">
         <is>
-          <t>15,2%</t>
+          <t>14,62%</t>
         </is>
       </c>
       <c r="J47" s="2" t="inlineStr">
@@ -5652,12 +5652,12 @@
       </c>
       <c r="L47" s="2" t="inlineStr">
         <is>
-          <t>4066</t>
+          <t>3800</t>
         </is>
       </c>
       <c r="M47" s="2" t="inlineStr">
         <is>
-          <t>15521</t>
+          <t>13933</t>
         </is>
       </c>
       <c r="N47" s="2" t="inlineStr">
@@ -5667,12 +5667,12 @@
       </c>
       <c r="O47" s="2" t="inlineStr">
         <is>
-          <t>5,06%</t>
+          <t>4,73%</t>
         </is>
       </c>
       <c r="P47" s="2" t="inlineStr">
         <is>
-          <t>19,3%</t>
+          <t>17,33%</t>
         </is>
       </c>
       <c r="Q47" s="2" t="inlineStr">
@@ -5687,12 +5687,12 @@
       </c>
       <c r="S47" s="2" t="inlineStr">
         <is>
-          <t>7158</t>
+          <t>7065</t>
         </is>
       </c>
       <c r="T47" s="2" t="inlineStr">
         <is>
-          <t>19550</t>
+          <t>19067</t>
         </is>
       </c>
       <c r="U47" s="2" t="inlineStr">
@@ -5702,12 +5702,12 @@
       </c>
       <c r="V47" s="2" t="inlineStr">
         <is>
-          <t>5,47%</t>
+          <t>5,4%</t>
         </is>
       </c>
       <c r="W47" s="2" t="inlineStr">
         <is>
-          <t>14,95%</t>
+          <t>14,58%</t>
         </is>
       </c>
     </row>
@@ -5730,12 +5730,12 @@
       </c>
       <c r="E48" s="2" t="inlineStr">
         <is>
-          <t>10307</t>
+          <t>10538</t>
         </is>
       </c>
       <c r="F48" s="2" t="inlineStr">
         <is>
-          <t>20941</t>
+          <t>21176</t>
         </is>
       </c>
       <c r="G48" s="2" t="inlineStr">
@@ -5745,12 +5745,12 @@
       </c>
       <c r="H48" s="2" t="inlineStr">
         <is>
-          <t>20,47%</t>
+          <t>20,93%</t>
         </is>
       </c>
       <c r="I48" s="2" t="inlineStr">
         <is>
-          <t>41,58%</t>
+          <t>42,05%</t>
         </is>
       </c>
       <c r="J48" s="2" t="inlineStr">
@@ -5765,12 +5765,12 @@
       </c>
       <c r="L48" s="2" t="inlineStr">
         <is>
-          <t>16861</t>
+          <t>17167</t>
         </is>
       </c>
       <c r="M48" s="2" t="inlineStr">
         <is>
-          <t>31966</t>
+          <t>32047</t>
         </is>
       </c>
       <c r="N48" s="2" t="inlineStr">
@@ -5780,12 +5780,12 @@
       </c>
       <c r="O48" s="2" t="inlineStr">
         <is>
-          <t>20,97%</t>
+          <t>21,35%</t>
         </is>
       </c>
       <c r="P48" s="2" t="inlineStr">
         <is>
-          <t>39,75%</t>
+          <t>39,85%</t>
         </is>
       </c>
       <c r="Q48" s="2" t="inlineStr">
@@ -5800,12 +5800,12 @@
       </c>
       <c r="S48" s="2" t="inlineStr">
         <is>
-          <t>29270</t>
+          <t>29182</t>
         </is>
       </c>
       <c r="T48" s="2" t="inlineStr">
         <is>
-          <t>48216</t>
+          <t>48272</t>
         </is>
       </c>
       <c r="U48" s="2" t="inlineStr">
@@ -5815,12 +5815,12 @@
       </c>
       <c r="V48" s="2" t="inlineStr">
         <is>
-          <t>22,38%</t>
+          <t>22,31%</t>
         </is>
       </c>
       <c r="W48" s="2" t="inlineStr">
         <is>
-          <t>36,87%</t>
+          <t>36,91%</t>
         </is>
       </c>
     </row>
@@ -5843,12 +5843,12 @@
       </c>
       <c r="E49" s="2" t="inlineStr">
         <is>
-          <t>14521</t>
+          <t>14492</t>
         </is>
       </c>
       <c r="F49" s="2" t="inlineStr">
         <is>
-          <t>26038</t>
+          <t>26037</t>
         </is>
       </c>
       <c r="G49" s="2" t="inlineStr">
@@ -5858,12 +5858,12 @@
       </c>
       <c r="H49" s="2" t="inlineStr">
         <is>
-          <t>28,83%</t>
+          <t>28,78%</t>
         </is>
       </c>
       <c r="I49" s="2" t="inlineStr">
         <is>
-          <t>51,71%</t>
+          <t>51,7%</t>
         </is>
       </c>
       <c r="J49" s="2" t="inlineStr">
@@ -5878,12 +5878,12 @@
       </c>
       <c r="L49" s="2" t="inlineStr">
         <is>
-          <t>25937</t>
+          <t>25709</t>
         </is>
       </c>
       <c r="M49" s="2" t="inlineStr">
         <is>
-          <t>42645</t>
+          <t>42696</t>
         </is>
       </c>
       <c r="N49" s="2" t="inlineStr">
@@ -5893,12 +5893,12 @@
       </c>
       <c r="O49" s="2" t="inlineStr">
         <is>
-          <t>32,25%</t>
+          <t>31,97%</t>
         </is>
       </c>
       <c r="P49" s="2" t="inlineStr">
         <is>
-          <t>53,03%</t>
+          <t>53,09%</t>
         </is>
       </c>
       <c r="Q49" s="2" t="inlineStr">
@@ -5913,12 +5913,12 @@
       </c>
       <c r="S49" s="2" t="inlineStr">
         <is>
-          <t>44123</t>
+          <t>44492</t>
         </is>
       </c>
       <c r="T49" s="2" t="inlineStr">
         <is>
-          <t>64530</t>
+          <t>63685</t>
         </is>
       </c>
       <c r="U49" s="2" t="inlineStr">
@@ -5928,12 +5928,12 @@
       </c>
       <c r="V49" s="2" t="inlineStr">
         <is>
-          <t>33,74%</t>
+          <t>34,02%</t>
         </is>
       </c>
       <c r="W49" s="2" t="inlineStr">
         <is>
-          <t>49,34%</t>
+          <t>48,7%</t>
         </is>
       </c>
     </row>
@@ -5956,12 +5956,12 @@
       </c>
       <c r="E50" s="2" t="inlineStr">
         <is>
-          <t>7245</t>
+          <t>7158</t>
         </is>
       </c>
       <c r="F50" s="2" t="inlineStr">
         <is>
-          <t>16970</t>
+          <t>16746</t>
         </is>
       </c>
       <c r="G50" s="2" t="inlineStr">
@@ -5971,12 +5971,12 @@
       </c>
       <c r="H50" s="2" t="inlineStr">
         <is>
-          <t>14,39%</t>
+          <t>14,21%</t>
         </is>
       </c>
       <c r="I50" s="2" t="inlineStr">
         <is>
-          <t>33,7%</t>
+          <t>33,25%</t>
         </is>
       </c>
       <c r="J50" s="2" t="inlineStr">
@@ -5991,12 +5991,12 @@
       </c>
       <c r="L50" s="2" t="inlineStr">
         <is>
-          <t>8331</t>
+          <t>8321</t>
         </is>
       </c>
       <c r="M50" s="2" t="inlineStr">
         <is>
-          <t>20863</t>
+          <t>20210</t>
         </is>
       </c>
       <c r="N50" s="2" t="inlineStr">
@@ -6006,12 +6006,12 @@
       </c>
       <c r="O50" s="2" t="inlineStr">
         <is>
-          <t>10,36%</t>
+          <t>10,35%</t>
         </is>
       </c>
       <c r="P50" s="2" t="inlineStr">
         <is>
-          <t>25,94%</t>
+          <t>25,13%</t>
         </is>
       </c>
       <c r="Q50" s="2" t="inlineStr">
@@ -6026,12 +6026,12 @@
       </c>
       <c r="S50" s="2" t="inlineStr">
         <is>
-          <t>18127</t>
+          <t>17889</t>
         </is>
       </c>
       <c r="T50" s="2" t="inlineStr">
         <is>
-          <t>34562</t>
+          <t>34281</t>
         </is>
       </c>
       <c r="U50" s="2" t="inlineStr">
@@ -6041,12 +6041,12 @@
       </c>
       <c r="V50" s="2" t="inlineStr">
         <is>
-          <t>13,86%</t>
+          <t>13,68%</t>
         </is>
       </c>
       <c r="W50" s="2" t="inlineStr">
         <is>
-          <t>26,43%</t>
+          <t>26,21%</t>
         </is>
       </c>
     </row>
@@ -6186,12 +6186,12 @@
       </c>
       <c r="E52" s="2" t="inlineStr">
         <is>
-          <t>8604</t>
+          <t>9154</t>
         </is>
       </c>
       <c r="F52" s="2" t="inlineStr">
         <is>
-          <t>23235</t>
+          <t>24443</t>
         </is>
       </c>
       <c r="G52" s="2" t="inlineStr">
@@ -6201,12 +6201,12 @@
       </c>
       <c r="H52" s="2" t="inlineStr">
         <is>
-          <t>3,41%</t>
+          <t>3,63%</t>
         </is>
       </c>
       <c r="I52" s="2" t="inlineStr">
         <is>
-          <t>9,22%</t>
+          <t>9,69%</t>
         </is>
       </c>
       <c r="J52" s="2" t="inlineStr">
@@ -6221,12 +6221,12 @@
       </c>
       <c r="L52" s="2" t="inlineStr">
         <is>
-          <t>13180</t>
+          <t>13446</t>
         </is>
       </c>
       <c r="M52" s="2" t="inlineStr">
         <is>
-          <t>29865</t>
+          <t>29446</t>
         </is>
       </c>
       <c r="N52" s="2" t="inlineStr">
@@ -6236,12 +6236,12 @@
       </c>
       <c r="O52" s="2" t="inlineStr">
         <is>
-          <t>4,7%</t>
+          <t>4,8%</t>
         </is>
       </c>
       <c r="P52" s="2" t="inlineStr">
         <is>
-          <t>10,66%</t>
+          <t>10,51%</t>
         </is>
       </c>
       <c r="Q52" s="2" t="inlineStr">
@@ -6256,12 +6256,12 @@
       </c>
       <c r="S52" s="2" t="inlineStr">
         <is>
-          <t>26045</t>
+          <t>25795</t>
         </is>
       </c>
       <c r="T52" s="2" t="inlineStr">
         <is>
-          <t>48235</t>
+          <t>46620</t>
         </is>
       </c>
       <c r="U52" s="2" t="inlineStr">
@@ -6271,12 +6271,12 @@
       </c>
       <c r="V52" s="2" t="inlineStr">
         <is>
-          <t>4,89%</t>
+          <t>4,84%</t>
         </is>
       </c>
       <c r="W52" s="2" t="inlineStr">
         <is>
-          <t>9,06%</t>
+          <t>8,76%</t>
         </is>
       </c>
     </row>
@@ -6299,12 +6299,12 @@
       </c>
       <c r="E53" s="2" t="inlineStr">
         <is>
-          <t>50871</t>
+          <t>51338</t>
         </is>
       </c>
       <c r="F53" s="2" t="inlineStr">
         <is>
-          <t>138388</t>
+          <t>142413</t>
         </is>
       </c>
       <c r="G53" s="2" t="inlineStr">
@@ -6314,12 +6314,12 @@
       </c>
       <c r="H53" s="2" t="inlineStr">
         <is>
-          <t>20,18%</t>
+          <t>20,36%</t>
         </is>
       </c>
       <c r="I53" s="2" t="inlineStr">
         <is>
-          <t>54,89%</t>
+          <t>56,48%</t>
         </is>
       </c>
       <c r="J53" s="2" t="inlineStr">
@@ -6334,12 +6334,12 @@
       </c>
       <c r="L53" s="2" t="inlineStr">
         <is>
-          <t>58080</t>
+          <t>58500</t>
         </is>
       </c>
       <c r="M53" s="2" t="inlineStr">
         <is>
-          <t>84479</t>
+          <t>85366</t>
         </is>
       </c>
       <c r="N53" s="2" t="inlineStr">
@@ -6349,12 +6349,12 @@
       </c>
       <c r="O53" s="2" t="inlineStr">
         <is>
-          <t>20,72%</t>
+          <t>20,87%</t>
         </is>
       </c>
       <c r="P53" s="2" t="inlineStr">
         <is>
-          <t>30,14%</t>
+          <t>30,46%</t>
         </is>
       </c>
       <c r="Q53" s="2" t="inlineStr">
@@ -6369,12 +6369,12 @@
       </c>
       <c r="S53" s="2" t="inlineStr">
         <is>
-          <t>119905</t>
+          <t>121665</t>
         </is>
       </c>
       <c r="T53" s="2" t="inlineStr">
         <is>
-          <t>213505</t>
+          <t>210906</t>
         </is>
       </c>
       <c r="U53" s="2" t="inlineStr">
@@ -6384,12 +6384,12 @@
       </c>
       <c r="V53" s="2" t="inlineStr">
         <is>
-          <t>22,52%</t>
+          <t>22,85%</t>
         </is>
       </c>
       <c r="W53" s="2" t="inlineStr">
         <is>
-          <t>40,1%</t>
+          <t>39,61%</t>
         </is>
       </c>
     </row>
@@ -6412,12 +6412,12 @@
       </c>
       <c r="E54" s="2" t="inlineStr">
         <is>
-          <t>63966</t>
+          <t>60260</t>
         </is>
       </c>
       <c r="F54" s="2" t="inlineStr">
         <is>
-          <t>112771</t>
+          <t>112187</t>
         </is>
       </c>
       <c r="G54" s="2" t="inlineStr">
@@ -6427,12 +6427,12 @@
       </c>
       <c r="H54" s="2" t="inlineStr">
         <is>
-          <t>25,37%</t>
+          <t>23,9%</t>
         </is>
       </c>
       <c r="I54" s="2" t="inlineStr">
         <is>
-          <t>44,73%</t>
+          <t>44,49%</t>
         </is>
       </c>
       <c r="J54" s="2" t="inlineStr">
@@ -6447,12 +6447,12 @@
       </c>
       <c r="L54" s="2" t="inlineStr">
         <is>
-          <t>100414</t>
+          <t>101797</t>
         </is>
       </c>
       <c r="M54" s="2" t="inlineStr">
         <is>
-          <t>130137</t>
+          <t>129402</t>
         </is>
       </c>
       <c r="N54" s="2" t="inlineStr">
@@ -6462,12 +6462,12 @@
       </c>
       <c r="O54" s="2" t="inlineStr">
         <is>
-          <t>35,83%</t>
+          <t>36,32%</t>
         </is>
       </c>
       <c r="P54" s="2" t="inlineStr">
         <is>
-          <t>46,43%</t>
+          <t>46,17%</t>
         </is>
       </c>
       <c r="Q54" s="2" t="inlineStr">
@@ -6482,12 +6482,12 @@
       </c>
       <c r="S54" s="2" t="inlineStr">
         <is>
-          <t>179111</t>
+          <t>172806</t>
         </is>
       </c>
       <c r="T54" s="2" t="inlineStr">
         <is>
-          <t>236039</t>
+          <t>230690</t>
         </is>
       </c>
       <c r="U54" s="2" t="inlineStr">
@@ -6497,12 +6497,12 @@
       </c>
       <c r="V54" s="2" t="inlineStr">
         <is>
-          <t>33,64%</t>
+          <t>32,46%</t>
         </is>
       </c>
       <c r="W54" s="2" t="inlineStr">
         <is>
-          <t>44,33%</t>
+          <t>43,33%</t>
         </is>
       </c>
     </row>
@@ -6525,12 +6525,12 @@
       </c>
       <c r="E55" s="2" t="inlineStr">
         <is>
-          <t>22935</t>
+          <t>23898</t>
         </is>
       </c>
       <c r="F55" s="2" t="inlineStr">
         <is>
-          <t>45156</t>
+          <t>45198</t>
         </is>
       </c>
       <c r="G55" s="2" t="inlineStr">
@@ -6540,12 +6540,12 @@
       </c>
       <c r="H55" s="2" t="inlineStr">
         <is>
-          <t>9,1%</t>
+          <t>9,48%</t>
         </is>
       </c>
       <c r="I55" s="2" t="inlineStr">
         <is>
-          <t>17,91%</t>
+          <t>17,93%</t>
         </is>
       </c>
       <c r="J55" s="2" t="inlineStr">
@@ -6560,12 +6560,12 @@
       </c>
       <c r="L55" s="2" t="inlineStr">
         <is>
-          <t>36028</t>
+          <t>35108</t>
         </is>
       </c>
       <c r="M55" s="2" t="inlineStr">
         <is>
-          <t>58322</t>
+          <t>57106</t>
         </is>
       </c>
       <c r="N55" s="2" t="inlineStr">
@@ -6575,12 +6575,12 @@
       </c>
       <c r="O55" s="2" t="inlineStr">
         <is>
-          <t>12,85%</t>
+          <t>12,53%</t>
         </is>
       </c>
       <c r="P55" s="2" t="inlineStr">
         <is>
-          <t>20,81%</t>
+          <t>20,38%</t>
         </is>
       </c>
       <c r="Q55" s="2" t="inlineStr">
@@ -6595,12 +6595,12 @@
       </c>
       <c r="S55" s="2" t="inlineStr">
         <is>
-          <t>63763</t>
+          <t>64375</t>
         </is>
       </c>
       <c r="T55" s="2" t="inlineStr">
         <is>
-          <t>96098</t>
+          <t>96832</t>
         </is>
       </c>
       <c r="U55" s="2" t="inlineStr">
@@ -6610,12 +6610,12 @@
       </c>
       <c r="V55" s="2" t="inlineStr">
         <is>
-          <t>11,98%</t>
+          <t>12,09%</t>
         </is>
       </c>
       <c r="W55" s="2" t="inlineStr">
         <is>
-          <t>18,05%</t>
+          <t>18,19%</t>
         </is>
       </c>
     </row>
@@ -6638,12 +6638,12 @@
       </c>
       <c r="E56" s="2" t="inlineStr">
         <is>
-          <t>19490</t>
+          <t>20236</t>
         </is>
       </c>
       <c r="F56" s="2" t="inlineStr">
         <is>
-          <t>39998</t>
+          <t>40142</t>
         </is>
       </c>
       <c r="G56" s="2" t="inlineStr">
@@ -6653,12 +6653,12 @@
       </c>
       <c r="H56" s="2" t="inlineStr">
         <is>
-          <t>7,73%</t>
+          <t>8,03%</t>
         </is>
       </c>
       <c r="I56" s="2" t="inlineStr">
         <is>
-          <t>15,86%</t>
+          <t>15,92%</t>
         </is>
       </c>
       <c r="J56" s="2" t="inlineStr">
@@ -6673,12 +6673,12 @@
       </c>
       <c r="L56" s="2" t="inlineStr">
         <is>
-          <t>20084</t>
+          <t>20098</t>
         </is>
       </c>
       <c r="M56" s="2" t="inlineStr">
         <is>
-          <t>38204</t>
+          <t>38123</t>
         </is>
       </c>
       <c r="N56" s="2" t="inlineStr">
@@ -6693,7 +6693,7 @@
       </c>
       <c r="P56" s="2" t="inlineStr">
         <is>
-          <t>13,63%</t>
+          <t>13,6%</t>
         </is>
       </c>
       <c r="Q56" s="2" t="inlineStr">
@@ -6708,12 +6708,12 @@
       </c>
       <c r="S56" s="2" t="inlineStr">
         <is>
-          <t>46140</t>
+          <t>45025</t>
         </is>
       </c>
       <c r="T56" s="2" t="inlineStr">
         <is>
-          <t>73063</t>
+          <t>73119</t>
         </is>
       </c>
       <c r="U56" s="2" t="inlineStr">
@@ -6723,12 +6723,12 @@
       </c>
       <c r="V56" s="2" t="inlineStr">
         <is>
-          <t>8,67%</t>
+          <t>8,46%</t>
         </is>
       </c>
       <c r="W56" s="2" t="inlineStr">
         <is>
-          <t>13,72%</t>
+          <t>13,73%</t>
         </is>
       </c>
     </row>

--- a/data/trans_orig/AIRE_2-Provincia-trans_orig.xlsx
+++ b/data/trans_orig/AIRE_2-Provincia-trans_orig.xlsx
@@ -541,7 +541,7 @@
       <c r="B1" s="2" t="n"/>
       <c r="C1" s="3" t="inlineStr">
         <is>
-          <t>Niña</t>
+          <t>Niño</t>
         </is>
       </c>
       <c r="D1" s="3" t="n"/>
@@ -552,7 +552,7 @@
       <c r="I1" s="3" t="n"/>
       <c r="J1" s="3" t="inlineStr">
         <is>
-          <t>Niño</t>
+          <t>Niña</t>
         </is>
       </c>
       <c r="K1" s="3" t="n"/>
@@ -833,72 +833,72 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
+          <t>17</t>
+        </is>
+      </c>
+      <c r="D5" s="2" t="inlineStr">
+        <is>
+          <t>9890</t>
+        </is>
+      </c>
+      <c r="E5" s="2" t="inlineStr">
+        <is>
+          <t>5995</t>
+        </is>
+      </c>
+      <c r="F5" s="2" t="inlineStr">
+        <is>
+          <t>14568</t>
+        </is>
+      </c>
+      <c r="G5" s="2" t="inlineStr">
+        <is>
+          <t>34,56%</t>
+        </is>
+      </c>
+      <c r="H5" s="2" t="inlineStr">
+        <is>
+          <t>20,95%</t>
+        </is>
+      </c>
+      <c r="I5" s="2" t="inlineStr">
+        <is>
+          <t>50,91%</t>
+        </is>
+      </c>
+      <c r="J5" s="2" t="inlineStr">
+        <is>
           <t>13</t>
         </is>
       </c>
-      <c r="D5" s="2" t="inlineStr">
-        <is>
-          <t>8327</t>
-        </is>
-      </c>
-      <c r="E5" s="2" t="inlineStr">
-        <is>
-          <t>4423</t>
-        </is>
-      </c>
-      <c r="F5" s="2" t="inlineStr">
-        <is>
-          <t>12983</t>
-        </is>
-      </c>
-      <c r="G5" s="2" t="inlineStr">
-        <is>
-          <t>28,75%</t>
-        </is>
-      </c>
-      <c r="H5" s="2" t="inlineStr">
-        <is>
-          <t>15,27%</t>
-        </is>
-      </c>
-      <c r="I5" s="2" t="inlineStr">
-        <is>
-          <t>44,83%</t>
-        </is>
-      </c>
-      <c r="J5" s="2" t="inlineStr">
-        <is>
-          <t>17</t>
-        </is>
-      </c>
       <c r="K5" s="2" t="inlineStr">
         <is>
-          <t>13536</t>
+          <t>6975</t>
         </is>
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>8406</t>
+          <t>4142</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>19596</t>
+          <t>10756</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
         <is>
-          <t>36,5%</t>
+          <t>28,74%</t>
         </is>
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>22,67%</t>
+          <t>17,06%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>52,84%</t>
+          <t>44,31%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -908,32 +908,32 @@
       </c>
       <c r="R5" s="2" t="inlineStr">
         <is>
-          <t>21862</t>
+          <t>16865</t>
         </is>
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>15937</t>
+          <t>11936</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>29624</t>
+          <t>22402</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
         <is>
-          <t>33,1%</t>
+          <t>31,89%</t>
         </is>
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>24,13%</t>
+          <t>22,57%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>44,85%</t>
+          <t>42,36%</t>
         </is>
       </c>
     </row>
@@ -946,72 +946,72 @@
       </c>
       <c r="C6" s="2" t="inlineStr">
         <is>
+          <t>26</t>
+        </is>
+      </c>
+      <c r="D6" s="2" t="inlineStr">
+        <is>
+          <t>16454</t>
+        </is>
+      </c>
+      <c r="E6" s="2" t="inlineStr">
+        <is>
+          <t>11786</t>
+        </is>
+      </c>
+      <c r="F6" s="2" t="inlineStr">
+        <is>
+          <t>20259</t>
+        </is>
+      </c>
+      <c r="G6" s="2" t="inlineStr">
+        <is>
+          <t>57,5%</t>
+        </is>
+      </c>
+      <c r="H6" s="2" t="inlineStr">
+        <is>
+          <t>41,19%</t>
+        </is>
+      </c>
+      <c r="I6" s="2" t="inlineStr">
+        <is>
+          <t>70,8%</t>
+        </is>
+      </c>
+      <c r="J6" s="2" t="inlineStr">
+        <is>
           <t>21</t>
         </is>
       </c>
-      <c r="D6" s="2" t="inlineStr">
-        <is>
-          <t>15153</t>
-        </is>
-      </c>
-      <c r="E6" s="2" t="inlineStr">
-        <is>
-          <t>10808</t>
-        </is>
-      </c>
-      <c r="F6" s="2" t="inlineStr">
-        <is>
-          <t>20986</t>
-        </is>
-      </c>
-      <c r="G6" s="2" t="inlineStr">
-        <is>
-          <t>52,32%</t>
-        </is>
-      </c>
-      <c r="H6" s="2" t="inlineStr">
-        <is>
-          <t>37,31%</t>
-        </is>
-      </c>
-      <c r="I6" s="2" t="inlineStr">
-        <is>
-          <t>72,46%</t>
-        </is>
-      </c>
-      <c r="J6" s="2" t="inlineStr">
-        <is>
-          <t>26</t>
-        </is>
-      </c>
       <c r="K6" s="2" t="inlineStr">
         <is>
-          <t>20948</t>
+          <t>12191</t>
         </is>
       </c>
       <c r="L6" s="2" t="inlineStr">
         <is>
-          <t>15328</t>
+          <t>8581</t>
         </is>
       </c>
       <c r="M6" s="2" t="inlineStr">
         <is>
-          <t>26851</t>
+          <t>16232</t>
         </is>
       </c>
       <c r="N6" s="2" t="inlineStr">
         <is>
-          <t>56,49%</t>
+          <t>50,23%</t>
         </is>
       </c>
       <c r="O6" s="2" t="inlineStr">
         <is>
-          <t>41,33%</t>
+          <t>35,36%</t>
         </is>
       </c>
       <c r="P6" s="2" t="inlineStr">
         <is>
-          <t>72,41%</t>
+          <t>66,88%</t>
         </is>
       </c>
       <c r="Q6" s="2" t="inlineStr">
@@ -1021,32 +1021,32 @@
       </c>
       <c r="R6" s="2" t="inlineStr">
         <is>
-          <t>36100</t>
+          <t>28645</t>
         </is>
       </c>
       <c r="S6" s="2" t="inlineStr">
         <is>
-          <t>28849</t>
+          <t>23396</t>
         </is>
       </c>
       <c r="T6" s="2" t="inlineStr">
         <is>
-          <t>43107</t>
+          <t>34290</t>
         </is>
       </c>
       <c r="U6" s="2" t="inlineStr">
         <is>
-          <t>54,66%</t>
+          <t>54,16%</t>
         </is>
       </c>
       <c r="V6" s="2" t="inlineStr">
         <is>
-          <t>43,68%</t>
+          <t>44,24%</t>
         </is>
       </c>
       <c r="W6" s="2" t="inlineStr">
         <is>
-          <t>65,27%</t>
+          <t>64,84%</t>
         </is>
       </c>
     </row>
@@ -1059,72 +1059,72 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="D7" s="2" t="inlineStr">
+        <is>
+          <t>594</t>
+        </is>
+      </c>
+      <c r="E7" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="F7" s="2" t="inlineStr">
+        <is>
+          <t>3037</t>
+        </is>
+      </c>
+      <c r="G7" s="2" t="inlineStr">
+        <is>
+          <t>2,08%</t>
+        </is>
+      </c>
+      <c r="H7" s="2" t="inlineStr">
+        <is>
+          <t>0,0%</t>
+        </is>
+      </c>
+      <c r="I7" s="2" t="inlineStr">
+        <is>
+          <t>10,61%</t>
+        </is>
+      </c>
+      <c r="J7" s="2" t="inlineStr">
+        <is>
           <t>7</t>
         </is>
       </c>
-      <c r="D7" s="2" t="inlineStr">
-        <is>
-          <t>4909</t>
-        </is>
-      </c>
-      <c r="E7" s="2" t="inlineStr">
-        <is>
-          <t>1604</t>
-        </is>
-      </c>
-      <c r="F7" s="2" t="inlineStr">
-        <is>
-          <t>8896</t>
-        </is>
-      </c>
-      <c r="G7" s="2" t="inlineStr">
-        <is>
-          <t>16,95%</t>
-        </is>
-      </c>
-      <c r="H7" s="2" t="inlineStr">
-        <is>
-          <t>5,54%</t>
-        </is>
-      </c>
-      <c r="I7" s="2" t="inlineStr">
-        <is>
-          <t>30,71%</t>
-        </is>
-      </c>
-      <c r="J7" s="2" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
       <c r="K7" s="2" t="inlineStr">
         <is>
-          <t>593</t>
+          <t>4521</t>
         </is>
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>1941</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>2521</t>
+          <t>8177</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
         <is>
-          <t>1,6%</t>
+          <t>18,63%</t>
         </is>
       </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
+          <t>8,0%</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>6,8%</t>
+          <t>33,69%</t>
         </is>
       </c>
       <c r="Q7" s="2" t="inlineStr">
@@ -1134,32 +1134,32 @@
       </c>
       <c r="R7" s="2" t="inlineStr">
         <is>
-          <t>5502</t>
+          <t>5115</t>
         </is>
       </c>
       <c r="S7" s="2" t="inlineStr">
         <is>
-          <t>2576</t>
+          <t>2484</t>
         </is>
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>10433</t>
+          <t>9178</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
         <is>
-          <t>8,33%</t>
+          <t>9,67%</t>
         </is>
       </c>
       <c r="V7" s="2" t="inlineStr">
         <is>
-          <t>3,9%</t>
+          <t>4,7%</t>
         </is>
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>15,8%</t>
+          <t>17,35%</t>
         </is>
       </c>
     </row>
@@ -1172,72 +1172,72 @@
       </c>
       <c r="C8" s="2" t="inlineStr">
         <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="D8" s="2" t="inlineStr">
+        <is>
+          <t>1675</t>
+        </is>
+      </c>
+      <c r="E8" s="2" t="inlineStr">
+        <is>
+          <t>342</t>
+        </is>
+      </c>
+      <c r="F8" s="2" t="inlineStr">
+        <is>
+          <t>4741</t>
+        </is>
+      </c>
+      <c r="G8" s="2" t="inlineStr">
+        <is>
+          <t>5,85%</t>
+        </is>
+      </c>
+      <c r="H8" s="2" t="inlineStr">
+        <is>
+          <t>1,19%</t>
+        </is>
+      </c>
+      <c r="I8" s="2" t="inlineStr">
+        <is>
+          <t>16,57%</t>
+        </is>
+      </c>
+      <c r="J8" s="2" t="inlineStr">
+        <is>
           <t>1</t>
         </is>
       </c>
-      <c r="D8" s="2" t="inlineStr">
-        <is>
-          <t>575</t>
-        </is>
-      </c>
-      <c r="E8" s="2" t="inlineStr">
+      <c r="K8" s="2" t="inlineStr">
+        <is>
+          <t>585</t>
+        </is>
+      </c>
+      <c r="L8" s="2" t="inlineStr">
         <is>
           <t>0</t>
         </is>
       </c>
-      <c r="F8" s="2" t="inlineStr">
-        <is>
-          <t>3017</t>
-        </is>
-      </c>
-      <c r="G8" s="2" t="inlineStr">
-        <is>
-          <t>1,99%</t>
-        </is>
-      </c>
-      <c r="H8" s="2" t="inlineStr">
+      <c r="M8" s="2" t="inlineStr">
+        <is>
+          <t>2536</t>
+        </is>
+      </c>
+      <c r="N8" s="2" t="inlineStr">
+        <is>
+          <t>2,41%</t>
+        </is>
+      </c>
+      <c r="O8" s="2" t="inlineStr">
         <is>
           <t>0,0%</t>
         </is>
       </c>
-      <c r="I8" s="2" t="inlineStr">
-        <is>
-          <t>10,42%</t>
-        </is>
-      </c>
-      <c r="J8" s="2" t="inlineStr">
-        <is>
-          <t>3</t>
-        </is>
-      </c>
-      <c r="K8" s="2" t="inlineStr">
-        <is>
-          <t>2008</t>
-        </is>
-      </c>
-      <c r="L8" s="2" t="inlineStr">
-        <is>
-          <t>436</t>
-        </is>
-      </c>
-      <c r="M8" s="2" t="inlineStr">
-        <is>
-          <t>5889</t>
-        </is>
-      </c>
-      <c r="N8" s="2" t="inlineStr">
-        <is>
-          <t>5,41%</t>
-        </is>
-      </c>
-      <c r="O8" s="2" t="inlineStr">
-        <is>
-          <t>1,17%</t>
-        </is>
-      </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t>15,88%</t>
+          <t>10,45%</t>
         </is>
       </c>
       <c r="Q8" s="2" t="inlineStr">
@@ -1247,32 +1247,32 @@
       </c>
       <c r="R8" s="2" t="inlineStr">
         <is>
-          <t>2583</t>
+          <t>2260</t>
         </is>
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>621</t>
+          <t>603</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>6447</t>
+          <t>5628</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
         <is>
-          <t>3,91%</t>
+          <t>4,27%</t>
         </is>
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>0,94%</t>
+          <t>1,14%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>9,76%</t>
+          <t>10,64%</t>
         </is>
       </c>
     </row>
@@ -1285,57 +1285,57 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
+          <t>47</t>
+        </is>
+      </c>
+      <c r="D9" s="2" t="inlineStr">
+        <is>
+          <t>28614</t>
+        </is>
+      </c>
+      <c r="E9" s="2" t="inlineStr">
+        <is>
+          <t>28614</t>
+        </is>
+      </c>
+      <c r="F9" s="2" t="inlineStr">
+        <is>
+          <t>28614</t>
+        </is>
+      </c>
+      <c r="G9" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="H9" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="I9" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="J9" s="2" t="inlineStr">
+        <is>
           <t>42</t>
         </is>
       </c>
-      <c r="D9" s="2" t="inlineStr">
-        <is>
-          <t>28964</t>
-        </is>
-      </c>
-      <c r="E9" s="2" t="inlineStr">
-        <is>
-          <t>28964</t>
-        </is>
-      </c>
-      <c r="F9" s="2" t="inlineStr">
-        <is>
-          <t>28964</t>
-        </is>
-      </c>
-      <c r="G9" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="H9" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="I9" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="J9" s="2" t="inlineStr">
-        <is>
-          <t>47</t>
-        </is>
-      </c>
       <c r="K9" s="2" t="inlineStr">
         <is>
-          <t>37084</t>
+          <t>24271</t>
         </is>
       </c>
       <c r="L9" s="2" t="inlineStr">
         <is>
-          <t>37084</t>
+          <t>24271</t>
         </is>
       </c>
       <c r="M9" s="2" t="inlineStr">
         <is>
-          <t>37084</t>
+          <t>24271</t>
         </is>
       </c>
       <c r="N9" s="2" t="inlineStr">
@@ -1360,17 +1360,17 @@
       </c>
       <c r="R9" s="2" t="inlineStr">
         <is>
-          <t>66047</t>
+          <t>52885</t>
         </is>
       </c>
       <c r="S9" s="2" t="inlineStr">
         <is>
-          <t>66047</t>
+          <t>52885</t>
         </is>
       </c>
       <c r="T9" s="2" t="inlineStr">
         <is>
-          <t>66047</t>
+          <t>52885</t>
         </is>
       </c>
       <c r="U9" s="2" t="inlineStr">
@@ -1402,72 +1402,72 @@
       </c>
       <c r="C10" s="2" t="inlineStr">
         <is>
+          <t>13</t>
+        </is>
+      </c>
+      <c r="D10" s="2" t="inlineStr">
+        <is>
+          <t>8486</t>
+        </is>
+      </c>
+      <c r="E10" s="2" t="inlineStr">
+        <is>
+          <t>4733</t>
+        </is>
+      </c>
+      <c r="F10" s="2" t="inlineStr">
+        <is>
+          <t>14692</t>
+        </is>
+      </c>
+      <c r="G10" s="2" t="inlineStr">
+        <is>
+          <t>22,53%</t>
+        </is>
+      </c>
+      <c r="H10" s="2" t="inlineStr">
+        <is>
+          <t>12,57%</t>
+        </is>
+      </c>
+      <c r="I10" s="2" t="inlineStr">
+        <is>
+          <t>39,01%</t>
+        </is>
+      </c>
+      <c r="J10" s="2" t="inlineStr">
+        <is>
           <t>14</t>
         </is>
       </c>
-      <c r="D10" s="2" t="inlineStr">
-        <is>
-          <t>9375</t>
-        </is>
-      </c>
-      <c r="E10" s="2" t="inlineStr">
-        <is>
-          <t>2120</t>
-        </is>
-      </c>
-      <c r="F10" s="2" t="inlineStr">
-        <is>
-          <t>18763</t>
-        </is>
-      </c>
-      <c r="G10" s="2" t="inlineStr">
-        <is>
-          <t>13,86%</t>
-        </is>
-      </c>
-      <c r="H10" s="2" t="inlineStr">
-        <is>
-          <t>3,13%</t>
-        </is>
-      </c>
-      <c r="I10" s="2" t="inlineStr">
-        <is>
-          <t>27,74%</t>
-        </is>
-      </c>
-      <c r="J10" s="2" t="inlineStr">
-        <is>
-          <t>13</t>
-        </is>
-      </c>
       <c r="K10" s="2" t="inlineStr">
         <is>
-          <t>9675</t>
+          <t>9428</t>
         </is>
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>5295</t>
+          <t>5365</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>15349</t>
+          <t>14250</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
         <is>
-          <t>23,18%</t>
+          <t>22,76%</t>
         </is>
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>12,68%</t>
+          <t>12,95%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>36,77%</t>
+          <t>34,4%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -1477,32 +1477,32 @@
       </c>
       <c r="R10" s="2" t="inlineStr">
         <is>
-          <t>19050</t>
+          <t>17913</t>
         </is>
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>7714</t>
+          <t>12191</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>28630</t>
+          <t>25931</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
         <is>
-          <t>17,42%</t>
+          <t>22,65%</t>
         </is>
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>7,05%</t>
+          <t>15,42%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>26,17%</t>
+          <t>32,79%</t>
         </is>
       </c>
     </row>
@@ -1515,72 +1515,72 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
+          <t>27</t>
+        </is>
+      </c>
+      <c r="D11" s="2" t="inlineStr">
+        <is>
+          <t>17973</t>
+        </is>
+      </c>
+      <c r="E11" s="2" t="inlineStr">
+        <is>
+          <t>12365</t>
+        </is>
+      </c>
+      <c r="F11" s="2" t="inlineStr">
+        <is>
+          <t>23751</t>
+        </is>
+      </c>
+      <c r="G11" s="2" t="inlineStr">
+        <is>
+          <t>47,72%</t>
+        </is>
+      </c>
+      <c r="H11" s="2" t="inlineStr">
+        <is>
+          <t>32,83%</t>
+        </is>
+      </c>
+      <c r="I11" s="2" t="inlineStr">
+        <is>
+          <t>63,06%</t>
+        </is>
+      </c>
+      <c r="J11" s="2" t="inlineStr">
+        <is>
           <t>20</t>
         </is>
       </c>
-      <c r="D11" s="2" t="inlineStr">
-        <is>
-          <t>42446</t>
-        </is>
-      </c>
-      <c r="E11" s="2" t="inlineStr">
-        <is>
-          <t>21438</t>
-        </is>
-      </c>
-      <c r="F11" s="2" t="inlineStr">
-        <is>
-          <t>58681</t>
-        </is>
-      </c>
-      <c r="G11" s="2" t="inlineStr">
-        <is>
-          <t>62,75%</t>
-        </is>
-      </c>
-      <c r="H11" s="2" t="inlineStr">
-        <is>
-          <t>31,69%</t>
-        </is>
-      </c>
-      <c r="I11" s="2" t="inlineStr">
-        <is>
-          <t>86,75%</t>
-        </is>
-      </c>
-      <c r="J11" s="2" t="inlineStr">
-        <is>
-          <t>27</t>
-        </is>
-      </c>
       <c r="K11" s="2" t="inlineStr">
         <is>
-          <t>19820</t>
+          <t>15800</t>
         </is>
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>13757</t>
+          <t>10704</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>25676</t>
+          <t>22649</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
         <is>
-          <t>47,48%</t>
+          <t>38,14%</t>
         </is>
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>32,95%</t>
+          <t>25,84%</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
         <is>
-          <t>61,51%</t>
+          <t>54,68%</t>
         </is>
       </c>
       <c r="Q11" s="2" t="inlineStr">
@@ -1590,32 +1590,32 @@
       </c>
       <c r="R11" s="2" t="inlineStr">
         <is>
-          <t>62266</t>
+          <t>33773</t>
         </is>
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>43033</t>
+          <t>25810</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>88716</t>
+          <t>41580</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
         <is>
-          <t>56,92%</t>
+          <t>42,71%</t>
         </is>
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>39,34%</t>
+          <t>32,64%</t>
         </is>
       </c>
       <c r="W11" s="2" t="inlineStr">
         <is>
-          <t>81,1%</t>
+          <t>52,58%</t>
         </is>
       </c>
     </row>
@@ -1628,72 +1628,72 @@
       </c>
       <c r="C12" s="2" t="inlineStr">
         <is>
+          <t>12</t>
+        </is>
+      </c>
+      <c r="D12" s="2" t="inlineStr">
+        <is>
+          <t>9647</t>
+        </is>
+      </c>
+      <c r="E12" s="2" t="inlineStr">
+        <is>
+          <t>5241</t>
+        </is>
+      </c>
+      <c r="F12" s="2" t="inlineStr">
+        <is>
+          <t>15588</t>
+        </is>
+      </c>
+      <c r="G12" s="2" t="inlineStr">
+        <is>
+          <t>25,61%</t>
+        </is>
+      </c>
+      <c r="H12" s="2" t="inlineStr">
+        <is>
+          <t>13,92%</t>
+        </is>
+      </c>
+      <c r="I12" s="2" t="inlineStr">
+        <is>
+          <t>41,39%</t>
+        </is>
+      </c>
+      <c r="J12" s="2" t="inlineStr">
+        <is>
           <t>17</t>
         </is>
       </c>
-      <c r="D12" s="2" t="inlineStr">
-        <is>
-          <t>12369</t>
-        </is>
-      </c>
-      <c r="E12" s="2" t="inlineStr">
-        <is>
-          <t>3655</t>
-        </is>
-      </c>
-      <c r="F12" s="2" t="inlineStr">
-        <is>
-          <t>23776</t>
-        </is>
-      </c>
-      <c r="G12" s="2" t="inlineStr">
-        <is>
-          <t>18,29%</t>
-        </is>
-      </c>
-      <c r="H12" s="2" t="inlineStr">
-        <is>
-          <t>5,4%</t>
-        </is>
-      </c>
-      <c r="I12" s="2" t="inlineStr">
-        <is>
-          <t>35,15%</t>
-        </is>
-      </c>
-      <c r="J12" s="2" t="inlineStr">
-        <is>
-          <t>12</t>
-        </is>
-      </c>
       <c r="K12" s="2" t="inlineStr">
         <is>
-          <t>10486</t>
+          <t>12656</t>
         </is>
       </c>
       <c r="L12" s="2" t="inlineStr">
         <is>
-          <t>5726</t>
+          <t>7136</t>
         </is>
       </c>
       <c r="M12" s="2" t="inlineStr">
         <is>
-          <t>17368</t>
+          <t>18763</t>
         </is>
       </c>
       <c r="N12" s="2" t="inlineStr">
         <is>
-          <t>25,12%</t>
+          <t>30,56%</t>
         </is>
       </c>
       <c r="O12" s="2" t="inlineStr">
         <is>
-          <t>13,72%</t>
+          <t>17,23%</t>
         </is>
       </c>
       <c r="P12" s="2" t="inlineStr">
         <is>
-          <t>41,6%</t>
+          <t>45,3%</t>
         </is>
       </c>
       <c r="Q12" s="2" t="inlineStr">
@@ -1703,32 +1703,32 @@
       </c>
       <c r="R12" s="2" t="inlineStr">
         <is>
-          <t>22856</t>
+          <t>22303</t>
         </is>
       </c>
       <c r="S12" s="2" t="inlineStr">
         <is>
-          <t>10298</t>
+          <t>15027</t>
         </is>
       </c>
       <c r="T12" s="2" t="inlineStr">
         <is>
-          <t>35177</t>
+          <t>30574</t>
         </is>
       </c>
       <c r="U12" s="2" t="inlineStr">
         <is>
-          <t>20,89%</t>
+          <t>28,2%</t>
         </is>
       </c>
       <c r="V12" s="2" t="inlineStr">
         <is>
-          <t>9,41%</t>
+          <t>19,0%</t>
         </is>
       </c>
       <c r="W12" s="2" t="inlineStr">
         <is>
-          <t>32,16%</t>
+          <t>38,66%</t>
         </is>
       </c>
     </row>
@@ -1741,72 +1741,72 @@
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="D13" s="2" t="inlineStr">
+        <is>
+          <t>359</t>
+        </is>
+      </c>
+      <c r="E13" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="F13" s="2" t="inlineStr">
+        <is>
+          <t>1793</t>
+        </is>
+      </c>
+      <c r="G13" s="2" t="inlineStr">
+        <is>
+          <t>0,95%</t>
+        </is>
+      </c>
+      <c r="H13" s="2" t="inlineStr">
+        <is>
+          <t>0,0%</t>
+        </is>
+      </c>
+      <c r="I13" s="2" t="inlineStr">
+        <is>
+          <t>4,76%</t>
+        </is>
+      </c>
+      <c r="J13" s="2" t="inlineStr">
+        <is>
           <t>3</t>
         </is>
       </c>
-      <c r="D13" s="2" t="inlineStr">
-        <is>
-          <t>1974</t>
-        </is>
-      </c>
-      <c r="E13" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="F13" s="2" t="inlineStr">
-        <is>
-          <t>6128</t>
-        </is>
-      </c>
-      <c r="G13" s="2" t="inlineStr">
-        <is>
-          <t>2,92%</t>
-        </is>
-      </c>
-      <c r="H13" s="2" t="inlineStr">
-        <is>
-          <t>0,0%</t>
-        </is>
-      </c>
-      <c r="I13" s="2" t="inlineStr">
-        <is>
-          <t>9,06%</t>
-        </is>
-      </c>
-      <c r="J13" s="2" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
       <c r="K13" s="2" t="inlineStr">
         <is>
-          <t>464</t>
+          <t>1992</t>
         </is>
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>385</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>2352</t>
+          <t>5868</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
         <is>
-          <t>1,11%</t>
+          <t>4,81%</t>
         </is>
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
+          <t>0,93%</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>5,63%</t>
+          <t>14,17%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -1816,32 +1816,32 @@
       </c>
       <c r="R13" s="2" t="inlineStr">
         <is>
-          <t>2438</t>
+          <t>2350</t>
         </is>
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>508</t>
+          <t>697</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>6679</t>
+          <t>6333</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
         <is>
-          <t>2,23%</t>
+          <t>2,97%</t>
         </is>
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>0,46%</t>
+          <t>0,88%</t>
         </is>
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>6,11%</t>
+          <t>8,01%</t>
         </is>
       </c>
     </row>
@@ -1859,7 +1859,7 @@
       </c>
       <c r="D14" s="2" t="inlineStr">
         <is>
-          <t>1477</t>
+          <t>1199</t>
         </is>
       </c>
       <c r="E14" s="2" t="inlineStr">
@@ -1869,12 +1869,12 @@
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>6026</t>
+          <t>4487</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
         <is>
-          <t>2,18%</t>
+          <t>3,18%</t>
         </is>
       </c>
       <c r="H14" s="2" t="inlineStr">
@@ -1884,7 +1884,7 @@
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>8,91%</t>
+          <t>11,91%</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr">
@@ -1894,7 +1894,7 @@
       </c>
       <c r="K14" s="2" t="inlineStr">
         <is>
-          <t>1301</t>
+          <t>1545</t>
         </is>
       </c>
       <c r="L14" s="2" t="inlineStr">
@@ -1909,7 +1909,7 @@
       </c>
       <c r="N14" s="2" t="inlineStr">
         <is>
-          <t>3,12%</t>
+          <t>3,73%</t>
         </is>
       </c>
       <c r="O14" s="2" t="inlineStr">
@@ -1919,7 +1919,7 @@
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>13,57%</t>
+          <t>13,68%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -1929,32 +1929,32 @@
       </c>
       <c r="R14" s="2" t="inlineStr">
         <is>
-          <t>2778</t>
+          <t>2743</t>
         </is>
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>558</t>
+          <t>862</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>7417</t>
+          <t>7285</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
         <is>
-          <t>2,54%</t>
+          <t>3,47%</t>
         </is>
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>0,51%</t>
+          <t>1,09%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>6,78%</t>
+          <t>9,21%</t>
         </is>
       </c>
     </row>
@@ -1967,57 +1967,57 @@
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
+          <t>55</t>
+        </is>
+      </c>
+      <c r="D15" s="2" t="inlineStr">
+        <is>
+          <t>37663</t>
+        </is>
+      </c>
+      <c r="E15" s="2" t="inlineStr">
+        <is>
+          <t>37663</t>
+        </is>
+      </c>
+      <c r="F15" s="2" t="inlineStr">
+        <is>
+          <t>37663</t>
+        </is>
+      </c>
+      <c r="G15" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="H15" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="I15" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="J15" s="2" t="inlineStr">
+        <is>
           <t>56</t>
         </is>
       </c>
-      <c r="D15" s="2" t="inlineStr">
-        <is>
-          <t>67641</t>
-        </is>
-      </c>
-      <c r="E15" s="2" t="inlineStr">
-        <is>
-          <t>67641</t>
-        </is>
-      </c>
-      <c r="F15" s="2" t="inlineStr">
-        <is>
-          <t>67641</t>
-        </is>
-      </c>
-      <c r="G15" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="H15" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="I15" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="J15" s="2" t="inlineStr">
-        <is>
-          <t>55</t>
-        </is>
-      </c>
       <c r="K15" s="2" t="inlineStr">
         <is>
-          <t>41746</t>
+          <t>41420</t>
         </is>
       </c>
       <c r="L15" s="2" t="inlineStr">
         <is>
-          <t>41746</t>
+          <t>41420</t>
         </is>
       </c>
       <c r="M15" s="2" t="inlineStr">
         <is>
-          <t>41746</t>
+          <t>41420</t>
         </is>
       </c>
       <c r="N15" s="2" t="inlineStr">
@@ -2042,17 +2042,17 @@
       </c>
       <c r="R15" s="2" t="inlineStr">
         <is>
-          <t>109388</t>
+          <t>79083</t>
         </is>
       </c>
       <c r="S15" s="2" t="inlineStr">
         <is>
-          <t>109388</t>
+          <t>79083</t>
         </is>
       </c>
       <c r="T15" s="2" t="inlineStr">
         <is>
-          <t>109388</t>
+          <t>79083</t>
         </is>
       </c>
       <c r="U15" s="2" t="inlineStr">
@@ -2084,107 +2084,107 @@
       </c>
       <c r="C16" s="2" t="inlineStr">
         <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="D16" s="2" t="inlineStr">
+        <is>
+          <t>1389</t>
+        </is>
+      </c>
+      <c r="E16" s="2" t="inlineStr">
+        <is>
+          <t>304</t>
+        </is>
+      </c>
+      <c r="F16" s="2" t="inlineStr">
+        <is>
+          <t>3980</t>
+        </is>
+      </c>
+      <c r="G16" s="2" t="inlineStr">
+        <is>
+          <t>6,09%</t>
+        </is>
+      </c>
+      <c r="H16" s="2" t="inlineStr">
+        <is>
+          <t>1,33%</t>
+        </is>
+      </c>
+      <c r="I16" s="2" t="inlineStr">
+        <is>
+          <t>17,46%</t>
+        </is>
+      </c>
+      <c r="J16" s="2" t="inlineStr">
+        <is>
           <t>0</t>
         </is>
       </c>
-      <c r="D16" s="2" t="inlineStr">
+      <c r="K16" s="2" t="inlineStr">
         <is>
           <t>0</t>
         </is>
       </c>
-      <c r="E16" s="2" t="inlineStr">
+      <c r="L16" s="2" t="inlineStr">
         <is>
           <t>—</t>
         </is>
       </c>
-      <c r="F16" s="2" t="inlineStr">
+      <c r="M16" s="2" t="inlineStr">
         <is>
           <t>—</t>
         </is>
       </c>
-      <c r="G16" s="2" t="inlineStr">
+      <c r="N16" s="2" t="inlineStr">
         <is>
           <t>0,0%</t>
         </is>
       </c>
-      <c r="H16" s="2" t="inlineStr">
+      <c r="O16" s="2" t="inlineStr">
         <is>
           <t>—%</t>
         </is>
       </c>
-      <c r="I16" s="2" t="inlineStr">
+      <c r="P16" s="2" t="inlineStr">
         <is>
           <t>—%</t>
         </is>
       </c>
-      <c r="J16" s="2" t="inlineStr">
+      <c r="Q16" s="2" t="inlineStr">
         <is>
           <t>3</t>
         </is>
       </c>
-      <c r="K16" s="2" t="inlineStr">
-        <is>
-          <t>1550</t>
-        </is>
-      </c>
-      <c r="L16" s="2" t="inlineStr">
-        <is>
-          <t>377</t>
-        </is>
-      </c>
-      <c r="M16" s="2" t="inlineStr">
-        <is>
-          <t>4494</t>
-        </is>
-      </c>
-      <c r="N16" s="2" t="inlineStr">
-        <is>
-          <t>6,03%</t>
-        </is>
-      </c>
-      <c r="O16" s="2" t="inlineStr">
-        <is>
-          <t>1,47%</t>
-        </is>
-      </c>
-      <c r="P16" s="2" t="inlineStr">
-        <is>
-          <t>17,49%</t>
-        </is>
-      </c>
-      <c r="Q16" s="2" t="inlineStr">
-        <is>
-          <t>3</t>
-        </is>
-      </c>
       <c r="R16" s="2" t="inlineStr">
         <is>
-          <t>1551</t>
+          <t>1389</t>
         </is>
       </c>
       <c r="S16" s="2" t="inlineStr">
         <is>
-          <t>371</t>
+          <t>444</t>
         </is>
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>4264</t>
+          <t>5331</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
         <is>
-          <t>3,34%</t>
+          <t>3,2%</t>
         </is>
       </c>
       <c r="V16" s="2" t="inlineStr">
         <is>
-          <t>0,8%</t>
+          <t>1,02%</t>
         </is>
       </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>9,19%</t>
+          <t>12,26%</t>
         </is>
       </c>
     </row>
@@ -2197,72 +2197,72 @@
       </c>
       <c r="C17" s="2" t="inlineStr">
         <is>
+          <t>14</t>
+        </is>
+      </c>
+      <c r="D17" s="2" t="inlineStr">
+        <is>
+          <t>7971</t>
+        </is>
+      </c>
+      <c r="E17" s="2" t="inlineStr">
+        <is>
+          <t>4925</t>
+        </is>
+      </c>
+      <c r="F17" s="2" t="inlineStr">
+        <is>
+          <t>11837</t>
+        </is>
+      </c>
+      <c r="G17" s="2" t="inlineStr">
+        <is>
+          <t>34,96%</t>
+        </is>
+      </c>
+      <c r="H17" s="2" t="inlineStr">
+        <is>
+          <t>21,6%</t>
+        </is>
+      </c>
+      <c r="I17" s="2" t="inlineStr">
+        <is>
+          <t>51,92%</t>
+        </is>
+      </c>
+      <c r="J17" s="2" t="inlineStr">
+        <is>
           <t>8</t>
         </is>
       </c>
-      <c r="D17" s="2" t="inlineStr">
-        <is>
-          <t>4728</t>
-        </is>
-      </c>
-      <c r="E17" s="2" t="inlineStr">
-        <is>
-          <t>2332</t>
-        </is>
-      </c>
-      <c r="F17" s="2" t="inlineStr">
-        <is>
-          <t>8131</t>
-        </is>
-      </c>
-      <c r="G17" s="2" t="inlineStr">
-        <is>
-          <t>22,84%</t>
-        </is>
-      </c>
-      <c r="H17" s="2" t="inlineStr">
-        <is>
-          <t>11,27%</t>
-        </is>
-      </c>
-      <c r="I17" s="2" t="inlineStr">
-        <is>
-          <t>39,28%</t>
-        </is>
-      </c>
-      <c r="J17" s="2" t="inlineStr">
-        <is>
-          <t>14</t>
-        </is>
-      </c>
       <c r="K17" s="2" t="inlineStr">
         <is>
-          <t>9440</t>
+          <t>5027</t>
         </is>
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>5778</t>
+          <t>2405</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>13710</t>
+          <t>8467</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
         <is>
-          <t>36,73%</t>
+          <t>24,32%</t>
         </is>
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>22,48%</t>
+          <t>11,64%</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
         <is>
-          <t>53,35%</t>
+          <t>40,97%</t>
         </is>
       </c>
       <c r="Q17" s="2" t="inlineStr">
@@ -2272,32 +2272,32 @@
       </c>
       <c r="R17" s="2" t="inlineStr">
         <is>
-          <t>14168</t>
+          <t>12998</t>
         </is>
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>9865</t>
+          <t>8833</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>20202</t>
+          <t>17622</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
         <is>
-          <t>30,54%</t>
+          <t>29,9%</t>
         </is>
       </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>21,26%</t>
+          <t>20,32%</t>
         </is>
       </c>
       <c r="W17" s="2" t="inlineStr">
         <is>
-          <t>43,54%</t>
+          <t>40,54%</t>
         </is>
       </c>
     </row>
@@ -2310,72 +2310,72 @@
       </c>
       <c r="C18" s="2" t="inlineStr">
         <is>
+          <t>14</t>
+        </is>
+      </c>
+      <c r="D18" s="2" t="inlineStr">
+        <is>
+          <t>7894</t>
+        </is>
+      </c>
+      <c r="E18" s="2" t="inlineStr">
+        <is>
+          <t>4762</t>
+        </is>
+      </c>
+      <c r="F18" s="2" t="inlineStr">
+        <is>
+          <t>11660</t>
+        </is>
+      </c>
+      <c r="G18" s="2" t="inlineStr">
+        <is>
+          <t>34,62%</t>
+        </is>
+      </c>
+      <c r="H18" s="2" t="inlineStr">
+        <is>
+          <t>20,89%</t>
+        </is>
+      </c>
+      <c r="I18" s="2" t="inlineStr">
+        <is>
+          <t>51,14%</t>
+        </is>
+      </c>
+      <c r="J18" s="2" t="inlineStr">
+        <is>
           <t>18</t>
         </is>
       </c>
-      <c r="D18" s="2" t="inlineStr">
-        <is>
-          <t>10235</t>
-        </is>
-      </c>
-      <c r="E18" s="2" t="inlineStr">
-        <is>
-          <t>6823</t>
-        </is>
-      </c>
-      <c r="F18" s="2" t="inlineStr">
-        <is>
-          <t>13296</t>
-        </is>
-      </c>
-      <c r="G18" s="2" t="inlineStr">
-        <is>
-          <t>49,45%</t>
-        </is>
-      </c>
-      <c r="H18" s="2" t="inlineStr">
-        <is>
-          <t>32,97%</t>
-        </is>
-      </c>
-      <c r="I18" s="2" t="inlineStr">
-        <is>
-          <t>64,24%</t>
-        </is>
-      </c>
-      <c r="J18" s="2" t="inlineStr">
-        <is>
-          <t>14</t>
-        </is>
-      </c>
       <c r="K18" s="2" t="inlineStr">
         <is>
-          <t>8562</t>
+          <t>10061</t>
         </is>
       </c>
       <c r="L18" s="2" t="inlineStr">
         <is>
-          <t>5245</t>
+          <t>6851</t>
         </is>
       </c>
       <c r="M18" s="2" t="inlineStr">
         <is>
-          <t>12463</t>
+          <t>13550</t>
         </is>
       </c>
       <c r="N18" s="2" t="inlineStr">
         <is>
-          <t>33,32%</t>
+          <t>48,68%</t>
         </is>
       </c>
       <c r="O18" s="2" t="inlineStr">
         <is>
-          <t>20,41%</t>
+          <t>33,15%</t>
         </is>
       </c>
       <c r="P18" s="2" t="inlineStr">
         <is>
-          <t>48,5%</t>
+          <t>65,56%</t>
         </is>
       </c>
       <c r="Q18" s="2" t="inlineStr">
@@ -2385,32 +2385,32 @@
       </c>
       <c r="R18" s="2" t="inlineStr">
         <is>
-          <t>18797</t>
+          <t>17955</t>
         </is>
       </c>
       <c r="S18" s="2" t="inlineStr">
         <is>
-          <t>13743</t>
+          <t>13272</t>
         </is>
       </c>
       <c r="T18" s="2" t="inlineStr">
         <is>
-          <t>23914</t>
+          <t>22927</t>
         </is>
       </c>
       <c r="U18" s="2" t="inlineStr">
         <is>
-          <t>40,51%</t>
+          <t>41,31%</t>
         </is>
       </c>
       <c r="V18" s="2" t="inlineStr">
         <is>
-          <t>29,62%</t>
+          <t>30,53%</t>
         </is>
       </c>
       <c r="W18" s="2" t="inlineStr">
         <is>
-          <t>51,54%</t>
+          <t>52,74%</t>
         </is>
       </c>
     </row>
@@ -2423,72 +2423,72 @@
       </c>
       <c r="C19" s="2" t="inlineStr">
         <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="D19" s="2" t="inlineStr">
+        <is>
+          <t>2503</t>
+        </is>
+      </c>
+      <c r="E19" s="2" t="inlineStr">
+        <is>
+          <t>642</t>
+        </is>
+      </c>
+      <c r="F19" s="2" t="inlineStr">
+        <is>
+          <t>5537</t>
+        </is>
+      </c>
+      <c r="G19" s="2" t="inlineStr">
+        <is>
+          <t>10,98%</t>
+        </is>
+      </c>
+      <c r="H19" s="2" t="inlineStr">
+        <is>
+          <t>2,82%</t>
+        </is>
+      </c>
+      <c r="I19" s="2" t="inlineStr">
+        <is>
+          <t>24,29%</t>
+        </is>
+      </c>
+      <c r="J19" s="2" t="inlineStr">
+        <is>
           <t>2</t>
         </is>
       </c>
-      <c r="D19" s="2" t="inlineStr">
-        <is>
-          <t>1241</t>
-        </is>
-      </c>
-      <c r="E19" s="2" t="inlineStr">
+      <c r="K19" s="2" t="inlineStr">
+        <is>
+          <t>1235</t>
+        </is>
+      </c>
+      <c r="L19" s="2" t="inlineStr">
         <is>
           <t>0</t>
         </is>
       </c>
-      <c r="F19" s="2" t="inlineStr">
-        <is>
-          <t>3795</t>
-        </is>
-      </c>
-      <c r="G19" s="2" t="inlineStr">
-        <is>
-          <t>6,0%</t>
-        </is>
-      </c>
-      <c r="H19" s="2" t="inlineStr">
+      <c r="M19" s="2" t="inlineStr">
+        <is>
+          <t>3809</t>
+        </is>
+      </c>
+      <c r="N19" s="2" t="inlineStr">
+        <is>
+          <t>5,97%</t>
+        </is>
+      </c>
+      <c r="O19" s="2" t="inlineStr">
         <is>
           <t>0,0%</t>
         </is>
       </c>
-      <c r="I19" s="2" t="inlineStr">
-        <is>
-          <t>18,33%</t>
-        </is>
-      </c>
-      <c r="J19" s="2" t="inlineStr">
-        <is>
-          <t>4</t>
-        </is>
-      </c>
-      <c r="K19" s="2" t="inlineStr">
-        <is>
-          <t>2629</t>
-        </is>
-      </c>
-      <c r="L19" s="2" t="inlineStr">
-        <is>
-          <t>683</t>
-        </is>
-      </c>
-      <c r="M19" s="2" t="inlineStr">
-        <is>
-          <t>5979</t>
-        </is>
-      </c>
-      <c r="N19" s="2" t="inlineStr">
-        <is>
-          <t>10,23%</t>
-        </is>
-      </c>
-      <c r="O19" s="2" t="inlineStr">
-        <is>
-          <t>2,66%</t>
-        </is>
-      </c>
       <c r="P19" s="2" t="inlineStr">
         <is>
-          <t>23,26%</t>
+          <t>18,43%</t>
         </is>
       </c>
       <c r="Q19" s="2" t="inlineStr">
@@ -2498,32 +2498,32 @@
       </c>
       <c r="R19" s="2" t="inlineStr">
         <is>
-          <t>3871</t>
+          <t>3737</t>
         </is>
       </c>
       <c r="S19" s="2" t="inlineStr">
         <is>
-          <t>1381</t>
+          <t>1778</t>
         </is>
       </c>
       <c r="T19" s="2" t="inlineStr">
         <is>
-          <t>7672</t>
+          <t>7812</t>
         </is>
       </c>
       <c r="U19" s="2" t="inlineStr">
         <is>
-          <t>8,34%</t>
+          <t>8,6%</t>
         </is>
       </c>
       <c r="V19" s="2" t="inlineStr">
         <is>
-          <t>2,98%</t>
+          <t>4,09%</t>
         </is>
       </c>
       <c r="W19" s="2" t="inlineStr">
         <is>
-          <t>16,54%</t>
+          <t>17,97%</t>
         </is>
       </c>
     </row>
@@ -2536,72 +2536,72 @@
       </c>
       <c r="C20" s="2" t="inlineStr">
         <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="D20" s="2" t="inlineStr">
+        <is>
+          <t>3042</t>
+        </is>
+      </c>
+      <c r="E20" s="2" t="inlineStr">
+        <is>
+          <t>1096</t>
+        </is>
+      </c>
+      <c r="F20" s="2" t="inlineStr">
+        <is>
+          <t>6290</t>
+        </is>
+      </c>
+      <c r="G20" s="2" t="inlineStr">
+        <is>
+          <t>13,34%</t>
+        </is>
+      </c>
+      <c r="H20" s="2" t="inlineStr">
+        <is>
+          <t>4,81%</t>
+        </is>
+      </c>
+      <c r="I20" s="2" t="inlineStr">
+        <is>
+          <t>27,59%</t>
+        </is>
+      </c>
+      <c r="J20" s="2" t="inlineStr">
+        <is>
           <t>8</t>
         </is>
       </c>
-      <c r="D20" s="2" t="inlineStr">
-        <is>
-          <t>4494</t>
-        </is>
-      </c>
-      <c r="E20" s="2" t="inlineStr">
-        <is>
-          <t>2044</t>
-        </is>
-      </c>
-      <c r="F20" s="2" t="inlineStr">
-        <is>
-          <t>7897</t>
-        </is>
-      </c>
-      <c r="G20" s="2" t="inlineStr">
-        <is>
-          <t>21,71%</t>
-        </is>
-      </c>
-      <c r="H20" s="2" t="inlineStr">
-        <is>
-          <t>9,87%</t>
-        </is>
-      </c>
-      <c r="I20" s="2" t="inlineStr">
-        <is>
-          <t>38,15%</t>
-        </is>
-      </c>
-      <c r="J20" s="2" t="inlineStr">
-        <is>
-          <t>5</t>
-        </is>
-      </c>
       <c r="K20" s="2" t="inlineStr">
         <is>
-          <t>3517</t>
+          <t>4346</t>
         </is>
       </c>
       <c r="L20" s="2" t="inlineStr">
         <is>
-          <t>1279</t>
+          <t>2161</t>
         </is>
       </c>
       <c r="M20" s="2" t="inlineStr">
         <is>
-          <t>7297</t>
+          <t>7634</t>
         </is>
       </c>
       <c r="N20" s="2" t="inlineStr">
         <is>
-          <t>13,68%</t>
+          <t>21,03%</t>
         </is>
       </c>
       <c r="O20" s="2" t="inlineStr">
         <is>
-          <t>4,98%</t>
+          <t>10,46%</t>
         </is>
       </c>
       <c r="P20" s="2" t="inlineStr">
         <is>
-          <t>28,39%</t>
+          <t>36,93%</t>
         </is>
       </c>
       <c r="Q20" s="2" t="inlineStr">
@@ -2611,32 +2611,32 @@
       </c>
       <c r="R20" s="2" t="inlineStr">
         <is>
-          <t>8011</t>
+          <t>7388</t>
         </is>
       </c>
       <c r="S20" s="2" t="inlineStr">
         <is>
-          <t>4457</t>
+          <t>4246</t>
         </is>
       </c>
       <c r="T20" s="2" t="inlineStr">
         <is>
-          <t>12903</t>
+          <t>11751</t>
         </is>
       </c>
       <c r="U20" s="2" t="inlineStr">
         <is>
-          <t>17,27%</t>
+          <t>17,0%</t>
         </is>
       </c>
       <c r="V20" s="2" t="inlineStr">
         <is>
-          <t>9,61%</t>
+          <t>9,77%</t>
         </is>
       </c>
       <c r="W20" s="2" t="inlineStr">
         <is>
-          <t>27,81%</t>
+          <t>27,03%</t>
         </is>
       </c>
     </row>
@@ -2649,57 +2649,57 @@
       </c>
       <c r="C21" s="2" t="inlineStr">
         <is>
+          <t>40</t>
+        </is>
+      </c>
+      <c r="D21" s="2" t="inlineStr">
+        <is>
+          <t>22799</t>
+        </is>
+      </c>
+      <c r="E21" s="2" t="inlineStr">
+        <is>
+          <t>22799</t>
+        </is>
+      </c>
+      <c r="F21" s="2" t="inlineStr">
+        <is>
+          <t>22799</t>
+        </is>
+      </c>
+      <c r="G21" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="H21" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="I21" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="J21" s="2" t="inlineStr">
+        <is>
           <t>36</t>
         </is>
       </c>
-      <c r="D21" s="2" t="inlineStr">
-        <is>
-          <t>20698</t>
-        </is>
-      </c>
-      <c r="E21" s="2" t="inlineStr">
-        <is>
-          <t>20698</t>
-        </is>
-      </c>
-      <c r="F21" s="2" t="inlineStr">
-        <is>
-          <t>20698</t>
-        </is>
-      </c>
-      <c r="G21" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="H21" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="I21" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="J21" s="2" t="inlineStr">
-        <is>
-          <t>40</t>
-        </is>
-      </c>
       <c r="K21" s="2" t="inlineStr">
         <is>
-          <t>25699</t>
+          <t>20669</t>
         </is>
       </c>
       <c r="L21" s="2" t="inlineStr">
         <is>
-          <t>25699</t>
+          <t>20669</t>
         </is>
       </c>
       <c r="M21" s="2" t="inlineStr">
         <is>
-          <t>25699</t>
+          <t>20669</t>
         </is>
       </c>
       <c r="N21" s="2" t="inlineStr">
@@ -2724,17 +2724,17 @@
       </c>
       <c r="R21" s="2" t="inlineStr">
         <is>
-          <t>46397</t>
+          <t>43468</t>
         </is>
       </c>
       <c r="S21" s="2" t="inlineStr">
         <is>
-          <t>46397</t>
+          <t>43468</t>
         </is>
       </c>
       <c r="T21" s="2" t="inlineStr">
         <is>
-          <t>46397</t>
+          <t>43468</t>
         </is>
       </c>
       <c r="U21" s="2" t="inlineStr">
@@ -2766,72 +2766,72 @@
       </c>
       <c r="C22" s="2" t="inlineStr">
         <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="D22" s="2" t="inlineStr">
+        <is>
+          <t>3181</t>
+        </is>
+      </c>
+      <c r="E22" s="2" t="inlineStr">
+        <is>
+          <t>871</t>
+        </is>
+      </c>
+      <c r="F22" s="2" t="inlineStr">
+        <is>
+          <t>7639</t>
+        </is>
+      </c>
+      <c r="G22" s="2" t="inlineStr">
+        <is>
+          <t>21,15%</t>
+        </is>
+      </c>
+      <c r="H22" s="2" t="inlineStr">
+        <is>
+          <t>5,79%</t>
+        </is>
+      </c>
+      <c r="I22" s="2" t="inlineStr">
+        <is>
+          <t>50,8%</t>
+        </is>
+      </c>
+      <c r="J22" s="2" t="inlineStr">
+        <is>
           <t>4</t>
         </is>
       </c>
-      <c r="D22" s="2" t="inlineStr">
-        <is>
-          <t>3909</t>
-        </is>
-      </c>
-      <c r="E22" s="2" t="inlineStr">
-        <is>
-          <t>1311</t>
-        </is>
-      </c>
-      <c r="F22" s="2" t="inlineStr">
-        <is>
-          <t>8273</t>
-        </is>
-      </c>
-      <c r="G22" s="2" t="inlineStr">
-        <is>
-          <t>17,97%</t>
-        </is>
-      </c>
-      <c r="H22" s="2" t="inlineStr">
-        <is>
-          <t>6,03%</t>
-        </is>
-      </c>
-      <c r="I22" s="2" t="inlineStr">
-        <is>
-          <t>38,03%</t>
-        </is>
-      </c>
-      <c r="J22" s="2" t="inlineStr">
-        <is>
-          <t>5</t>
-        </is>
-      </c>
       <c r="K22" s="2" t="inlineStr">
         <is>
-          <t>3477</t>
+          <t>4286</t>
         </is>
       </c>
       <c r="L22" s="2" t="inlineStr">
         <is>
-          <t>961</t>
+          <t>1157</t>
         </is>
       </c>
       <c r="M22" s="2" t="inlineStr">
         <is>
-          <t>7798</t>
+          <t>8747</t>
         </is>
       </c>
       <c r="N22" s="2" t="inlineStr">
         <is>
-          <t>22,38%</t>
+          <t>19,38%</t>
         </is>
       </c>
       <c r="O22" s="2" t="inlineStr">
         <is>
-          <t>6,18%</t>
+          <t>5,23%</t>
         </is>
       </c>
       <c r="P22" s="2" t="inlineStr">
         <is>
-          <t>50,2%</t>
+          <t>39,55%</t>
         </is>
       </c>
       <c r="Q22" s="2" t="inlineStr">
@@ -2841,32 +2841,32 @@
       </c>
       <c r="R22" s="2" t="inlineStr">
         <is>
-          <t>7386</t>
+          <t>7467</t>
         </is>
       </c>
       <c r="S22" s="2" t="inlineStr">
         <is>
-          <t>3477</t>
+          <t>3512</t>
         </is>
       </c>
       <c r="T22" s="2" t="inlineStr">
         <is>
-          <t>13132</t>
+          <t>13690</t>
         </is>
       </c>
       <c r="U22" s="2" t="inlineStr">
         <is>
-          <t>19,81%</t>
+          <t>20,1%</t>
         </is>
       </c>
       <c r="V22" s="2" t="inlineStr">
         <is>
-          <t>9,33%</t>
+          <t>9,45%</t>
         </is>
       </c>
       <c r="W22" s="2" t="inlineStr">
         <is>
-          <t>35,22%</t>
+          <t>36,85%</t>
         </is>
       </c>
     </row>
@@ -2879,72 +2879,72 @@
       </c>
       <c r="C23" s="2" t="inlineStr">
         <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="D23" s="2" t="inlineStr">
+        <is>
+          <t>3708</t>
+        </is>
+      </c>
+      <c r="E23" s="2" t="inlineStr">
+        <is>
+          <t>617</t>
+        </is>
+      </c>
+      <c r="F23" s="2" t="inlineStr">
+        <is>
+          <t>8439</t>
+        </is>
+      </c>
+      <c r="G23" s="2" t="inlineStr">
+        <is>
+          <t>24,65%</t>
+        </is>
+      </c>
+      <c r="H23" s="2" t="inlineStr">
+        <is>
+          <t>4,11%</t>
+        </is>
+      </c>
+      <c r="I23" s="2" t="inlineStr">
+        <is>
+          <t>56,12%</t>
+        </is>
+      </c>
+      <c r="J23" s="2" t="inlineStr">
+        <is>
           <t>6</t>
         </is>
       </c>
-      <c r="D23" s="2" t="inlineStr">
-        <is>
-          <t>3964</t>
-        </is>
-      </c>
-      <c r="E23" s="2" t="inlineStr">
-        <is>
-          <t>1654</t>
-        </is>
-      </c>
-      <c r="F23" s="2" t="inlineStr">
-        <is>
-          <t>8818</t>
-        </is>
-      </c>
-      <c r="G23" s="2" t="inlineStr">
-        <is>
-          <t>18,23%</t>
-        </is>
-      </c>
-      <c r="H23" s="2" t="inlineStr">
-        <is>
-          <t>7,61%</t>
-        </is>
-      </c>
-      <c r="I23" s="2" t="inlineStr">
-        <is>
-          <t>40,54%</t>
-        </is>
-      </c>
-      <c r="J23" s="2" t="inlineStr">
-        <is>
-          <t>3</t>
-        </is>
-      </c>
       <c r="K23" s="2" t="inlineStr">
         <is>
-          <t>3622</t>
+          <t>3596</t>
         </is>
       </c>
       <c r="L23" s="2" t="inlineStr">
         <is>
-          <t>989</t>
+          <t>1506</t>
         </is>
       </c>
       <c r="M23" s="2" t="inlineStr">
         <is>
-          <t>9039</t>
+          <t>8138</t>
         </is>
       </c>
       <c r="N23" s="2" t="inlineStr">
         <is>
-          <t>23,32%</t>
+          <t>16,26%</t>
         </is>
       </c>
       <c r="O23" s="2" t="inlineStr">
         <is>
-          <t>6,37%</t>
+          <t>6,81%</t>
         </is>
       </c>
       <c r="P23" s="2" t="inlineStr">
         <is>
-          <t>58,19%</t>
+          <t>36,8%</t>
         </is>
       </c>
       <c r="Q23" s="2" t="inlineStr">
@@ -2954,32 +2954,32 @@
       </c>
       <c r="R23" s="2" t="inlineStr">
         <is>
-          <t>7586</t>
+          <t>7304</t>
         </is>
       </c>
       <c r="S23" s="2" t="inlineStr">
         <is>
-          <t>3636</t>
+          <t>3841</t>
         </is>
       </c>
       <c r="T23" s="2" t="inlineStr">
         <is>
-          <t>13589</t>
+          <t>13676</t>
         </is>
       </c>
       <c r="U23" s="2" t="inlineStr">
         <is>
-          <t>20,35%</t>
+          <t>19,66%</t>
         </is>
       </c>
       <c r="V23" s="2" t="inlineStr">
         <is>
-          <t>9,75%</t>
+          <t>10,34%</t>
         </is>
       </c>
       <c r="W23" s="2" t="inlineStr">
         <is>
-          <t>36,45%</t>
+          <t>36,81%</t>
         </is>
       </c>
     </row>
@@ -2992,72 +2992,72 @@
       </c>
       <c r="C24" s="2" t="inlineStr">
         <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="D24" s="2" t="inlineStr">
+        <is>
+          <t>3518</t>
+        </is>
+      </c>
+      <c r="E24" s="2" t="inlineStr">
+        <is>
+          <t>822</t>
+        </is>
+      </c>
+      <c r="F24" s="2" t="inlineStr">
+        <is>
+          <t>8072</t>
+        </is>
+      </c>
+      <c r="G24" s="2" t="inlineStr">
+        <is>
+          <t>23,4%</t>
+        </is>
+      </c>
+      <c r="H24" s="2" t="inlineStr">
+        <is>
+          <t>5,47%</t>
+        </is>
+      </c>
+      <c r="I24" s="2" t="inlineStr">
+        <is>
+          <t>53,68%</t>
+        </is>
+      </c>
+      <c r="J24" s="2" t="inlineStr">
+        <is>
           <t>11</t>
         </is>
       </c>
-      <c r="D24" s="2" t="inlineStr">
-        <is>
-          <t>7038</t>
-        </is>
-      </c>
-      <c r="E24" s="2" t="inlineStr">
-        <is>
-          <t>3739</t>
-        </is>
-      </c>
-      <c r="F24" s="2" t="inlineStr">
-        <is>
-          <t>10924</t>
-        </is>
-      </c>
-      <c r="G24" s="2" t="inlineStr">
-        <is>
-          <t>32,36%</t>
-        </is>
-      </c>
-      <c r="H24" s="2" t="inlineStr">
-        <is>
-          <t>17,19%</t>
-        </is>
-      </c>
-      <c r="I24" s="2" t="inlineStr">
-        <is>
-          <t>50,23%</t>
-        </is>
-      </c>
-      <c r="J24" s="2" t="inlineStr">
-        <is>
-          <t>4</t>
-        </is>
-      </c>
       <c r="K24" s="2" t="inlineStr">
         <is>
-          <t>3786</t>
+          <t>7104</t>
         </is>
       </c>
       <c r="L24" s="2" t="inlineStr">
         <is>
-          <t>1171</t>
+          <t>3776</t>
         </is>
       </c>
       <c r="M24" s="2" t="inlineStr">
         <is>
-          <t>8667</t>
+          <t>11380</t>
         </is>
       </c>
       <c r="N24" s="2" t="inlineStr">
         <is>
-          <t>24,37%</t>
+          <t>32,12%</t>
         </is>
       </c>
       <c r="O24" s="2" t="inlineStr">
         <is>
-          <t>7,54%</t>
+          <t>17,07%</t>
         </is>
       </c>
       <c r="P24" s="2" t="inlineStr">
         <is>
-          <t>55,79%</t>
+          <t>51,45%</t>
         </is>
       </c>
       <c r="Q24" s="2" t="inlineStr">
@@ -3067,32 +3067,32 @@
       </c>
       <c r="R24" s="2" t="inlineStr">
         <is>
-          <t>10825</t>
+          <t>10623</t>
         </is>
       </c>
       <c r="S24" s="2" t="inlineStr">
         <is>
-          <t>6504</t>
+          <t>6091</t>
         </is>
       </c>
       <c r="T24" s="2" t="inlineStr">
         <is>
-          <t>16531</t>
+          <t>15920</t>
         </is>
       </c>
       <c r="U24" s="2" t="inlineStr">
         <is>
-          <t>29,03%</t>
+          <t>28,59%</t>
         </is>
       </c>
       <c r="V24" s="2" t="inlineStr">
         <is>
-          <t>17,44%</t>
+          <t>16,39%</t>
         </is>
       </c>
       <c r="W24" s="2" t="inlineStr">
         <is>
-          <t>44,34%</t>
+          <t>42,85%</t>
         </is>
       </c>
     </row>
@@ -3105,72 +3105,72 @@
       </c>
       <c r="C25" s="2" t="inlineStr">
         <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="D25" s="2" t="inlineStr">
+        <is>
+          <t>2663</t>
+        </is>
+      </c>
+      <c r="E25" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="F25" s="2" t="inlineStr">
+        <is>
+          <t>8046</t>
+        </is>
+      </c>
+      <c r="G25" s="2" t="inlineStr">
+        <is>
+          <t>17,71%</t>
+        </is>
+      </c>
+      <c r="H25" s="2" t="inlineStr">
+        <is>
+          <t>0,0%</t>
+        </is>
+      </c>
+      <c r="I25" s="2" t="inlineStr">
+        <is>
+          <t>53,51%</t>
+        </is>
+      </c>
+      <c r="J25" s="2" t="inlineStr">
+        <is>
           <t>1</t>
         </is>
       </c>
-      <c r="D25" s="2" t="inlineStr">
-        <is>
-          <t>945</t>
-        </is>
-      </c>
-      <c r="E25" s="2" t="inlineStr">
+      <c r="K25" s="2" t="inlineStr">
+        <is>
+          <t>1052</t>
+        </is>
+      </c>
+      <c r="L25" s="2" t="inlineStr">
         <is>
           <t>0</t>
         </is>
       </c>
-      <c r="F25" s="2" t="inlineStr">
-        <is>
-          <t>4433</t>
-        </is>
-      </c>
-      <c r="G25" s="2" t="inlineStr">
-        <is>
-          <t>4,35%</t>
-        </is>
-      </c>
-      <c r="H25" s="2" t="inlineStr">
+      <c r="M25" s="2" t="inlineStr">
+        <is>
+          <t>5091</t>
+        </is>
+      </c>
+      <c r="N25" s="2" t="inlineStr">
+        <is>
+          <t>4,76%</t>
+        </is>
+      </c>
+      <c r="O25" s="2" t="inlineStr">
         <is>
           <t>0,0%</t>
         </is>
       </c>
-      <c r="I25" s="2" t="inlineStr">
-        <is>
-          <t>20,38%</t>
-        </is>
-      </c>
-      <c r="J25" s="2" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="K25" s="2" t="inlineStr">
-        <is>
-          <t>2631</t>
-        </is>
-      </c>
-      <c r="L25" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="M25" s="2" t="inlineStr">
-        <is>
-          <t>7327</t>
-        </is>
-      </c>
-      <c r="N25" s="2" t="inlineStr">
-        <is>
-          <t>16,94%</t>
-        </is>
-      </c>
-      <c r="O25" s="2" t="inlineStr">
-        <is>
-          <t>0,0%</t>
-        </is>
-      </c>
       <c r="P25" s="2" t="inlineStr">
         <is>
-          <t>47,17%</t>
+          <t>23,02%</t>
         </is>
       </c>
       <c r="Q25" s="2" t="inlineStr">
@@ -3180,32 +3180,32 @@
       </c>
       <c r="R25" s="2" t="inlineStr">
         <is>
-          <t>3577</t>
+          <t>3715</t>
         </is>
       </c>
       <c r="S25" s="2" t="inlineStr">
         <is>
-          <t>999</t>
+          <t>971</t>
         </is>
       </c>
       <c r="T25" s="2" t="inlineStr">
         <is>
-          <t>9285</t>
+          <t>9289</t>
         </is>
       </c>
       <c r="U25" s="2" t="inlineStr">
         <is>
-          <t>9,59%</t>
+          <t>10,0%</t>
         </is>
       </c>
       <c r="V25" s="2" t="inlineStr">
         <is>
-          <t>2,68%</t>
+          <t>2,61%</t>
         </is>
       </c>
       <c r="W25" s="2" t="inlineStr">
         <is>
-          <t>24,9%</t>
+          <t>25,0%</t>
         </is>
       </c>
     </row>
@@ -3218,72 +3218,72 @@
       </c>
       <c r="C26" s="2" t="inlineStr">
         <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="D26" s="2" t="inlineStr">
+        <is>
+          <t>1968</t>
+        </is>
+      </c>
+      <c r="E26" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="F26" s="2" t="inlineStr">
+        <is>
+          <t>6809</t>
+        </is>
+      </c>
+      <c r="G26" s="2" t="inlineStr">
+        <is>
+          <t>13,09%</t>
+        </is>
+      </c>
+      <c r="H26" s="2" t="inlineStr">
+        <is>
+          <t>0,0%</t>
+        </is>
+      </c>
+      <c r="I26" s="2" t="inlineStr">
+        <is>
+          <t>45,28%</t>
+        </is>
+      </c>
+      <c r="J26" s="2" t="inlineStr">
+        <is>
           <t>9</t>
         </is>
       </c>
-      <c r="D26" s="2" t="inlineStr">
-        <is>
-          <t>5893</t>
-        </is>
-      </c>
-      <c r="E26" s="2" t="inlineStr">
-        <is>
-          <t>2856</t>
-        </is>
-      </c>
-      <c r="F26" s="2" t="inlineStr">
-        <is>
-          <t>10587</t>
-        </is>
-      </c>
-      <c r="G26" s="2" t="inlineStr">
-        <is>
-          <t>27,09%</t>
-        </is>
-      </c>
-      <c r="H26" s="2" t="inlineStr">
-        <is>
-          <t>13,13%</t>
-        </is>
-      </c>
-      <c r="I26" s="2" t="inlineStr">
-        <is>
-          <t>48,67%</t>
-        </is>
-      </c>
-      <c r="J26" s="2" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
       <c r="K26" s="2" t="inlineStr">
         <is>
-          <t>2017</t>
+          <t>6079</t>
         </is>
       </c>
       <c r="L26" s="2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>2786</t>
         </is>
       </c>
       <c r="M26" s="2" t="inlineStr">
         <is>
-          <t>5972</t>
+          <t>10119</t>
         </is>
       </c>
       <c r="N26" s="2" t="inlineStr">
         <is>
-          <t>12,99%</t>
+          <t>27,49%</t>
         </is>
       </c>
       <c r="O26" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
+          <t>12,6%</t>
         </is>
       </c>
       <c r="P26" s="2" t="inlineStr">
         <is>
-          <t>38,44%</t>
+          <t>45,75%</t>
         </is>
       </c>
       <c r="Q26" s="2" t="inlineStr">
@@ -3293,32 +3293,32 @@
       </c>
       <c r="R26" s="2" t="inlineStr">
         <is>
-          <t>7911</t>
+          <t>8047</t>
         </is>
       </c>
       <c r="S26" s="2" t="inlineStr">
         <is>
-          <t>4388</t>
+          <t>4312</t>
         </is>
       </c>
       <c r="T26" s="2" t="inlineStr">
         <is>
-          <t>13634</t>
+          <t>13055</t>
         </is>
       </c>
       <c r="U26" s="2" t="inlineStr">
         <is>
-          <t>21,22%</t>
+          <t>21,66%</t>
         </is>
       </c>
       <c r="V26" s="2" t="inlineStr">
         <is>
-          <t>11,77%</t>
+          <t>11,6%</t>
         </is>
       </c>
       <c r="W26" s="2" t="inlineStr">
         <is>
-          <t>36,57%</t>
+          <t>35,14%</t>
         </is>
       </c>
     </row>
@@ -3331,57 +3331,57 @@
       </c>
       <c r="C27" s="2" t="inlineStr">
         <is>
+          <t>16</t>
+        </is>
+      </c>
+      <c r="D27" s="2" t="inlineStr">
+        <is>
+          <t>15038</t>
+        </is>
+      </c>
+      <c r="E27" s="2" t="inlineStr">
+        <is>
+          <t>15038</t>
+        </is>
+      </c>
+      <c r="F27" s="2" t="inlineStr">
+        <is>
+          <t>15038</t>
+        </is>
+      </c>
+      <c r="G27" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="H27" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="I27" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="J27" s="2" t="inlineStr">
+        <is>
           <t>31</t>
         </is>
       </c>
-      <c r="D27" s="2" t="inlineStr">
-        <is>
-          <t>21750</t>
-        </is>
-      </c>
-      <c r="E27" s="2" t="inlineStr">
-        <is>
-          <t>21750</t>
-        </is>
-      </c>
-      <c r="F27" s="2" t="inlineStr">
-        <is>
-          <t>21750</t>
-        </is>
-      </c>
-      <c r="G27" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="H27" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="I27" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="J27" s="2" t="inlineStr">
-        <is>
-          <t>16</t>
-        </is>
-      </c>
       <c r="K27" s="2" t="inlineStr">
         <is>
-          <t>15534</t>
+          <t>22117</t>
         </is>
       </c>
       <c r="L27" s="2" t="inlineStr">
         <is>
-          <t>15534</t>
+          <t>22117</t>
         </is>
       </c>
       <c r="M27" s="2" t="inlineStr">
         <is>
-          <t>15534</t>
+          <t>22117</t>
         </is>
       </c>
       <c r="N27" s="2" t="inlineStr">
@@ -3406,17 +3406,17 @@
       </c>
       <c r="R27" s="2" t="inlineStr">
         <is>
-          <t>37284</t>
+          <t>37155</t>
         </is>
       </c>
       <c r="S27" s="2" t="inlineStr">
         <is>
-          <t>37284</t>
+          <t>37155</t>
         </is>
       </c>
       <c r="T27" s="2" t="inlineStr">
         <is>
-          <t>37284</t>
+          <t>37155</t>
         </is>
       </c>
       <c r="U27" s="2" t="inlineStr">
@@ -3561,72 +3561,72 @@
       </c>
       <c r="C29" s="2" t="inlineStr">
         <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="D29" s="2" t="inlineStr">
+        <is>
+          <t>2786</t>
+        </is>
+      </c>
+      <c r="E29" s="2" t="inlineStr">
+        <is>
+          <t>963</t>
+        </is>
+      </c>
+      <c r="F29" s="2" t="inlineStr">
+        <is>
+          <t>5583</t>
+        </is>
+      </c>
+      <c r="G29" s="2" t="inlineStr">
+        <is>
+          <t>21,66%</t>
+        </is>
+      </c>
+      <c r="H29" s="2" t="inlineStr">
+        <is>
+          <t>7,48%</t>
+        </is>
+      </c>
+      <c r="I29" s="2" t="inlineStr">
+        <is>
+          <t>43,41%</t>
+        </is>
+      </c>
+      <c r="J29" s="2" t="inlineStr">
+        <is>
           <t>2</t>
         </is>
       </c>
-      <c r="D29" s="2" t="inlineStr">
-        <is>
-          <t>880</t>
-        </is>
-      </c>
-      <c r="E29" s="2" t="inlineStr">
+      <c r="K29" s="2" t="inlineStr">
+        <is>
+          <t>861</t>
+        </is>
+      </c>
+      <c r="L29" s="2" t="inlineStr">
         <is>
           <t>0</t>
         </is>
       </c>
-      <c r="F29" s="2" t="inlineStr">
-        <is>
-          <t>2900</t>
-        </is>
-      </c>
-      <c r="G29" s="2" t="inlineStr">
-        <is>
-          <t>10,19%</t>
-        </is>
-      </c>
-      <c r="H29" s="2" t="inlineStr">
+      <c r="M29" s="2" t="inlineStr">
+        <is>
+          <t>3127</t>
+        </is>
+      </c>
+      <c r="N29" s="2" t="inlineStr">
+        <is>
+          <t>10,07%</t>
+        </is>
+      </c>
+      <c r="O29" s="2" t="inlineStr">
         <is>
           <t>0,0%</t>
         </is>
       </c>
-      <c r="I29" s="2" t="inlineStr">
-        <is>
-          <t>33,58%</t>
-        </is>
-      </c>
-      <c r="J29" s="2" t="inlineStr">
-        <is>
-          <t>6</t>
-        </is>
-      </c>
-      <c r="K29" s="2" t="inlineStr">
-        <is>
-          <t>2866</t>
-        </is>
-      </c>
-      <c r="L29" s="2" t="inlineStr">
-        <is>
-          <t>1153</t>
-        </is>
-      </c>
-      <c r="M29" s="2" t="inlineStr">
-        <is>
-          <t>5812</t>
-        </is>
-      </c>
-      <c r="N29" s="2" t="inlineStr">
-        <is>
-          <t>22,08%</t>
-        </is>
-      </c>
-      <c r="O29" s="2" t="inlineStr">
-        <is>
-          <t>8,88%</t>
-        </is>
-      </c>
       <c r="P29" s="2" t="inlineStr">
         <is>
-          <t>44,78%</t>
+          <t>36,59%</t>
         </is>
       </c>
       <c r="Q29" s="2" t="inlineStr">
@@ -3636,32 +3636,32 @@
       </c>
       <c r="R29" s="2" t="inlineStr">
         <is>
-          <t>3746</t>
+          <t>3647</t>
         </is>
       </c>
       <c r="S29" s="2" t="inlineStr">
         <is>
-          <t>1553</t>
+          <t>1629</t>
         </is>
       </c>
       <c r="T29" s="2" t="inlineStr">
         <is>
-          <t>6661</t>
+          <t>6740</t>
         </is>
       </c>
       <c r="U29" s="2" t="inlineStr">
         <is>
-          <t>17,33%</t>
+          <t>17,03%</t>
         </is>
       </c>
       <c r="V29" s="2" t="inlineStr">
         <is>
-          <t>7,18%</t>
+          <t>7,61%</t>
         </is>
       </c>
       <c r="W29" s="2" t="inlineStr">
         <is>
-          <t>30,81%</t>
+          <t>31,49%</t>
         </is>
       </c>
     </row>
@@ -3674,74 +3674,74 @@
       </c>
       <c r="C30" s="2" t="inlineStr">
         <is>
+          <t>17</t>
+        </is>
+      </c>
+      <c r="D30" s="2" t="inlineStr">
+        <is>
+          <t>10076</t>
+        </is>
+      </c>
+      <c r="E30" s="2" t="inlineStr">
+        <is>
+          <t>7279</t>
+        </is>
+      </c>
+      <c r="F30" s="2" t="inlineStr">
+        <is>
+          <t>11899</t>
+        </is>
+      </c>
+      <c r="G30" s="2" t="inlineStr">
+        <is>
+          <t>78,34%</t>
+        </is>
+      </c>
+      <c r="H30" s="2" t="inlineStr">
+        <is>
+          <t>56,59%</t>
+        </is>
+      </c>
+      <c r="I30" s="2" t="inlineStr">
+        <is>
+          <t>92,52%</t>
+        </is>
+      </c>
+      <c r="J30" s="2" t="inlineStr">
+        <is>
           <t>15</t>
         </is>
       </c>
-      <c r="D30" s="2" t="inlineStr">
-        <is>
-          <t>7758</t>
-        </is>
-      </c>
-      <c r="E30" s="2" t="inlineStr">
-        <is>
-          <t>5738</t>
-        </is>
-      </c>
-      <c r="F30" s="2" t="inlineStr">
-        <is>
-          <t>8638</t>
-        </is>
-      </c>
-      <c r="G30" s="2" t="inlineStr">
-        <is>
-          <t>89,81%</t>
-        </is>
-      </c>
-      <c r="H30" s="2" t="inlineStr">
-        <is>
-          <t>66,42%</t>
-        </is>
-      </c>
-      <c r="I30" s="2" t="inlineStr">
+      <c r="K30" s="2" t="inlineStr">
+        <is>
+          <t>7685</t>
+        </is>
+      </c>
+      <c r="L30" s="2" t="inlineStr">
+        <is>
+          <t>5419</t>
+        </is>
+      </c>
+      <c r="M30" s="2" t="inlineStr">
+        <is>
+          <t>8546</t>
+        </is>
+      </c>
+      <c r="N30" s="2" t="inlineStr">
+        <is>
+          <t>89,93%</t>
+        </is>
+      </c>
+      <c r="O30" s="2" t="inlineStr">
+        <is>
+          <t>63,41%</t>
+        </is>
+      </c>
+      <c r="P30" s="2" t="inlineStr">
         <is>
           <t>100,0%</t>
         </is>
       </c>
-      <c r="J30" s="2" t="inlineStr">
-        <is>
-          <t>17</t>
-        </is>
-      </c>
-      <c r="K30" s="2" t="inlineStr">
-        <is>
-          <t>10113</t>
-        </is>
-      </c>
-      <c r="L30" s="2" t="inlineStr">
-        <is>
-          <t>7167</t>
-        </is>
-      </c>
-      <c r="M30" s="2" t="inlineStr">
-        <is>
-          <t>11826</t>
-        </is>
-      </c>
-      <c r="N30" s="2" t="inlineStr">
-        <is>
-          <t>77,92%</t>
-        </is>
-      </c>
-      <c r="O30" s="2" t="inlineStr">
-        <is>
-          <t>55,22%</t>
-        </is>
-      </c>
-      <c r="P30" s="2" t="inlineStr">
-        <is>
-          <t>91,12%</t>
-        </is>
-      </c>
       <c r="Q30" s="2" t="inlineStr">
         <is>
           <t>32</t>
@@ -3749,32 +3749,32 @@
       </c>
       <c r="R30" s="2" t="inlineStr">
         <is>
-          <t>17872</t>
+          <t>17761</t>
         </is>
       </c>
       <c r="S30" s="2" t="inlineStr">
         <is>
-          <t>14957</t>
+          <t>14668</t>
         </is>
       </c>
       <c r="T30" s="2" t="inlineStr">
         <is>
-          <t>20065</t>
+          <t>19779</t>
         </is>
       </c>
       <c r="U30" s="2" t="inlineStr">
         <is>
-          <t>82,67%</t>
+          <t>82,97%</t>
         </is>
       </c>
       <c r="V30" s="2" t="inlineStr">
         <is>
-          <t>69,19%</t>
+          <t>68,51%</t>
         </is>
       </c>
       <c r="W30" s="2" t="inlineStr">
         <is>
-          <t>92,82%</t>
+          <t>92,39%</t>
         </is>
       </c>
     </row>
@@ -4013,57 +4013,57 @@
       </c>
       <c r="C33" s="2" t="inlineStr">
         <is>
+          <t>23</t>
+        </is>
+      </c>
+      <c r="D33" s="2" t="inlineStr">
+        <is>
+          <t>12862</t>
+        </is>
+      </c>
+      <c r="E33" s="2" t="inlineStr">
+        <is>
+          <t>12862</t>
+        </is>
+      </c>
+      <c r="F33" s="2" t="inlineStr">
+        <is>
+          <t>12862</t>
+        </is>
+      </c>
+      <c r="G33" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="H33" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="I33" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="J33" s="2" t="inlineStr">
+        <is>
           <t>17</t>
         </is>
       </c>
-      <c r="D33" s="2" t="inlineStr">
-        <is>
-          <t>8638</t>
-        </is>
-      </c>
-      <c r="E33" s="2" t="inlineStr">
-        <is>
-          <t>8638</t>
-        </is>
-      </c>
-      <c r="F33" s="2" t="inlineStr">
-        <is>
-          <t>8638</t>
-        </is>
-      </c>
-      <c r="G33" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="H33" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="I33" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="J33" s="2" t="inlineStr">
-        <is>
-          <t>23</t>
-        </is>
-      </c>
       <c r="K33" s="2" t="inlineStr">
         <is>
-          <t>12979</t>
+          <t>8546</t>
         </is>
       </c>
       <c r="L33" s="2" t="inlineStr">
         <is>
-          <t>12979</t>
+          <t>8546</t>
         </is>
       </c>
       <c r="M33" s="2" t="inlineStr">
         <is>
-          <t>12979</t>
+          <t>8546</t>
         </is>
       </c>
       <c r="N33" s="2" t="inlineStr">
@@ -4088,17 +4088,17 @@
       </c>
       <c r="R33" s="2" t="inlineStr">
         <is>
-          <t>21618</t>
+          <t>21408</t>
         </is>
       </c>
       <c r="S33" s="2" t="inlineStr">
         <is>
-          <t>21618</t>
+          <t>21408</t>
         </is>
       </c>
       <c r="T33" s="2" t="inlineStr">
         <is>
-          <t>21618</t>
+          <t>21408</t>
         </is>
       </c>
       <c r="U33" s="2" t="inlineStr">
@@ -4130,107 +4130,107 @@
       </c>
       <c r="C34" s="2" t="inlineStr">
         <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="D34" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="E34" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="F34" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="G34" s="2" t="inlineStr">
+        <is>
+          <t>0,0%</t>
+        </is>
+      </c>
+      <c r="H34" s="2" t="inlineStr">
+        <is>
+          <t>—%</t>
+        </is>
+      </c>
+      <c r="I34" s="2" t="inlineStr">
+        <is>
+          <t>—%</t>
+        </is>
+      </c>
+      <c r="J34" s="2" t="inlineStr">
+        <is>
           <t>1</t>
         </is>
       </c>
-      <c r="D34" s="2" t="inlineStr">
-        <is>
-          <t>469</t>
-        </is>
-      </c>
-      <c r="E34" s="2" t="inlineStr">
+      <c r="K34" s="2" t="inlineStr">
+        <is>
+          <t>445</t>
+        </is>
+      </c>
+      <c r="L34" s="2" t="inlineStr">
         <is>
           <t>0</t>
         </is>
       </c>
-      <c r="F34" s="2" t="inlineStr">
-        <is>
-          <t>2702</t>
-        </is>
-      </c>
-      <c r="G34" s="2" t="inlineStr">
-        <is>
-          <t>2,62%</t>
-        </is>
-      </c>
-      <c r="H34" s="2" t="inlineStr">
+      <c r="M34" s="2" t="inlineStr">
+        <is>
+          <t>2405</t>
+        </is>
+      </c>
+      <c r="N34" s="2" t="inlineStr">
+        <is>
+          <t>2,5%</t>
+        </is>
+      </c>
+      <c r="O34" s="2" t="inlineStr">
         <is>
           <t>0,0%</t>
         </is>
       </c>
-      <c r="I34" s="2" t="inlineStr">
-        <is>
-          <t>15,09%</t>
-        </is>
-      </c>
-      <c r="J34" s="2" t="inlineStr">
+      <c r="P34" s="2" t="inlineStr">
+        <is>
+          <t>13,52%</t>
+        </is>
+      </c>
+      <c r="Q34" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="R34" s="2" t="inlineStr">
+        <is>
+          <t>445</t>
+        </is>
+      </c>
+      <c r="S34" s="2" t="inlineStr">
         <is>
           <t>0</t>
         </is>
       </c>
-      <c r="K34" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="L34" s="2" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="M34" s="2" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="N34" s="2" t="inlineStr">
+      <c r="T34" s="2" t="inlineStr">
+        <is>
+          <t>1898</t>
+        </is>
+      </c>
+      <c r="U34" s="2" t="inlineStr">
+        <is>
+          <t>1,14%</t>
+        </is>
+      </c>
+      <c r="V34" s="2" t="inlineStr">
         <is>
           <t>0,0%</t>
         </is>
       </c>
-      <c r="O34" s="2" t="inlineStr">
-        <is>
-          <t>—%</t>
-        </is>
-      </c>
-      <c r="P34" s="2" t="inlineStr">
-        <is>
-          <t>—%</t>
-        </is>
-      </c>
-      <c r="Q34" s="2" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="R34" s="2" t="inlineStr">
-        <is>
-          <t>469</t>
-        </is>
-      </c>
-      <c r="S34" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="T34" s="2" t="inlineStr">
-        <is>
-          <t>2380</t>
-        </is>
-      </c>
-      <c r="U34" s="2" t="inlineStr">
-        <is>
-          <t>1,11%</t>
-        </is>
-      </c>
-      <c r="V34" s="2" t="inlineStr">
-        <is>
-          <t>0,0%</t>
-        </is>
-      </c>
       <c r="W34" s="2" t="inlineStr">
         <is>
-          <t>5,65%</t>
+          <t>4,86%</t>
         </is>
       </c>
     </row>
@@ -4243,72 +4243,72 @@
       </c>
       <c r="C35" s="2" t="inlineStr">
         <is>
+          <t>8</t>
+        </is>
+      </c>
+      <c r="D35" s="2" t="inlineStr">
+        <is>
+          <t>4611</t>
+        </is>
+      </c>
+      <c r="E35" s="2" t="inlineStr">
+        <is>
+          <t>2037</t>
+        </is>
+      </c>
+      <c r="F35" s="2" t="inlineStr">
+        <is>
+          <t>8130</t>
+        </is>
+      </c>
+      <c r="G35" s="2" t="inlineStr">
+        <is>
+          <t>21,68%</t>
+        </is>
+      </c>
+      <c r="H35" s="2" t="inlineStr">
+        <is>
+          <t>9,58%</t>
+        </is>
+      </c>
+      <c r="I35" s="2" t="inlineStr">
+        <is>
+          <t>38,22%</t>
+        </is>
+      </c>
+      <c r="J35" s="2" t="inlineStr">
+        <is>
           <t>6</t>
         </is>
       </c>
-      <c r="D35" s="2" t="inlineStr">
-        <is>
-          <t>3369</t>
-        </is>
-      </c>
-      <c r="E35" s="2" t="inlineStr">
-        <is>
-          <t>1494</t>
-        </is>
-      </c>
-      <c r="F35" s="2" t="inlineStr">
-        <is>
-          <t>6800</t>
-        </is>
-      </c>
-      <c r="G35" s="2" t="inlineStr">
-        <is>
-          <t>18,81%</t>
-        </is>
-      </c>
-      <c r="H35" s="2" t="inlineStr">
-        <is>
-          <t>8,34%</t>
-        </is>
-      </c>
-      <c r="I35" s="2" t="inlineStr">
-        <is>
-          <t>37,97%</t>
-        </is>
-      </c>
-      <c r="J35" s="2" t="inlineStr">
-        <is>
-          <t>8</t>
-        </is>
-      </c>
       <c r="K35" s="2" t="inlineStr">
         <is>
-          <t>5141</t>
+          <t>3333</t>
         </is>
       </c>
       <c r="L35" s="2" t="inlineStr">
         <is>
-          <t>2253</t>
+          <t>1189</t>
         </is>
       </c>
       <c r="M35" s="2" t="inlineStr">
         <is>
-          <t>9166</t>
+          <t>6156</t>
         </is>
       </c>
       <c r="N35" s="2" t="inlineStr">
         <is>
-          <t>21,26%</t>
+          <t>18,74%</t>
         </is>
       </c>
       <c r="O35" s="2" t="inlineStr">
         <is>
-          <t>9,31%</t>
+          <t>6,68%</t>
         </is>
       </c>
       <c r="P35" s="2" t="inlineStr">
         <is>
-          <t>37,9%</t>
+          <t>34,62%</t>
         </is>
       </c>
       <c r="Q35" s="2" t="inlineStr">
@@ -4318,32 +4318,32 @@
       </c>
       <c r="R35" s="2" t="inlineStr">
         <is>
-          <t>8510</t>
+          <t>7944</t>
         </is>
       </c>
       <c r="S35" s="2" t="inlineStr">
         <is>
-          <t>5360</t>
+          <t>4525</t>
         </is>
       </c>
       <c r="T35" s="2" t="inlineStr">
         <is>
-          <t>13862</t>
+          <t>12267</t>
         </is>
       </c>
       <c r="U35" s="2" t="inlineStr">
         <is>
-          <t>20,22%</t>
+          <t>20,34%</t>
         </is>
       </c>
       <c r="V35" s="2" t="inlineStr">
         <is>
-          <t>12,73%</t>
+          <t>11,59%</t>
         </is>
       </c>
       <c r="W35" s="2" t="inlineStr">
         <is>
-          <t>32,93%</t>
+          <t>31,41%</t>
         </is>
       </c>
     </row>
@@ -4356,72 +4356,72 @@
       </c>
       <c r="C36" s="2" t="inlineStr">
         <is>
+          <t>24</t>
+        </is>
+      </c>
+      <c r="D36" s="2" t="inlineStr">
+        <is>
+          <t>14721</t>
+        </is>
+      </c>
+      <c r="E36" s="2" t="inlineStr">
+        <is>
+          <t>11104</t>
+        </is>
+      </c>
+      <c r="F36" s="2" t="inlineStr">
+        <is>
+          <t>17736</t>
+        </is>
+      </c>
+      <c r="G36" s="2" t="inlineStr">
+        <is>
+          <t>69,21%</t>
+        </is>
+      </c>
+      <c r="H36" s="2" t="inlineStr">
+        <is>
+          <t>52,21%</t>
+        </is>
+      </c>
+      <c r="I36" s="2" t="inlineStr">
+        <is>
+          <t>83,39%</t>
+        </is>
+      </c>
+      <c r="J36" s="2" t="inlineStr">
+        <is>
           <t>19</t>
         </is>
       </c>
-      <c r="D36" s="2" t="inlineStr">
-        <is>
-          <t>11401</t>
-        </is>
-      </c>
-      <c r="E36" s="2" t="inlineStr">
-        <is>
-          <t>8390</t>
-        </is>
-      </c>
-      <c r="F36" s="2" t="inlineStr">
-        <is>
-          <t>14314</t>
-        </is>
-      </c>
-      <c r="G36" s="2" t="inlineStr">
-        <is>
-          <t>63,66%</t>
-        </is>
-      </c>
-      <c r="H36" s="2" t="inlineStr">
-        <is>
-          <t>46,85%</t>
-        </is>
-      </c>
-      <c r="I36" s="2" t="inlineStr">
-        <is>
-          <t>79,93%</t>
-        </is>
-      </c>
-      <c r="J36" s="2" t="inlineStr">
-        <is>
-          <t>24</t>
-        </is>
-      </c>
       <c r="K36" s="2" t="inlineStr">
         <is>
-          <t>16794</t>
+          <t>11374</t>
         </is>
       </c>
       <c r="L36" s="2" t="inlineStr">
         <is>
-          <t>12434</t>
+          <t>7908</t>
         </is>
       </c>
       <c r="M36" s="2" t="inlineStr">
         <is>
-          <t>20064</t>
+          <t>14090</t>
         </is>
       </c>
       <c r="N36" s="2" t="inlineStr">
         <is>
-          <t>69,44%</t>
+          <t>63,96%</t>
         </is>
       </c>
       <c r="O36" s="2" t="inlineStr">
         <is>
-          <t>51,42%</t>
+          <t>44,47%</t>
         </is>
       </c>
       <c r="P36" s="2" t="inlineStr">
         <is>
-          <t>82,96%</t>
+          <t>79,23%</t>
         </is>
       </c>
       <c r="Q36" s="2" t="inlineStr">
@@ -4431,32 +4431,32 @@
       </c>
       <c r="R36" s="2" t="inlineStr">
         <is>
-          <t>28194</t>
+          <t>26096</t>
         </is>
       </c>
       <c r="S36" s="2" t="inlineStr">
         <is>
-          <t>22660</t>
+          <t>21412</t>
         </is>
       </c>
       <c r="T36" s="2" t="inlineStr">
         <is>
-          <t>32824</t>
+          <t>30552</t>
         </is>
       </c>
       <c r="U36" s="2" t="inlineStr">
         <is>
-          <t>66,98%</t>
+          <t>66,82%</t>
         </is>
       </c>
       <c r="V36" s="2" t="inlineStr">
         <is>
-          <t>53,83%</t>
+          <t>54,83%</t>
         </is>
       </c>
       <c r="W36" s="2" t="inlineStr">
         <is>
-          <t>77,98%</t>
+          <t>78,23%</t>
         </is>
       </c>
     </row>
@@ -4469,107 +4469,107 @@
       </c>
       <c r="C37" s="2" t="inlineStr">
         <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="D37" s="2" t="inlineStr">
+        <is>
+          <t>854</t>
+        </is>
+      </c>
+      <c r="E37" s="2" t="inlineStr">
+        <is>
           <t>0</t>
         </is>
       </c>
-      <c r="D37" s="2" t="inlineStr">
+      <c r="F37" s="2" t="inlineStr">
+        <is>
+          <t>4592</t>
+        </is>
+      </c>
+      <c r="G37" s="2" t="inlineStr">
+        <is>
+          <t>4,02%</t>
+        </is>
+      </c>
+      <c r="H37" s="2" t="inlineStr">
+        <is>
+          <t>0,0%</t>
+        </is>
+      </c>
+      <c r="I37" s="2" t="inlineStr">
+        <is>
+          <t>21,59%</t>
+        </is>
+      </c>
+      <c r="J37" s="2" t="inlineStr">
         <is>
           <t>0</t>
         </is>
       </c>
-      <c r="E37" s="2" t="inlineStr">
+      <c r="K37" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="L37" s="2" t="inlineStr">
         <is>
           <t>—</t>
         </is>
       </c>
-      <c r="F37" s="2" t="inlineStr">
+      <c r="M37" s="2" t="inlineStr">
         <is>
           <t>—</t>
         </is>
       </c>
-      <c r="G37" s="2" t="inlineStr">
+      <c r="N37" s="2" t="inlineStr">
         <is>
           <t>0,0%</t>
         </is>
       </c>
-      <c r="H37" s="2" t="inlineStr">
+      <c r="O37" s="2" t="inlineStr">
         <is>
           <t>—%</t>
         </is>
       </c>
-      <c r="I37" s="2" t="inlineStr">
+      <c r="P37" s="2" t="inlineStr">
         <is>
           <t>—%</t>
         </is>
       </c>
-      <c r="J37" s="2" t="inlineStr">
+      <c r="Q37" s="2" t="inlineStr">
         <is>
           <t>1</t>
         </is>
       </c>
-      <c r="K37" s="2" t="inlineStr">
-        <is>
-          <t>969</t>
-        </is>
-      </c>
-      <c r="L37" s="2" t="inlineStr">
+      <c r="R37" s="2" t="inlineStr">
+        <is>
+          <t>854</t>
+        </is>
+      </c>
+      <c r="S37" s="2" t="inlineStr">
         <is>
           <t>0</t>
         </is>
       </c>
-      <c r="M37" s="2" t="inlineStr">
-        <is>
-          <t>4600</t>
-        </is>
-      </c>
-      <c r="N37" s="2" t="inlineStr">
-        <is>
-          <t>4,01%</t>
-        </is>
-      </c>
-      <c r="O37" s="2" t="inlineStr">
+      <c r="T37" s="2" t="inlineStr">
+        <is>
+          <t>4222</t>
+        </is>
+      </c>
+      <c r="U37" s="2" t="inlineStr">
+        <is>
+          <t>2,19%</t>
+        </is>
+      </c>
+      <c r="V37" s="2" t="inlineStr">
         <is>
           <t>0,0%</t>
         </is>
       </c>
-      <c r="P37" s="2" t="inlineStr">
-        <is>
-          <t>19,02%</t>
-        </is>
-      </c>
-      <c r="Q37" s="2" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="R37" s="2" t="inlineStr">
-        <is>
-          <t>969</t>
-        </is>
-      </c>
-      <c r="S37" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="T37" s="2" t="inlineStr">
-        <is>
-          <t>5279</t>
-        </is>
-      </c>
-      <c r="U37" s="2" t="inlineStr">
-        <is>
-          <t>2,3%</t>
-        </is>
-      </c>
-      <c r="V37" s="2" t="inlineStr">
-        <is>
-          <t>0,0%</t>
-        </is>
-      </c>
       <c r="W37" s="2" t="inlineStr">
         <is>
-          <t>12,54%</t>
+          <t>10,81%</t>
         </is>
       </c>
     </row>
@@ -4582,72 +4582,72 @@
       </c>
       <c r="C38" s="2" t="inlineStr">
         <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="D38" s="2" t="inlineStr">
+        <is>
+          <t>1083</t>
+        </is>
+      </c>
+      <c r="E38" s="2" t="inlineStr">
+        <is>
+          <t>236</t>
+        </is>
+      </c>
+      <c r="F38" s="2" t="inlineStr">
+        <is>
+          <t>3282</t>
+        </is>
+      </c>
+      <c r="G38" s="2" t="inlineStr">
+        <is>
+          <t>5,09%</t>
+        </is>
+      </c>
+      <c r="H38" s="2" t="inlineStr">
+        <is>
+          <t>1,11%</t>
+        </is>
+      </c>
+      <c r="I38" s="2" t="inlineStr">
+        <is>
+          <t>15,43%</t>
+        </is>
+      </c>
+      <c r="J38" s="2" t="inlineStr">
+        <is>
           <t>5</t>
         </is>
       </c>
-      <c r="D38" s="2" t="inlineStr">
-        <is>
-          <t>2670</t>
-        </is>
-      </c>
-      <c r="E38" s="2" t="inlineStr">
-        <is>
-          <t>979</t>
-        </is>
-      </c>
-      <c r="F38" s="2" t="inlineStr">
-        <is>
-          <t>5594</t>
-        </is>
-      </c>
-      <c r="G38" s="2" t="inlineStr">
-        <is>
-          <t>14,91%</t>
-        </is>
-      </c>
-      <c r="H38" s="2" t="inlineStr">
-        <is>
-          <t>5,47%</t>
-        </is>
-      </c>
-      <c r="I38" s="2" t="inlineStr">
-        <is>
-          <t>31,24%</t>
-        </is>
-      </c>
-      <c r="J38" s="2" t="inlineStr">
-        <is>
-          <t>3</t>
-        </is>
-      </c>
       <c r="K38" s="2" t="inlineStr">
         <is>
-          <t>1280</t>
+          <t>2631</t>
         </is>
       </c>
       <c r="L38" s="2" t="inlineStr">
         <is>
-          <t>339</t>
+          <t>1003</t>
         </is>
       </c>
       <c r="M38" s="2" t="inlineStr">
         <is>
-          <t>3972</t>
+          <t>6243</t>
         </is>
       </c>
       <c r="N38" s="2" t="inlineStr">
         <is>
-          <t>5,29%</t>
+          <t>14,79%</t>
         </is>
       </c>
       <c r="O38" s="2" t="inlineStr">
         <is>
-          <t>1,4%</t>
+          <t>5,64%</t>
         </is>
       </c>
       <c r="P38" s="2" t="inlineStr">
         <is>
-          <t>16,42%</t>
+          <t>35,1%</t>
         </is>
       </c>
       <c r="Q38" s="2" t="inlineStr">
@@ -4657,32 +4657,32 @@
       </c>
       <c r="R38" s="2" t="inlineStr">
         <is>
-          <t>3950</t>
+          <t>3714</t>
         </is>
       </c>
       <c r="S38" s="2" t="inlineStr">
         <is>
-          <t>1833</t>
+          <t>1684</t>
         </is>
       </c>
       <c r="T38" s="2" t="inlineStr">
         <is>
-          <t>7442</t>
+          <t>7174</t>
         </is>
       </c>
       <c r="U38" s="2" t="inlineStr">
         <is>
-          <t>9,38%</t>
+          <t>9,51%</t>
         </is>
       </c>
       <c r="V38" s="2" t="inlineStr">
         <is>
-          <t>4,35%</t>
+          <t>4,31%</t>
         </is>
       </c>
       <c r="W38" s="2" t="inlineStr">
         <is>
-          <t>17,68%</t>
+          <t>18,37%</t>
         </is>
       </c>
     </row>
@@ -4695,57 +4695,57 @@
       </c>
       <c r="C39" s="2" t="inlineStr">
         <is>
+          <t>36</t>
+        </is>
+      </c>
+      <c r="D39" s="2" t="inlineStr">
+        <is>
+          <t>21269</t>
+        </is>
+      </c>
+      <c r="E39" s="2" t="inlineStr">
+        <is>
+          <t>21269</t>
+        </is>
+      </c>
+      <c r="F39" s="2" t="inlineStr">
+        <is>
+          <t>21269</t>
+        </is>
+      </c>
+      <c r="G39" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="H39" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="I39" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="J39" s="2" t="inlineStr">
+        <is>
           <t>31</t>
         </is>
       </c>
-      <c r="D39" s="2" t="inlineStr">
-        <is>
-          <t>17908</t>
-        </is>
-      </c>
-      <c r="E39" s="2" t="inlineStr">
-        <is>
-          <t>17908</t>
-        </is>
-      </c>
-      <c r="F39" s="2" t="inlineStr">
-        <is>
-          <t>17908</t>
-        </is>
-      </c>
-      <c r="G39" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="H39" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="I39" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="J39" s="2" t="inlineStr">
-        <is>
-          <t>36</t>
-        </is>
-      </c>
       <c r="K39" s="2" t="inlineStr">
         <is>
-          <t>24184</t>
+          <t>17784</t>
         </is>
       </c>
       <c r="L39" s="2" t="inlineStr">
         <is>
-          <t>24184</t>
+          <t>17784</t>
         </is>
       </c>
       <c r="M39" s="2" t="inlineStr">
         <is>
-          <t>24184</t>
+          <t>17784</t>
         </is>
       </c>
       <c r="N39" s="2" t="inlineStr">
@@ -4770,17 +4770,17 @@
       </c>
       <c r="R39" s="2" t="inlineStr">
         <is>
-          <t>42092</t>
+          <t>39053</t>
         </is>
       </c>
       <c r="S39" s="2" t="inlineStr">
         <is>
-          <t>42092</t>
+          <t>39053</t>
         </is>
       </c>
       <c r="T39" s="2" t="inlineStr">
         <is>
-          <t>42092</t>
+          <t>39053</t>
         </is>
       </c>
       <c r="U39" s="2" t="inlineStr">
@@ -4812,72 +4812,72 @@
       </c>
       <c r="C40" s="2" t="inlineStr">
         <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="D40" s="2" t="inlineStr">
+        <is>
+          <t>4337</t>
+        </is>
+      </c>
+      <c r="E40" s="2" t="inlineStr">
+        <is>
+          <t>1388</t>
+        </is>
+      </c>
+      <c r="F40" s="2" t="inlineStr">
+        <is>
+          <t>9930</t>
+        </is>
+      </c>
+      <c r="G40" s="2" t="inlineStr">
+        <is>
+          <t>10,9%</t>
+        </is>
+      </c>
+      <c r="H40" s="2" t="inlineStr">
+        <is>
+          <t>3,49%</t>
+        </is>
+      </c>
+      <c r="I40" s="2" t="inlineStr">
+        <is>
+          <t>24,96%</t>
+        </is>
+      </c>
+      <c r="J40" s="2" t="inlineStr">
+        <is>
           <t>3</t>
         </is>
       </c>
-      <c r="D40" s="2" t="inlineStr">
-        <is>
-          <t>2028</t>
-        </is>
-      </c>
-      <c r="E40" s="2" t="inlineStr">
-        <is>
-          <t>555</t>
-        </is>
-      </c>
-      <c r="F40" s="2" t="inlineStr">
-        <is>
-          <t>5463</t>
-        </is>
-      </c>
-      <c r="G40" s="2" t="inlineStr">
-        <is>
-          <t>5,61%</t>
-        </is>
-      </c>
-      <c r="H40" s="2" t="inlineStr">
-        <is>
-          <t>1,53%</t>
-        </is>
-      </c>
-      <c r="I40" s="2" t="inlineStr">
-        <is>
-          <t>15,1%</t>
-        </is>
-      </c>
-      <c r="J40" s="2" t="inlineStr">
-        <is>
-          <t>5</t>
-        </is>
-      </c>
       <c r="K40" s="2" t="inlineStr">
         <is>
-          <t>4551</t>
+          <t>2102</t>
         </is>
       </c>
       <c r="L40" s="2" t="inlineStr">
         <is>
-          <t>1655</t>
+          <t>485</t>
         </is>
       </c>
       <c r="M40" s="2" t="inlineStr">
         <is>
-          <t>10192</t>
+          <t>5110</t>
         </is>
       </c>
       <c r="N40" s="2" t="inlineStr">
         <is>
-          <t>10,68%</t>
+          <t>6,22%</t>
         </is>
       </c>
       <c r="O40" s="2" t="inlineStr">
         <is>
-          <t>3,88%</t>
+          <t>1,44%</t>
         </is>
       </c>
       <c r="P40" s="2" t="inlineStr">
         <is>
-          <t>23,91%</t>
+          <t>15,12%</t>
         </is>
       </c>
       <c r="Q40" s="2" t="inlineStr">
@@ -4887,32 +4887,32 @@
       </c>
       <c r="R40" s="2" t="inlineStr">
         <is>
-          <t>6580</t>
+          <t>6440</t>
         </is>
       </c>
       <c r="S40" s="2" t="inlineStr">
         <is>
-          <t>3047</t>
+          <t>2929</t>
         </is>
       </c>
       <c r="T40" s="2" t="inlineStr">
         <is>
-          <t>12472</t>
+          <t>12519</t>
         </is>
       </c>
       <c r="U40" s="2" t="inlineStr">
         <is>
-          <t>8,35%</t>
+          <t>8,75%</t>
         </is>
       </c>
       <c r="V40" s="2" t="inlineStr">
         <is>
-          <t>3,87%</t>
+          <t>3,98%</t>
         </is>
       </c>
       <c r="W40" s="2" t="inlineStr">
         <is>
-          <t>15,83%</t>
+          <t>17,01%</t>
         </is>
       </c>
     </row>
@@ -4925,72 +4925,72 @@
       </c>
       <c r="C41" s="2" t="inlineStr">
         <is>
+          <t>10</t>
+        </is>
+      </c>
+      <c r="D41" s="2" t="inlineStr">
+        <is>
+          <t>7951</t>
+        </is>
+      </c>
+      <c r="E41" s="2" t="inlineStr">
+        <is>
+          <t>4108</t>
+        </is>
+      </c>
+      <c r="F41" s="2" t="inlineStr">
+        <is>
+          <t>13377</t>
+        </is>
+      </c>
+      <c r="G41" s="2" t="inlineStr">
+        <is>
+          <t>19,98%</t>
+        </is>
+      </c>
+      <c r="H41" s="2" t="inlineStr">
+        <is>
+          <t>10,32%</t>
+        </is>
+      </c>
+      <c r="I41" s="2" t="inlineStr">
+        <is>
+          <t>33,62%</t>
+        </is>
+      </c>
+      <c r="J41" s="2" t="inlineStr">
+        <is>
           <t>11</t>
         </is>
       </c>
-      <c r="D41" s="2" t="inlineStr">
-        <is>
-          <t>9024</t>
-        </is>
-      </c>
-      <c r="E41" s="2" t="inlineStr">
-        <is>
-          <t>4702</t>
-        </is>
-      </c>
-      <c r="F41" s="2" t="inlineStr">
-        <is>
-          <t>14902</t>
-        </is>
-      </c>
-      <c r="G41" s="2" t="inlineStr">
-        <is>
-          <t>24,94%</t>
-        </is>
-      </c>
-      <c r="H41" s="2" t="inlineStr">
-        <is>
-          <t>13,0%</t>
-        </is>
-      </c>
-      <c r="I41" s="2" t="inlineStr">
-        <is>
-          <t>41,19%</t>
-        </is>
-      </c>
-      <c r="J41" s="2" t="inlineStr">
-        <is>
-          <t>10</t>
-        </is>
-      </c>
       <c r="K41" s="2" t="inlineStr">
         <is>
-          <t>8373</t>
+          <t>7159</t>
         </is>
       </c>
       <c r="L41" s="2" t="inlineStr">
         <is>
-          <t>4709</t>
+          <t>3925</t>
         </is>
       </c>
       <c r="M41" s="2" t="inlineStr">
         <is>
-          <t>15185</t>
+          <t>11581</t>
         </is>
       </c>
       <c r="N41" s="2" t="inlineStr">
         <is>
-          <t>19,64%</t>
+          <t>21,18%</t>
         </is>
       </c>
       <c r="O41" s="2" t="inlineStr">
         <is>
-          <t>11,05%</t>
+          <t>11,61%</t>
         </is>
       </c>
       <c r="P41" s="2" t="inlineStr">
         <is>
-          <t>35,63%</t>
+          <t>34,26%</t>
         </is>
       </c>
       <c r="Q41" s="2" t="inlineStr">
@@ -5000,32 +5000,32 @@
       </c>
       <c r="R41" s="2" t="inlineStr">
         <is>
-          <t>17397</t>
+          <t>15110</t>
         </is>
       </c>
       <c r="S41" s="2" t="inlineStr">
         <is>
-          <t>10940</t>
+          <t>9861</t>
         </is>
       </c>
       <c r="T41" s="2" t="inlineStr">
         <is>
-          <t>25642</t>
+          <t>22204</t>
         </is>
       </c>
       <c r="U41" s="2" t="inlineStr">
         <is>
-          <t>22,07%</t>
+          <t>20,53%</t>
         </is>
       </c>
       <c r="V41" s="2" t="inlineStr">
         <is>
-          <t>13,88%</t>
+          <t>13,4%</t>
         </is>
       </c>
       <c r="W41" s="2" t="inlineStr">
         <is>
-          <t>32,54%</t>
+          <t>30,17%</t>
         </is>
       </c>
     </row>
@@ -5038,72 +5038,72 @@
       </c>
       <c r="C42" s="2" t="inlineStr">
         <is>
+          <t>26</t>
+        </is>
+      </c>
+      <c r="D42" s="2" t="inlineStr">
+        <is>
+          <t>19864</t>
+        </is>
+      </c>
+      <c r="E42" s="2" t="inlineStr">
+        <is>
+          <t>14372</t>
+        </is>
+      </c>
+      <c r="F42" s="2" t="inlineStr">
+        <is>
+          <t>25313</t>
+        </is>
+      </c>
+      <c r="G42" s="2" t="inlineStr">
+        <is>
+          <t>49,92%</t>
+        </is>
+      </c>
+      <c r="H42" s="2" t="inlineStr">
+        <is>
+          <t>36,12%</t>
+        </is>
+      </c>
+      <c r="I42" s="2" t="inlineStr">
+        <is>
+          <t>63,62%</t>
+        </is>
+      </c>
+      <c r="J42" s="2" t="inlineStr">
+        <is>
           <t>23</t>
         </is>
       </c>
-      <c r="D42" s="2" t="inlineStr">
-        <is>
-          <t>15464</t>
-        </is>
-      </c>
-      <c r="E42" s="2" t="inlineStr">
-        <is>
-          <t>10660</t>
-        </is>
-      </c>
-      <c r="F42" s="2" t="inlineStr">
-        <is>
-          <t>20611</t>
-        </is>
-      </c>
-      <c r="G42" s="2" t="inlineStr">
-        <is>
-          <t>42,74%</t>
-        </is>
-      </c>
-      <c r="H42" s="2" t="inlineStr">
-        <is>
-          <t>29,46%</t>
-        </is>
-      </c>
-      <c r="I42" s="2" t="inlineStr">
-        <is>
-          <t>56,96%</t>
-        </is>
-      </c>
-      <c r="J42" s="2" t="inlineStr">
-        <is>
-          <t>26</t>
-        </is>
-      </c>
       <c r="K42" s="2" t="inlineStr">
         <is>
-          <t>20881</t>
+          <t>15644</t>
         </is>
       </c>
       <c r="L42" s="2" t="inlineStr">
         <is>
-          <t>14153</t>
+          <t>11034</t>
         </is>
       </c>
       <c r="M42" s="2" t="inlineStr">
         <is>
-          <t>26020</t>
+          <t>20485</t>
         </is>
       </c>
       <c r="N42" s="2" t="inlineStr">
         <is>
-          <t>48,99%</t>
+          <t>46,28%</t>
         </is>
       </c>
       <c r="O42" s="2" t="inlineStr">
         <is>
-          <t>33,2%</t>
+          <t>32,64%</t>
         </is>
       </c>
       <c r="P42" s="2" t="inlineStr">
         <is>
-          <t>61,04%</t>
+          <t>60,61%</t>
         </is>
       </c>
       <c r="Q42" s="2" t="inlineStr">
@@ -5113,32 +5113,32 @@
       </c>
       <c r="R42" s="2" t="inlineStr">
         <is>
-          <t>36345</t>
+          <t>35508</t>
         </is>
       </c>
       <c r="S42" s="2" t="inlineStr">
         <is>
-          <t>28076</t>
+          <t>27687</t>
         </is>
       </c>
       <c r="T42" s="2" t="inlineStr">
         <is>
-          <t>44737</t>
+          <t>43168</t>
         </is>
       </c>
       <c r="U42" s="2" t="inlineStr">
         <is>
-          <t>46,12%</t>
+          <t>48,25%</t>
         </is>
       </c>
       <c r="V42" s="2" t="inlineStr">
         <is>
-          <t>35,63%</t>
+          <t>37,62%</t>
         </is>
       </c>
       <c r="W42" s="2" t="inlineStr">
         <is>
-          <t>56,77%</t>
+          <t>58,66%</t>
         </is>
       </c>
     </row>
@@ -5151,72 +5151,72 @@
       </c>
       <c r="C43" s="2" t="inlineStr">
         <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="D43" s="2" t="inlineStr">
+        <is>
+          <t>4596</t>
+        </is>
+      </c>
+      <c r="E43" s="2" t="inlineStr">
+        <is>
+          <t>1811</t>
+        </is>
+      </c>
+      <c r="F43" s="2" t="inlineStr">
+        <is>
+          <t>9480</t>
+        </is>
+      </c>
+      <c r="G43" s="2" t="inlineStr">
+        <is>
+          <t>11,55%</t>
+        </is>
+      </c>
+      <c r="H43" s="2" t="inlineStr">
+        <is>
+          <t>4,55%</t>
+        </is>
+      </c>
+      <c r="I43" s="2" t="inlineStr">
+        <is>
+          <t>23,82%</t>
+        </is>
+      </c>
+      <c r="J43" s="2" t="inlineStr">
+        <is>
           <t>9</t>
         </is>
       </c>
-      <c r="D43" s="2" t="inlineStr">
-        <is>
-          <t>5897</t>
-        </is>
-      </c>
-      <c r="E43" s="2" t="inlineStr">
-        <is>
-          <t>2743</t>
-        </is>
-      </c>
-      <c r="F43" s="2" t="inlineStr">
-        <is>
-          <t>10826</t>
-        </is>
-      </c>
-      <c r="G43" s="2" t="inlineStr">
-        <is>
-          <t>16,3%</t>
-        </is>
-      </c>
-      <c r="H43" s="2" t="inlineStr">
-        <is>
-          <t>7,58%</t>
-        </is>
-      </c>
-      <c r="I43" s="2" t="inlineStr">
-        <is>
-          <t>29,92%</t>
-        </is>
-      </c>
-      <c r="J43" s="2" t="inlineStr">
-        <is>
-          <t>6</t>
-        </is>
-      </c>
       <c r="K43" s="2" t="inlineStr">
         <is>
-          <t>4932</t>
+          <t>5988</t>
         </is>
       </c>
       <c r="L43" s="2" t="inlineStr">
         <is>
-          <t>1815</t>
+          <t>3227</t>
         </is>
       </c>
       <c r="M43" s="2" t="inlineStr">
         <is>
-          <t>10014</t>
+          <t>10888</t>
         </is>
       </c>
       <c r="N43" s="2" t="inlineStr">
         <is>
-          <t>11,57%</t>
+          <t>17,72%</t>
         </is>
       </c>
       <c r="O43" s="2" t="inlineStr">
         <is>
-          <t>4,26%</t>
+          <t>9,55%</t>
         </is>
       </c>
       <c r="P43" s="2" t="inlineStr">
         <is>
-          <t>23,49%</t>
+          <t>32,21%</t>
         </is>
       </c>
       <c r="Q43" s="2" t="inlineStr">
@@ -5226,32 +5226,32 @@
       </c>
       <c r="R43" s="2" t="inlineStr">
         <is>
-          <t>10829</t>
+          <t>10584</t>
         </is>
       </c>
       <c r="S43" s="2" t="inlineStr">
         <is>
-          <t>6137</t>
+          <t>5925</t>
         </is>
       </c>
       <c r="T43" s="2" t="inlineStr">
         <is>
-          <t>16745</t>
+          <t>16730</t>
         </is>
       </c>
       <c r="U43" s="2" t="inlineStr">
         <is>
-          <t>13,74%</t>
+          <t>14,38%</t>
         </is>
       </c>
       <c r="V43" s="2" t="inlineStr">
         <is>
-          <t>7,79%</t>
+          <t>8,05%</t>
         </is>
       </c>
       <c r="W43" s="2" t="inlineStr">
         <is>
-          <t>21,25%</t>
+          <t>22,73%</t>
         </is>
       </c>
     </row>
@@ -5269,32 +5269,32 @@
       </c>
       <c r="D44" s="2" t="inlineStr">
         <is>
-          <t>3769</t>
+          <t>3043</t>
         </is>
       </c>
       <c r="E44" s="2" t="inlineStr">
         <is>
-          <t>1445</t>
+          <t>800</t>
         </is>
       </c>
       <c r="F44" s="2" t="inlineStr">
         <is>
-          <t>8882</t>
+          <t>7409</t>
         </is>
       </c>
       <c r="G44" s="2" t="inlineStr">
         <is>
-          <t>10,42%</t>
+          <t>7,65%</t>
         </is>
       </c>
       <c r="H44" s="2" t="inlineStr">
         <is>
-          <t>3,99%</t>
+          <t>2,01%</t>
         </is>
       </c>
       <c r="I44" s="2" t="inlineStr">
         <is>
-          <t>24,55%</t>
+          <t>18,62%</t>
         </is>
       </c>
       <c r="J44" s="2" t="inlineStr">
@@ -5304,32 +5304,32 @@
       </c>
       <c r="K44" s="2" t="inlineStr">
         <is>
-          <t>3888</t>
+          <t>2907</t>
         </is>
       </c>
       <c r="L44" s="2" t="inlineStr">
         <is>
-          <t>992</t>
+          <t>764</t>
         </is>
       </c>
       <c r="M44" s="2" t="inlineStr">
         <is>
-          <t>9296</t>
+          <t>6925</t>
         </is>
       </c>
       <c r="N44" s="2" t="inlineStr">
         <is>
-          <t>9,12%</t>
+          <t>8,6%</t>
         </is>
       </c>
       <c r="O44" s="2" t="inlineStr">
         <is>
-          <t>2,33%</t>
+          <t>2,26%</t>
         </is>
       </c>
       <c r="P44" s="2" t="inlineStr">
         <is>
-          <t>21,81%</t>
+          <t>20,49%</t>
         </is>
       </c>
       <c r="Q44" s="2" t="inlineStr">
@@ -5339,32 +5339,32 @@
       </c>
       <c r="R44" s="2" t="inlineStr">
         <is>
-          <t>7657</t>
+          <t>5950</t>
         </is>
       </c>
       <c r="S44" s="2" t="inlineStr">
         <is>
-          <t>3653</t>
+          <t>2499</t>
         </is>
       </c>
       <c r="T44" s="2" t="inlineStr">
         <is>
-          <t>13488</t>
+          <t>10830</t>
         </is>
       </c>
       <c r="U44" s="2" t="inlineStr">
         <is>
-          <t>9,72%</t>
+          <t>8,08%</t>
         </is>
       </c>
       <c r="V44" s="2" t="inlineStr">
         <is>
-          <t>4,64%</t>
+          <t>3,4%</t>
         </is>
       </c>
       <c r="W44" s="2" t="inlineStr">
         <is>
-          <t>17,12%</t>
+          <t>14,72%</t>
         </is>
       </c>
     </row>
@@ -5377,57 +5377,57 @@
       </c>
       <c r="C45" s="2" t="inlineStr">
         <is>
+          <t>51</t>
+        </is>
+      </c>
+      <c r="D45" s="2" t="inlineStr">
+        <is>
+          <t>39790</t>
+        </is>
+      </c>
+      <c r="E45" s="2" t="inlineStr">
+        <is>
+          <t>39790</t>
+        </is>
+      </c>
+      <c r="F45" s="2" t="inlineStr">
+        <is>
+          <t>39790</t>
+        </is>
+      </c>
+      <c r="G45" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="H45" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="I45" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="J45" s="2" t="inlineStr">
+        <is>
           <t>50</t>
         </is>
       </c>
-      <c r="D45" s="2" t="inlineStr">
-        <is>
-          <t>36182</t>
-        </is>
-      </c>
-      <c r="E45" s="2" t="inlineStr">
-        <is>
-          <t>36182</t>
-        </is>
-      </c>
-      <c r="F45" s="2" t="inlineStr">
-        <is>
-          <t>36182</t>
-        </is>
-      </c>
-      <c r="G45" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="H45" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="I45" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="J45" s="2" t="inlineStr">
-        <is>
-          <t>51</t>
-        </is>
-      </c>
       <c r="K45" s="2" t="inlineStr">
         <is>
-          <t>42625</t>
+          <t>33800</t>
         </is>
       </c>
       <c r="L45" s="2" t="inlineStr">
         <is>
-          <t>42625</t>
+          <t>33800</t>
         </is>
       </c>
       <c r="M45" s="2" t="inlineStr">
         <is>
-          <t>42625</t>
+          <t>33800</t>
         </is>
       </c>
       <c r="N45" s="2" t="inlineStr">
@@ -5452,17 +5452,17 @@
       </c>
       <c r="R45" s="2" t="inlineStr">
         <is>
-          <t>78807</t>
+          <t>73591</t>
         </is>
       </c>
       <c r="S45" s="2" t="inlineStr">
         <is>
-          <t>78807</t>
+          <t>73591</t>
         </is>
       </c>
       <c r="T45" s="2" t="inlineStr">
         <is>
-          <t>78807</t>
+          <t>73591</t>
         </is>
       </c>
       <c r="U45" s="2" t="inlineStr">
@@ -5494,107 +5494,107 @@
       </c>
       <c r="C46" s="2" t="inlineStr">
         <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="D46" s="2" t="inlineStr">
+        <is>
+          <t>495</t>
+        </is>
+      </c>
+      <c r="E46" s="2" t="inlineStr">
+        <is>
           <t>0</t>
         </is>
       </c>
-      <c r="D46" s="2" t="inlineStr">
+      <c r="F46" s="2" t="inlineStr">
+        <is>
+          <t>2788</t>
+        </is>
+      </c>
+      <c r="G46" s="2" t="inlineStr">
+        <is>
+          <t>0,61%</t>
+        </is>
+      </c>
+      <c r="H46" s="2" t="inlineStr">
+        <is>
+          <t>0,0%</t>
+        </is>
+      </c>
+      <c r="I46" s="2" t="inlineStr">
+        <is>
+          <t>3,43%</t>
+        </is>
+      </c>
+      <c r="J46" s="2" t="inlineStr">
         <is>
           <t>0</t>
         </is>
       </c>
-      <c r="E46" s="2" t="inlineStr">
+      <c r="K46" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="L46" s="2" t="inlineStr">
         <is>
           <t>—</t>
         </is>
       </c>
-      <c r="F46" s="2" t="inlineStr">
+      <c r="M46" s="2" t="inlineStr">
         <is>
           <t>—</t>
         </is>
       </c>
-      <c r="G46" s="2" t="inlineStr">
+      <c r="N46" s="2" t="inlineStr">
         <is>
           <t>0,0%</t>
         </is>
       </c>
-      <c r="H46" s="2" t="inlineStr">
+      <c r="O46" s="2" t="inlineStr">
         <is>
           <t>—%</t>
         </is>
       </c>
-      <c r="I46" s="2" t="inlineStr">
+      <c r="P46" s="2" t="inlineStr">
         <is>
           <t>—%</t>
         </is>
       </c>
-      <c r="J46" s="2" t="inlineStr">
+      <c r="Q46" s="2" t="inlineStr">
         <is>
           <t>1</t>
         </is>
       </c>
-      <c r="K46" s="2" t="inlineStr">
-        <is>
-          <t>596</t>
-        </is>
-      </c>
-      <c r="L46" s="2" t="inlineStr">
+      <c r="R46" s="2" t="inlineStr">
+        <is>
+          <t>495</t>
+        </is>
+      </c>
+      <c r="S46" s="2" t="inlineStr">
         <is>
           <t>0</t>
         </is>
       </c>
-      <c r="M46" s="2" t="inlineStr">
-        <is>
-          <t>3065</t>
-        </is>
-      </c>
-      <c r="N46" s="2" t="inlineStr">
-        <is>
-          <t>0,74%</t>
-        </is>
-      </c>
-      <c r="O46" s="2" t="inlineStr">
+      <c r="T46" s="2" t="inlineStr">
+        <is>
+          <t>2528</t>
+        </is>
+      </c>
+      <c r="U46" s="2" t="inlineStr">
+        <is>
+          <t>0,37%</t>
+        </is>
+      </c>
+      <c r="V46" s="2" t="inlineStr">
         <is>
           <t>0,0%</t>
         </is>
       </c>
-      <c r="P46" s="2" t="inlineStr">
-        <is>
-          <t>3,81%</t>
-        </is>
-      </c>
-      <c r="Q46" s="2" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="R46" s="2" t="inlineStr">
-        <is>
-          <t>596</t>
-        </is>
-      </c>
-      <c r="S46" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="T46" s="2" t="inlineStr">
-        <is>
-          <t>2714</t>
-        </is>
-      </c>
-      <c r="U46" s="2" t="inlineStr">
-        <is>
-          <t>0,46%</t>
-        </is>
-      </c>
-      <c r="V46" s="2" t="inlineStr">
-        <is>
-          <t>0,0%</t>
-        </is>
-      </c>
       <c r="W46" s="2" t="inlineStr">
         <is>
-          <t>2,08%</t>
+          <t>1,9%</t>
         </is>
       </c>
     </row>
@@ -5607,72 +5607,72 @@
       </c>
       <c r="C47" s="2" t="inlineStr">
         <is>
+          <t>10</t>
+        </is>
+      </c>
+      <c r="D47" s="2" t="inlineStr">
+        <is>
+          <t>7522</t>
+        </is>
+      </c>
+      <c r="E47" s="2" t="inlineStr">
+        <is>
+          <t>3580</t>
+        </is>
+      </c>
+      <c r="F47" s="2" t="inlineStr">
+        <is>
+          <t>14514</t>
+        </is>
+      </c>
+      <c r="G47" s="2" t="inlineStr">
+        <is>
+          <t>9,24%</t>
+        </is>
+      </c>
+      <c r="H47" s="2" t="inlineStr">
+        <is>
+          <t>4,4%</t>
+        </is>
+      </c>
+      <c r="I47" s="2" t="inlineStr">
+        <is>
+          <t>17,83%</t>
+        </is>
+      </c>
+      <c r="J47" s="2" t="inlineStr">
+        <is>
           <t>8</t>
         </is>
       </c>
-      <c r="D47" s="2" t="inlineStr">
-        <is>
-          <t>3930</t>
-        </is>
-      </c>
-      <c r="E47" s="2" t="inlineStr">
-        <is>
-          <t>1744</t>
-        </is>
-      </c>
-      <c r="F47" s="2" t="inlineStr">
-        <is>
-          <t>7364</t>
-        </is>
-      </c>
-      <c r="G47" s="2" t="inlineStr">
-        <is>
-          <t>7,8%</t>
-        </is>
-      </c>
-      <c r="H47" s="2" t="inlineStr">
-        <is>
-          <t>3,46%</t>
-        </is>
-      </c>
-      <c r="I47" s="2" t="inlineStr">
-        <is>
-          <t>14,62%</t>
-        </is>
-      </c>
-      <c r="J47" s="2" t="inlineStr">
-        <is>
-          <t>10</t>
-        </is>
-      </c>
       <c r="K47" s="2" t="inlineStr">
         <is>
-          <t>8173</t>
+          <t>3830</t>
         </is>
       </c>
       <c r="L47" s="2" t="inlineStr">
         <is>
-          <t>3800</t>
+          <t>1741</t>
         </is>
       </c>
       <c r="M47" s="2" t="inlineStr">
         <is>
-          <t>13933</t>
+          <t>7980</t>
         </is>
       </c>
       <c r="N47" s="2" t="inlineStr">
         <is>
-          <t>10,16%</t>
+          <t>7,44%</t>
         </is>
       </c>
       <c r="O47" s="2" t="inlineStr">
         <is>
-          <t>4,73%</t>
+          <t>3,38%</t>
         </is>
       </c>
       <c r="P47" s="2" t="inlineStr">
         <is>
-          <t>17,33%</t>
+          <t>15,49%</t>
         </is>
       </c>
       <c r="Q47" s="2" t="inlineStr">
@@ -5682,32 +5682,32 @@
       </c>
       <c r="R47" s="2" t="inlineStr">
         <is>
-          <t>12103</t>
+          <t>11352</t>
         </is>
       </c>
       <c r="S47" s="2" t="inlineStr">
         <is>
-          <t>7065</t>
+          <t>6637</t>
         </is>
       </c>
       <c r="T47" s="2" t="inlineStr">
         <is>
-          <t>19067</t>
+          <t>18536</t>
         </is>
       </c>
       <c r="U47" s="2" t="inlineStr">
         <is>
-          <t>9,25%</t>
+          <t>8,54%</t>
         </is>
       </c>
       <c r="V47" s="2" t="inlineStr">
         <is>
-          <t>5,4%</t>
+          <t>4,99%</t>
         </is>
       </c>
       <c r="W47" s="2" t="inlineStr">
         <is>
-          <t>14,58%</t>
+          <t>13,95%</t>
         </is>
       </c>
     </row>
@@ -5720,72 +5720,72 @@
       </c>
       <c r="C48" s="2" t="inlineStr">
         <is>
+          <t>30</t>
+        </is>
+      </c>
+      <c r="D48" s="2" t="inlineStr">
+        <is>
+          <t>24418</t>
+        </is>
+      </c>
+      <c r="E48" s="2" t="inlineStr">
+        <is>
+          <t>17526</t>
+        </is>
+      </c>
+      <c r="F48" s="2" t="inlineStr">
+        <is>
+          <t>32671</t>
+        </is>
+      </c>
+      <c r="G48" s="2" t="inlineStr">
+        <is>
+          <t>30,0%</t>
+        </is>
+      </c>
+      <c r="H48" s="2" t="inlineStr">
+        <is>
+          <t>21,53%</t>
+        </is>
+      </c>
+      <c r="I48" s="2" t="inlineStr">
+        <is>
+          <t>40,14%</t>
+        </is>
+      </c>
+      <c r="J48" s="2" t="inlineStr">
+        <is>
           <t>24</t>
         </is>
       </c>
-      <c r="D48" s="2" t="inlineStr">
-        <is>
-          <t>15169</t>
-        </is>
-      </c>
-      <c r="E48" s="2" t="inlineStr">
-        <is>
-          <t>10538</t>
-        </is>
-      </c>
-      <c r="F48" s="2" t="inlineStr">
-        <is>
-          <t>21176</t>
-        </is>
-      </c>
-      <c r="G48" s="2" t="inlineStr">
-        <is>
-          <t>30,12%</t>
-        </is>
-      </c>
-      <c r="H48" s="2" t="inlineStr">
-        <is>
-          <t>20,93%</t>
-        </is>
-      </c>
-      <c r="I48" s="2" t="inlineStr">
-        <is>
-          <t>42,05%</t>
-        </is>
-      </c>
-      <c r="J48" s="2" t="inlineStr">
-        <is>
-          <t>30</t>
-        </is>
-      </c>
       <c r="K48" s="2" t="inlineStr">
         <is>
-          <t>23767</t>
+          <t>15238</t>
         </is>
       </c>
       <c r="L48" s="2" t="inlineStr">
         <is>
-          <t>17167</t>
+          <t>10377</t>
         </is>
       </c>
       <c r="M48" s="2" t="inlineStr">
         <is>
-          <t>32047</t>
+          <t>21095</t>
         </is>
       </c>
       <c r="N48" s="2" t="inlineStr">
         <is>
-          <t>29,55%</t>
+          <t>29,58%</t>
         </is>
       </c>
       <c r="O48" s="2" t="inlineStr">
         <is>
-          <t>21,35%</t>
+          <t>20,15%</t>
         </is>
       </c>
       <c r="P48" s="2" t="inlineStr">
         <is>
-          <t>39,85%</t>
+          <t>40,95%</t>
         </is>
       </c>
       <c r="Q48" s="2" t="inlineStr">
@@ -5795,32 +5795,32 @@
       </c>
       <c r="R48" s="2" t="inlineStr">
         <is>
-          <t>38937</t>
+          <t>39656</t>
         </is>
       </c>
       <c r="S48" s="2" t="inlineStr">
         <is>
-          <t>29182</t>
+          <t>31127</t>
         </is>
       </c>
       <c r="T48" s="2" t="inlineStr">
         <is>
-          <t>48272</t>
+          <t>49196</t>
         </is>
       </c>
       <c r="U48" s="2" t="inlineStr">
         <is>
-          <t>29,77%</t>
+          <t>29,84%</t>
         </is>
       </c>
       <c r="V48" s="2" t="inlineStr">
         <is>
-          <t>22,31%</t>
+          <t>23,42%</t>
         </is>
       </c>
       <c r="W48" s="2" t="inlineStr">
         <is>
-          <t>36,91%</t>
+          <t>37,02%</t>
         </is>
       </c>
     </row>
@@ -5833,72 +5833,72 @@
       </c>
       <c r="C49" s="2" t="inlineStr">
         <is>
+          <t>43</t>
+        </is>
+      </c>
+      <c r="D49" s="2" t="inlineStr">
+        <is>
+          <t>34945</t>
+        </is>
+      </c>
+      <c r="E49" s="2" t="inlineStr">
+        <is>
+          <t>26301</t>
+        </is>
+      </c>
+      <c r="F49" s="2" t="inlineStr">
+        <is>
+          <t>43037</t>
+        </is>
+      </c>
+      <c r="G49" s="2" t="inlineStr">
+        <is>
+          <t>42,93%</t>
+        </is>
+      </c>
+      <c r="H49" s="2" t="inlineStr">
+        <is>
+          <t>32,31%</t>
+        </is>
+      </c>
+      <c r="I49" s="2" t="inlineStr">
+        <is>
+          <t>52,87%</t>
+        </is>
+      </c>
+      <c r="J49" s="2" t="inlineStr">
+        <is>
           <t>31</t>
         </is>
       </c>
-      <c r="D49" s="2" t="inlineStr">
-        <is>
-          <t>19856</t>
-        </is>
-      </c>
-      <c r="E49" s="2" t="inlineStr">
-        <is>
-          <t>14492</t>
-        </is>
-      </c>
-      <c r="F49" s="2" t="inlineStr">
-        <is>
-          <t>26037</t>
-        </is>
-      </c>
-      <c r="G49" s="2" t="inlineStr">
-        <is>
-          <t>39,43%</t>
-        </is>
-      </c>
-      <c r="H49" s="2" t="inlineStr">
-        <is>
-          <t>28,78%</t>
-        </is>
-      </c>
-      <c r="I49" s="2" t="inlineStr">
-        <is>
-          <t>51,7%</t>
-        </is>
-      </c>
-      <c r="J49" s="2" t="inlineStr">
-        <is>
-          <t>43</t>
-        </is>
-      </c>
       <c r="K49" s="2" t="inlineStr">
         <is>
-          <t>34013</t>
+          <t>20279</t>
         </is>
       </c>
       <c r="L49" s="2" t="inlineStr">
         <is>
-          <t>25709</t>
+          <t>14462</t>
         </is>
       </c>
       <c r="M49" s="2" t="inlineStr">
         <is>
-          <t>42696</t>
+          <t>26162</t>
         </is>
       </c>
       <c r="N49" s="2" t="inlineStr">
         <is>
-          <t>42,29%</t>
+          <t>39,37%</t>
         </is>
       </c>
       <c r="O49" s="2" t="inlineStr">
         <is>
-          <t>31,97%</t>
+          <t>28,08%</t>
         </is>
       </c>
       <c r="P49" s="2" t="inlineStr">
         <is>
-          <t>53,09%</t>
+          <t>50,79%</t>
         </is>
       </c>
       <c r="Q49" s="2" t="inlineStr">
@@ -5908,32 +5908,32 @@
       </c>
       <c r="R49" s="2" t="inlineStr">
         <is>
-          <t>53869</t>
+          <t>55225</t>
         </is>
       </c>
       <c r="S49" s="2" t="inlineStr">
         <is>
-          <t>44492</t>
+          <t>45204</t>
         </is>
       </c>
       <c r="T49" s="2" t="inlineStr">
         <is>
-          <t>63685</t>
+          <t>65614</t>
         </is>
       </c>
       <c r="U49" s="2" t="inlineStr">
         <is>
-          <t>41,19%</t>
+          <t>41,55%</t>
         </is>
       </c>
       <c r="V49" s="2" t="inlineStr">
         <is>
-          <t>34,02%</t>
+          <t>34,01%</t>
         </is>
       </c>
       <c r="W49" s="2" t="inlineStr">
         <is>
-          <t>48,7%</t>
+          <t>49,37%</t>
         </is>
       </c>
     </row>
@@ -5951,32 +5951,32 @@
       </c>
       <c r="D50" s="2" t="inlineStr">
         <is>
-          <t>11403</t>
+          <t>14014</t>
         </is>
       </c>
       <c r="E50" s="2" t="inlineStr">
         <is>
-          <t>7158</t>
+          <t>8328</t>
         </is>
       </c>
       <c r="F50" s="2" t="inlineStr">
         <is>
-          <t>16746</t>
+          <t>21090</t>
         </is>
       </c>
       <c r="G50" s="2" t="inlineStr">
         <is>
-          <t>22,64%</t>
+          <t>17,22%</t>
         </is>
       </c>
       <c r="H50" s="2" t="inlineStr">
         <is>
-          <t>14,21%</t>
+          <t>10,23%</t>
         </is>
       </c>
       <c r="I50" s="2" t="inlineStr">
         <is>
-          <t>33,25%</t>
+          <t>25,91%</t>
         </is>
       </c>
       <c r="J50" s="2" t="inlineStr">
@@ -5986,32 +5986,32 @@
       </c>
       <c r="K50" s="2" t="inlineStr">
         <is>
-          <t>13871</t>
+          <t>12164</t>
         </is>
       </c>
       <c r="L50" s="2" t="inlineStr">
         <is>
-          <t>8321</t>
+          <t>7565</t>
         </is>
       </c>
       <c r="M50" s="2" t="inlineStr">
         <is>
-          <t>20210</t>
+          <t>18018</t>
         </is>
       </c>
       <c r="N50" s="2" t="inlineStr">
         <is>
-          <t>17,25%</t>
+          <t>23,61%</t>
         </is>
       </c>
       <c r="O50" s="2" t="inlineStr">
         <is>
-          <t>10,35%</t>
+          <t>14,69%</t>
         </is>
       </c>
       <c r="P50" s="2" t="inlineStr">
         <is>
-          <t>25,13%</t>
+          <t>34,98%</t>
         </is>
       </c>
       <c r="Q50" s="2" t="inlineStr">
@@ -6021,32 +6021,32 @@
       </c>
       <c r="R50" s="2" t="inlineStr">
         <is>
-          <t>25273</t>
+          <t>26179</t>
         </is>
       </c>
       <c r="S50" s="2" t="inlineStr">
         <is>
-          <t>17889</t>
+          <t>19196</t>
         </is>
       </c>
       <c r="T50" s="2" t="inlineStr">
         <is>
-          <t>34281</t>
+          <t>35831</t>
         </is>
       </c>
       <c r="U50" s="2" t="inlineStr">
         <is>
-          <t>19,33%</t>
+          <t>19,7%</t>
         </is>
       </c>
       <c r="V50" s="2" t="inlineStr">
         <is>
-          <t>13,68%</t>
+          <t>14,44%</t>
         </is>
       </c>
       <c r="W50" s="2" t="inlineStr">
         <is>
-          <t>26,21%</t>
+          <t>26,96%</t>
         </is>
       </c>
     </row>
@@ -6059,57 +6059,57 @@
       </c>
       <c r="C51" s="2" t="inlineStr">
         <is>
+          <t>102</t>
+        </is>
+      </c>
+      <c r="D51" s="2" t="inlineStr">
+        <is>
+          <t>81394</t>
+        </is>
+      </c>
+      <c r="E51" s="2" t="inlineStr">
+        <is>
+          <t>81394</t>
+        </is>
+      </c>
+      <c r="F51" s="2" t="inlineStr">
+        <is>
+          <t>81394</t>
+        </is>
+      </c>
+      <c r="G51" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="H51" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="I51" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="J51" s="2" t="inlineStr">
+        <is>
           <t>81</t>
         </is>
       </c>
-      <c r="D51" s="2" t="inlineStr">
-        <is>
-          <t>50358</t>
-        </is>
-      </c>
-      <c r="E51" s="2" t="inlineStr">
-        <is>
-          <t>50358</t>
-        </is>
-      </c>
-      <c r="F51" s="2" t="inlineStr">
-        <is>
-          <t>50358</t>
-        </is>
-      </c>
-      <c r="G51" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="H51" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="I51" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="J51" s="2" t="inlineStr">
-        <is>
-          <t>102</t>
-        </is>
-      </c>
       <c r="K51" s="2" t="inlineStr">
         <is>
-          <t>80421</t>
+          <t>51512</t>
         </is>
       </c>
       <c r="L51" s="2" t="inlineStr">
         <is>
-          <t>80421</t>
+          <t>51512</t>
         </is>
       </c>
       <c r="M51" s="2" t="inlineStr">
         <is>
-          <t>80421</t>
+          <t>51512</t>
         </is>
       </c>
       <c r="N51" s="2" t="inlineStr">
@@ -6134,17 +6134,17 @@
       </c>
       <c r="R51" s="2" t="inlineStr">
         <is>
-          <t>130779</t>
+          <t>132906</t>
         </is>
       </c>
       <c r="S51" s="2" t="inlineStr">
         <is>
-          <t>130779</t>
+          <t>132906</t>
         </is>
       </c>
       <c r="T51" s="2" t="inlineStr">
         <is>
-          <t>130779</t>
+          <t>132906</t>
         </is>
       </c>
       <c r="U51" s="2" t="inlineStr">
@@ -6176,72 +6176,72 @@
       </c>
       <c r="C52" s="2" t="inlineStr">
         <is>
+          <t>27</t>
+        </is>
+      </c>
+      <c r="D52" s="2" t="inlineStr">
+        <is>
+          <t>17887</t>
+        </is>
+      </c>
+      <c r="E52" s="2" t="inlineStr">
+        <is>
+          <t>11365</t>
+        </is>
+      </c>
+      <c r="F52" s="2" t="inlineStr">
+        <is>
+          <t>26633</t>
+        </is>
+      </c>
+      <c r="G52" s="2" t="inlineStr">
+        <is>
+          <t>6,89%</t>
+        </is>
+      </c>
+      <c r="H52" s="2" t="inlineStr">
+        <is>
+          <t>4,38%</t>
+        </is>
+      </c>
+      <c r="I52" s="2" t="inlineStr">
+        <is>
+          <t>10,27%</t>
+        </is>
+      </c>
+      <c r="J52" s="2" t="inlineStr">
+        <is>
           <t>22</t>
         </is>
       </c>
-      <c r="D52" s="2" t="inlineStr">
-        <is>
-          <t>15781</t>
-        </is>
-      </c>
-      <c r="E52" s="2" t="inlineStr">
-        <is>
-          <t>9154</t>
-        </is>
-      </c>
-      <c r="F52" s="2" t="inlineStr">
-        <is>
-          <t>24443</t>
-        </is>
-      </c>
-      <c r="G52" s="2" t="inlineStr">
-        <is>
-          <t>6,26%</t>
-        </is>
-      </c>
-      <c r="H52" s="2" t="inlineStr">
-        <is>
-          <t>3,63%</t>
-        </is>
-      </c>
-      <c r="I52" s="2" t="inlineStr">
-        <is>
-          <t>9,69%</t>
-        </is>
-      </c>
-      <c r="J52" s="2" t="inlineStr">
-        <is>
-          <t>27</t>
-        </is>
-      </c>
       <c r="K52" s="2" t="inlineStr">
         <is>
-          <t>19851</t>
+          <t>16261</t>
         </is>
       </c>
       <c r="L52" s="2" t="inlineStr">
         <is>
-          <t>13446</t>
+          <t>10727</t>
         </is>
       </c>
       <c r="M52" s="2" t="inlineStr">
         <is>
-          <t>29446</t>
+          <t>24564</t>
         </is>
       </c>
       <c r="N52" s="2" t="inlineStr">
         <is>
-          <t>7,08%</t>
+          <t>7,39%</t>
         </is>
       </c>
       <c r="O52" s="2" t="inlineStr">
         <is>
-          <t>4,8%</t>
+          <t>4,87%</t>
         </is>
       </c>
       <c r="P52" s="2" t="inlineStr">
         <is>
-          <t>10,51%</t>
+          <t>11,16%</t>
         </is>
       </c>
       <c r="Q52" s="2" t="inlineStr">
@@ -6251,32 +6251,32 @@
       </c>
       <c r="R52" s="2" t="inlineStr">
         <is>
-          <t>35632</t>
+          <t>34148</t>
         </is>
       </c>
       <c r="S52" s="2" t="inlineStr">
         <is>
-          <t>25795</t>
+          <t>24846</t>
         </is>
       </c>
       <c r="T52" s="2" t="inlineStr">
         <is>
-          <t>46620</t>
+          <t>45405</t>
         </is>
       </c>
       <c r="U52" s="2" t="inlineStr">
         <is>
-          <t>6,69%</t>
+          <t>7,12%</t>
         </is>
       </c>
       <c r="V52" s="2" t="inlineStr">
         <is>
-          <t>4,84%</t>
+          <t>5,18%</t>
         </is>
       </c>
       <c r="W52" s="2" t="inlineStr">
         <is>
-          <t>8,76%</t>
+          <t>9,47%</t>
         </is>
       </c>
     </row>
@@ -6289,72 +6289,72 @@
       </c>
       <c r="C53" s="2" t="inlineStr">
         <is>
+          <t>95</t>
+        </is>
+      </c>
+      <c r="D53" s="2" t="inlineStr">
+        <is>
+          <t>62411</t>
+        </is>
+      </c>
+      <c r="E53" s="2" t="inlineStr">
+        <is>
+          <t>51807</t>
+        </is>
+      </c>
+      <c r="F53" s="2" t="inlineStr">
+        <is>
+          <t>75490</t>
+        </is>
+      </c>
+      <c r="G53" s="2" t="inlineStr">
+        <is>
+          <t>24,06%</t>
+        </is>
+      </c>
+      <c r="H53" s="2" t="inlineStr">
+        <is>
+          <t>19,97%</t>
+        </is>
+      </c>
+      <c r="I53" s="2" t="inlineStr">
+        <is>
+          <t>29,1%</t>
+        </is>
+      </c>
+      <c r="J53" s="2" t="inlineStr">
+        <is>
           <t>74</t>
         </is>
       </c>
-      <c r="D53" s="2" t="inlineStr">
-        <is>
-          <t>76668</t>
-        </is>
-      </c>
-      <c r="E53" s="2" t="inlineStr">
-        <is>
-          <t>51338</t>
-        </is>
-      </c>
-      <c r="F53" s="2" t="inlineStr">
-        <is>
-          <t>142413</t>
-        </is>
-      </c>
-      <c r="G53" s="2" t="inlineStr">
-        <is>
-          <t>30,41%</t>
-        </is>
-      </c>
-      <c r="H53" s="2" t="inlineStr">
-        <is>
-          <t>20,36%</t>
-        </is>
-      </c>
-      <c r="I53" s="2" t="inlineStr">
-        <is>
-          <t>56,48%</t>
-        </is>
-      </c>
-      <c r="J53" s="2" t="inlineStr">
-        <is>
-          <t>95</t>
-        </is>
-      </c>
       <c r="K53" s="2" t="inlineStr">
         <is>
-          <t>70971</t>
+          <t>46581</t>
         </is>
       </c>
       <c r="L53" s="2" t="inlineStr">
         <is>
-          <t>58500</t>
+          <t>37123</t>
         </is>
       </c>
       <c r="M53" s="2" t="inlineStr">
         <is>
-          <t>85366</t>
+          <t>57781</t>
         </is>
       </c>
       <c r="N53" s="2" t="inlineStr">
         <is>
-          <t>25,32%</t>
+          <t>21,16%</t>
         </is>
       </c>
       <c r="O53" s="2" t="inlineStr">
         <is>
-          <t>20,87%</t>
+          <t>16,87%</t>
         </is>
       </c>
       <c r="P53" s="2" t="inlineStr">
         <is>
-          <t>30,46%</t>
+          <t>26,25%</t>
         </is>
       </c>
       <c r="Q53" s="2" t="inlineStr">
@@ -6364,32 +6364,32 @@
       </c>
       <c r="R53" s="2" t="inlineStr">
         <is>
-          <t>147639</t>
+          <t>108992</t>
         </is>
       </c>
       <c r="S53" s="2" t="inlineStr">
         <is>
-          <t>121665</t>
+          <t>93544</t>
         </is>
       </c>
       <c r="T53" s="2" t="inlineStr">
         <is>
-          <t>210906</t>
+          <t>126008</t>
         </is>
       </c>
       <c r="U53" s="2" t="inlineStr">
         <is>
-          <t>27,73%</t>
+          <t>22,73%</t>
         </is>
       </c>
       <c r="V53" s="2" t="inlineStr">
         <is>
-          <t>22,85%</t>
+          <t>19,51%</t>
         </is>
       </c>
       <c r="W53" s="2" t="inlineStr">
         <is>
-          <t>39,61%</t>
+          <t>26,28%</t>
         </is>
       </c>
     </row>
@@ -6402,72 +6402,72 @@
       </c>
       <c r="C54" s="2" t="inlineStr">
         <is>
+          <t>153</t>
+        </is>
+      </c>
+      <c r="D54" s="2" t="inlineStr">
+        <is>
+          <t>106593</t>
+        </is>
+      </c>
+      <c r="E54" s="2" t="inlineStr">
+        <is>
+          <t>91276</t>
+        </is>
+      </c>
+      <c r="F54" s="2" t="inlineStr">
+        <is>
+          <t>120418</t>
+        </is>
+      </c>
+      <c r="G54" s="2" t="inlineStr">
+        <is>
+          <t>41,09%</t>
+        </is>
+      </c>
+      <c r="H54" s="2" t="inlineStr">
+        <is>
+          <t>35,18%</t>
+        </is>
+      </c>
+      <c r="I54" s="2" t="inlineStr">
+        <is>
+          <t>46,42%</t>
+        </is>
+      </c>
+      <c r="J54" s="2" t="inlineStr">
+        <is>
           <t>148</t>
         </is>
       </c>
-      <c r="D54" s="2" t="inlineStr">
-        <is>
-          <t>94588</t>
-        </is>
-      </c>
-      <c r="E54" s="2" t="inlineStr">
-        <is>
-          <t>60260</t>
-        </is>
-      </c>
-      <c r="F54" s="2" t="inlineStr">
-        <is>
-          <t>112187</t>
-        </is>
-      </c>
-      <c r="G54" s="2" t="inlineStr">
-        <is>
-          <t>37,51%</t>
-        </is>
-      </c>
-      <c r="H54" s="2" t="inlineStr">
-        <is>
-          <t>23,9%</t>
-        </is>
-      </c>
-      <c r="I54" s="2" t="inlineStr">
-        <is>
-          <t>44,49%</t>
-        </is>
-      </c>
-      <c r="J54" s="2" t="inlineStr">
-        <is>
-          <t>153</t>
-        </is>
-      </c>
       <c r="K54" s="2" t="inlineStr">
         <is>
-          <t>115337</t>
+          <t>91955</t>
         </is>
       </c>
       <c r="L54" s="2" t="inlineStr">
         <is>
-          <t>101797</t>
+          <t>80074</t>
         </is>
       </c>
       <c r="M54" s="2" t="inlineStr">
         <is>
-          <t>129402</t>
+          <t>104040</t>
         </is>
       </c>
       <c r="N54" s="2" t="inlineStr">
         <is>
-          <t>41,15%</t>
+          <t>41,77%</t>
         </is>
       </c>
       <c r="O54" s="2" t="inlineStr">
         <is>
-          <t>36,32%</t>
+          <t>36,38%</t>
         </is>
       </c>
       <c r="P54" s="2" t="inlineStr">
         <is>
-          <t>46,17%</t>
+          <t>47,27%</t>
         </is>
       </c>
       <c r="Q54" s="2" t="inlineStr">
@@ -6477,32 +6477,32 @@
       </c>
       <c r="R54" s="2" t="inlineStr">
         <is>
-          <t>209926</t>
+          <t>198547</t>
         </is>
       </c>
       <c r="S54" s="2" t="inlineStr">
         <is>
-          <t>172806</t>
+          <t>180456</t>
         </is>
       </c>
       <c r="T54" s="2" t="inlineStr">
         <is>
-          <t>230690</t>
+          <t>216630</t>
         </is>
       </c>
       <c r="U54" s="2" t="inlineStr">
         <is>
-          <t>39,43%</t>
+          <t>41,4%</t>
         </is>
       </c>
       <c r="V54" s="2" t="inlineStr">
         <is>
-          <t>32,46%</t>
+          <t>37,63%</t>
         </is>
       </c>
       <c r="W54" s="2" t="inlineStr">
         <is>
-          <t>43,33%</t>
+          <t>45,17%</t>
         </is>
       </c>
     </row>
@@ -6515,67 +6515,67 @@
       </c>
       <c r="C55" s="2" t="inlineStr">
         <is>
+          <t>58</t>
+        </is>
+      </c>
+      <c r="D55" s="2" t="inlineStr">
+        <is>
+          <t>46515</t>
+        </is>
+      </c>
+      <c r="E55" s="2" t="inlineStr">
+        <is>
+          <t>35486</t>
+        </is>
+      </c>
+      <c r="F55" s="2" t="inlineStr">
+        <is>
+          <t>58749</t>
+        </is>
+      </c>
+      <c r="G55" s="2" t="inlineStr">
+        <is>
+          <t>17,93%</t>
+        </is>
+      </c>
+      <c r="H55" s="2" t="inlineStr">
+        <is>
+          <t>13,68%</t>
+        </is>
+      </c>
+      <c r="I55" s="2" t="inlineStr">
+        <is>
+          <t>22,65%</t>
+        </is>
+      </c>
+      <c r="J55" s="2" t="inlineStr">
+        <is>
           <t>53</t>
         </is>
       </c>
-      <c r="D55" s="2" t="inlineStr">
-        <is>
-          <t>34821</t>
-        </is>
-      </c>
-      <c r="E55" s="2" t="inlineStr">
-        <is>
-          <t>23898</t>
-        </is>
-      </c>
-      <c r="F55" s="2" t="inlineStr">
-        <is>
-          <t>45198</t>
-        </is>
-      </c>
-      <c r="G55" s="2" t="inlineStr">
-        <is>
-          <t>13,81%</t>
-        </is>
-      </c>
-      <c r="H55" s="2" t="inlineStr">
-        <is>
-          <t>9,48%</t>
-        </is>
-      </c>
-      <c r="I55" s="2" t="inlineStr">
-        <is>
-          <t>17,93%</t>
-        </is>
-      </c>
-      <c r="J55" s="2" t="inlineStr">
-        <is>
-          <t>58</t>
-        </is>
-      </c>
       <c r="K55" s="2" t="inlineStr">
         <is>
-          <t>46232</t>
+          <t>35066</t>
         </is>
       </c>
       <c r="L55" s="2" t="inlineStr">
         <is>
-          <t>35108</t>
+          <t>26868</t>
         </is>
       </c>
       <c r="M55" s="2" t="inlineStr">
         <is>
-          <t>57106</t>
+          <t>44866</t>
         </is>
       </c>
       <c r="N55" s="2" t="inlineStr">
         <is>
-          <t>16,5%</t>
+          <t>15,93%</t>
         </is>
       </c>
       <c r="O55" s="2" t="inlineStr">
         <is>
-          <t>12,53%</t>
+          <t>12,21%</t>
         </is>
       </c>
       <c r="P55" s="2" t="inlineStr">
@@ -6590,32 +6590,32 @@
       </c>
       <c r="R55" s="2" t="inlineStr">
         <is>
-          <t>81054</t>
+          <t>81581</t>
         </is>
       </c>
       <c r="S55" s="2" t="inlineStr">
         <is>
-          <t>64375</t>
+          <t>68910</t>
         </is>
       </c>
       <c r="T55" s="2" t="inlineStr">
         <is>
-          <t>96832</t>
+          <t>96798</t>
         </is>
       </c>
       <c r="U55" s="2" t="inlineStr">
         <is>
-          <t>15,22%</t>
+          <t>17,01%</t>
         </is>
       </c>
       <c r="V55" s="2" t="inlineStr">
         <is>
-          <t>12,09%</t>
+          <t>14,37%</t>
         </is>
       </c>
       <c r="W55" s="2" t="inlineStr">
         <is>
-          <t>18,19%</t>
+          <t>20,19%</t>
         </is>
       </c>
     </row>
@@ -6628,72 +6628,72 @@
       </c>
       <c r="C56" s="2" t="inlineStr">
         <is>
+          <t>37</t>
+        </is>
+      </c>
+      <c r="D56" s="2" t="inlineStr">
+        <is>
+          <t>26023</t>
+        </is>
+      </c>
+      <c r="E56" s="2" t="inlineStr">
+        <is>
+          <t>18805</t>
+        </is>
+      </c>
+      <c r="F56" s="2" t="inlineStr">
+        <is>
+          <t>35751</t>
+        </is>
+      </c>
+      <c r="G56" s="2" t="inlineStr">
+        <is>
+          <t>10,03%</t>
+        </is>
+      </c>
+      <c r="H56" s="2" t="inlineStr">
+        <is>
+          <t>7,25%</t>
+        </is>
+      </c>
+      <c r="I56" s="2" t="inlineStr">
+        <is>
+          <t>13,78%</t>
+        </is>
+      </c>
+      <c r="J56" s="2" t="inlineStr">
+        <is>
           <t>47</t>
         </is>
       </c>
-      <c r="D56" s="2" t="inlineStr">
-        <is>
-          <t>30281</t>
-        </is>
-      </c>
-      <c r="E56" s="2" t="inlineStr">
-        <is>
-          <t>20236</t>
-        </is>
-      </c>
-      <c r="F56" s="2" t="inlineStr">
-        <is>
-          <t>40142</t>
-        </is>
-      </c>
-      <c r="G56" s="2" t="inlineStr">
-        <is>
-          <t>12,01%</t>
-        </is>
-      </c>
-      <c r="H56" s="2" t="inlineStr">
-        <is>
-          <t>8,03%</t>
-        </is>
-      </c>
-      <c r="I56" s="2" t="inlineStr">
-        <is>
-          <t>15,92%</t>
-        </is>
-      </c>
-      <c r="J56" s="2" t="inlineStr">
-        <is>
-          <t>37</t>
-        </is>
-      </c>
       <c r="K56" s="2" t="inlineStr">
         <is>
-          <t>27881</t>
+          <t>30258</t>
         </is>
       </c>
       <c r="L56" s="2" t="inlineStr">
         <is>
-          <t>20098</t>
+          <t>22842</t>
         </is>
       </c>
       <c r="M56" s="2" t="inlineStr">
         <is>
-          <t>38123</t>
+          <t>39824</t>
         </is>
       </c>
       <c r="N56" s="2" t="inlineStr">
         <is>
-          <t>9,95%</t>
+          <t>13,75%</t>
         </is>
       </c>
       <c r="O56" s="2" t="inlineStr">
         <is>
-          <t>7,17%</t>
+          <t>10,38%</t>
         </is>
       </c>
       <c r="P56" s="2" t="inlineStr">
         <is>
-          <t>13,6%</t>
+          <t>18,09%</t>
         </is>
       </c>
       <c r="Q56" s="2" t="inlineStr">
@@ -6703,32 +6703,32 @@
       </c>
       <c r="R56" s="2" t="inlineStr">
         <is>
-          <t>58162</t>
+          <t>56280</t>
         </is>
       </c>
       <c r="S56" s="2" t="inlineStr">
         <is>
-          <t>45025</t>
+          <t>45226</t>
         </is>
       </c>
       <c r="T56" s="2" t="inlineStr">
         <is>
-          <t>73119</t>
+          <t>69207</t>
         </is>
       </c>
       <c r="U56" s="2" t="inlineStr">
         <is>
-          <t>10,92%</t>
+          <t>11,74%</t>
         </is>
       </c>
       <c r="V56" s="2" t="inlineStr">
         <is>
-          <t>8,46%</t>
+          <t>9,43%</t>
         </is>
       </c>
       <c r="W56" s="2" t="inlineStr">
         <is>
-          <t>13,73%</t>
+          <t>14,43%</t>
         </is>
       </c>
     </row>
@@ -6741,57 +6741,57 @@
       </c>
       <c r="C57" s="2" t="inlineStr">
         <is>
+          <t>370</t>
+        </is>
+      </c>
+      <c r="D57" s="2" t="inlineStr">
+        <is>
+          <t>259429</t>
+        </is>
+      </c>
+      <c r="E57" s="2" t="inlineStr">
+        <is>
+          <t>259429</t>
+        </is>
+      </c>
+      <c r="F57" s="2" t="inlineStr">
+        <is>
+          <t>259429</t>
+        </is>
+      </c>
+      <c r="G57" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="H57" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="I57" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="J57" s="2" t="inlineStr">
+        <is>
           <t>344</t>
         </is>
       </c>
-      <c r="D57" s="2" t="inlineStr">
-        <is>
-          <t>252140</t>
-        </is>
-      </c>
-      <c r="E57" s="2" t="inlineStr">
-        <is>
-          <t>252140</t>
-        </is>
-      </c>
-      <c r="F57" s="2" t="inlineStr">
-        <is>
-          <t>252140</t>
-        </is>
-      </c>
-      <c r="G57" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="H57" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="I57" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="J57" s="2" t="inlineStr">
-        <is>
-          <t>370</t>
-        </is>
-      </c>
       <c r="K57" s="2" t="inlineStr">
         <is>
-          <t>280272</t>
+          <t>220120</t>
         </is>
       </c>
       <c r="L57" s="2" t="inlineStr">
         <is>
-          <t>280272</t>
+          <t>220120</t>
         </is>
       </c>
       <c r="M57" s="2" t="inlineStr">
         <is>
-          <t>280272</t>
+          <t>220120</t>
         </is>
       </c>
       <c r="N57" s="2" t="inlineStr">
@@ -6816,17 +6816,17 @@
       </c>
       <c r="R57" s="2" t="inlineStr">
         <is>
-          <t>532412</t>
+          <t>479549</t>
         </is>
       </c>
       <c r="S57" s="2" t="inlineStr">
         <is>
-          <t>532412</t>
+          <t>479549</t>
         </is>
       </c>
       <c r="T57" s="2" t="inlineStr">
         <is>
-          <t>532412</t>
+          <t>479549</t>
         </is>
       </c>
       <c r="U57" s="2" t="inlineStr">
